--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -25817,7 +25817,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>18d8f2802debcbc06cca471c291f6b513e298dfbff9ca8797a5c3be711cded88</t>
+          <t>60ec4d101de723d8022073123c44f9391887d602251d229b8c1329ae7b245f14</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>直接实测</t>
+          <t>构件族直接实测｜SRC-ZG-WF-001 PDF p83 / 印刷p68 / 2.3.1.3 / 表2-40；样本与东/西缝逐件对应UNKNOWN</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1602,18 +1602,34 @@
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>平均广395.5；厚280.5</t>
+          <t>实测组A 390×280；实测组B 401×281；均值广395.5；厚280.5</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr"/>
-      <c r="M20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>整殿实例长度由后续装配端点显式推导；Master reference length不得进入整殿实例</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
-      <c r="P20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="n">
+        <v>395.5</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>280.5</v>
+      </c>
       <c r="Q20" s="2" t="inlineStr"/>
       <c r="R20" s="2" t="inlineStr"/>
-      <c r="S20" s="2" t="inlineStr"/>
-      <c r="T20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>表2-40未将390×280与401×281逐一对应到东缝/西缝，禁止静默映射；报告归整为广26分、厚18分，仅作REPORT_INFERRED尺度分析，不作963历史设计值。图2-41示平梁与斗栱交接关系。</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>{"modeling_disposition":"DIRECT_MEASURED_SECTION / BUILDABLE","observed_section_samples_mm":[{"thickness":280,"width":390},{"thickness":281,"width":401}],"sample_to_instance_mapping":"UNKNOWN"}</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1643,7 +1659,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>直接实测</t>
+          <t>构件族直接实测｜SRC-ZG-WF-001 PDF p83 / 印刷p68 / 2.3.1.3 / 表2-40；样本与东/西缝逐件对应UNKNOWN</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1656,18 +1672,34 @@
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>平均广395.5；厚280.5</t>
+          <t>实测组A 390×280；实测组B 401×281；均值广395.5；厚280.5</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>整殿实例长度由后续装配端点显式推导；Master reference length不得进入整殿实例</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="n">
+        <v>395.5</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>280.5</v>
+      </c>
       <c r="Q21" s="2" t="inlineStr"/>
       <c r="R21" s="2" t="inlineStr"/>
-      <c r="S21" s="2" t="inlineStr"/>
-      <c r="T21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>表2-40未将390×280与401×281逐一对应到东缝/西缝，禁止静默映射；报告归整为广26分、厚18分，仅作REPORT_INFERRED尺度分析，不作963历史设计值。图2-41示平梁与斗栱交接关系。</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>{"modeling_disposition":"DIRECT_MEASURED_SECTION / BUILDABLE","observed_section_samples_mm":[{"thickness":280,"width":390},{"thickness":281,"width":401}],"sample_to_instance_mapping":"UNKNOWN"}</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1697,7 +1729,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>直接实测</t>
+          <t>数量/位置直接确认 + 山面型单一样本实测｜SRC-ZG-WF-001 PDF p83 / 印刷p68 / 2.3.1.3 / 表2-40；样本与东/西山逐件对应UNKNOWN</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1710,18 +1742,32 @@
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>广约346；厚未及</t>
+          <t>广346；厚未及（UNKNOWN）</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr"/>
-      <c r="M22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>整殿实例长度由后续装配端点显式推导；Master reference length不得进入整殿实例</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="n">
+        <v>346</v>
+      </c>
       <c r="P22" s="2" t="inlineStr"/>
       <c r="Q22" s="2" t="inlineStr"/>
       <c r="R22" s="2" t="inlineStr"/>
-      <c r="S22" s="2" t="inlineStr"/>
-      <c r="T22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>表2-40仅记录山面平梁广346mm，实测厚度未及/UNKNOWN；历史事实字段不得借用东西缝型280.5mm。为完整建模，另以同构件族东西缝实测均值截面比例显式补全 thickness=245.4mm，分类为PARAMETRIC_COMPLETION、可替换、非历史声明。报告将广归整为23分，仅作REPORT_INFERRED尺度分析。图2-41示平梁与斗栱交接关系。</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>{"modeling_disposition":"PARAMETRIC_COMPLETION / BUILDABLE / REPLACEABLE","observed_section_samples_mm":[{"thickness":null,"width":346}],"parametric_completion":{"classification":"PARAMETRIC_COMPLETION","field":"thickness_mm","formula":"346 * 280.5 / 395.5","historical_claim":false,"method":"preserve_east_west_seam_mean_section_aspect_ratio","note":"仅用于完整建模；不是报告实测厚度，也不是963年历史设计值。若后续取得山面平梁厚度直接证据，替换本值。","production_value_mm":245.4,"replaceable":true,"source_inputs_mm":{"east_west_mean_thickness_observed":280.5,"east_west_mean_width_observed":395.5,"gable_width_observed":346},"width_mm":{"classification":"PARAMETRIC_COMPLETION","historical_claim":false,"method":"generalize_single_observed_gable_sample_to_both_gable_instances","production_value_mm":346,"replaceable":true}},"sample_to_instance_mapping":"UNKNOWN"}</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1751,7 +1797,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>直接实测</t>
+          <t>数量/位置直接确认 + 山面型单一样本实测｜SRC-ZG-WF-001 PDF p83 / 印刷p68 / 2.3.1.3 / 表2-40；样本与东/西山逐件对应UNKNOWN</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1764,18 +1810,32 @@
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>广约346；厚未及</t>
+          <t>广346；厚未及（UNKNOWN）</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>整殿实例长度由后续装配端点显式推导；Master reference length不得进入整殿实例</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr"/>
-      <c r="O23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="n">
+        <v>346</v>
+      </c>
       <c r="P23" s="2" t="inlineStr"/>
       <c r="Q23" s="2" t="inlineStr"/>
       <c r="R23" s="2" t="inlineStr"/>
-      <c r="S23" s="2" t="inlineStr"/>
-      <c r="T23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>表2-40仅记录山面平梁广346mm，实测厚度未及/UNKNOWN；历史事实字段不得借用东西缝型280.5mm。为完整建模，另以同构件族东西缝实测均值截面比例显式补全 thickness=245.4mm，分类为PARAMETRIC_COMPLETION、可替换、非历史声明。报告将广归整为23分，仅作REPORT_INFERRED尺度分析。图2-41示平梁与斗栱交接关系。</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>{"modeling_disposition":"PARAMETRIC_COMPLETION / BUILDABLE / REPLACEABLE","observed_section_samples_mm":[{"thickness":null,"width":346}],"parametric_completion":{"classification":"PARAMETRIC_COMPLETION","field":"thickness_mm","formula":"346 * 280.5 / 395.5","historical_claim":false,"method":"preserve_east_west_seam_mean_section_aspect_ratio","note":"仅用于完整建模；不是报告实测厚度，也不是963年历史设计值。若后续取得山面平梁厚度直接证据，替换本值。","production_value_mm":245.4,"replaceable":true,"source_inputs_mm":{"east_west_mean_thickness_observed":280.5,"east_west_mean_width_observed":395.5,"gable_width_observed":346},"width_mm":{"classification":"PARAMETRIC_COMPLETION","historical_claim":false,"method":"generalize_single_observed_gable_sample_to_both_gable_instances","production_value_mm":346,"replaceable":true}},"sample_to_instance_mapping":"UNKNOWN"}</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -27847,7 +27907,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>02856c23e5ba34b9cb6bb07bb3e25afd69c87968</t>
+          <t>db2578b291547ed5816d095bdc543f2c51aede86</t>
         </is>
       </c>
     </row>
@@ -27859,7 +27919,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>e6299d8306fd4f58dac29a43230d387c2f63ca4056d002fd03803df02bb072a7</t>
+          <t>6709d7c9940368c51ac43b903e96ce442ed958f8b2385ed8825099a885f2dddf</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -1865,7 +1865,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>总数+南北丁栿构造关系明确</t>
+          <t>数量/位置直接确认 + 构件族8组截面实测｜SRC-ZG-WF-001 PDF p81/83 / 印刷p66/68 / §2.3.1 + §2.3.1.3 / 表2-40；8组样本与8根实例逐一映射UNKNOWN</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -1874,22 +1874,30 @@
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>平均广331.6；厚200.9</t>
+          <t>构件族8组实测均值：广331.6；厚200.9</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>由装配端点求长</t>
+          <t>由装配端点求长；historical full length remains UNKNOWN</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr"/>
-      <c r="P24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="n">
+        <v>331.6</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>200.9</v>
+      </c>
       <c r="Q24" s="2" t="inlineStr"/>
       <c r="R24" s="2" t="inlineStr"/>
       <c r="S24" s="2" t="inlineStr"/>
-      <c r="T24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN"}</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1919,7 +1927,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>总数+南北丁栿构造关系明确</t>
+          <t>数量/位置直接确认 + 构件族8组截面实测｜SRC-ZG-WF-001 PDF p81/83 / 印刷p66/68 / §2.3.1 + §2.3.1.3 / 表2-40；8组样本与8根实例逐一映射UNKNOWN</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -1928,22 +1936,30 @@
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>平均广331.6；厚200.9</t>
+          <t>构件族8组实测均值：广331.6；厚200.9</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>由装配端点求长</t>
+          <t>由装配端点求长；historical full length remains UNKNOWN</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr"/>
-      <c r="O25" s="2" t="inlineStr"/>
-      <c r="P25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="n">
+        <v>331.6</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>200.9</v>
+      </c>
       <c r="Q25" s="2" t="inlineStr"/>
       <c r="R25" s="2" t="inlineStr"/>
       <c r="S25" s="2" t="inlineStr"/>
-      <c r="T25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN"}</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1973,7 +1989,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>总数+南北丁栿构造关系明确</t>
+          <t>数量/位置直接确认 + 构件族8组截面实测｜SRC-ZG-WF-001 PDF p81/83 / 印刷p66/68 / §2.3.1 + §2.3.1.3 / 表2-40；8组样本与8根实例逐一映射UNKNOWN</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1982,22 +1998,30 @@
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>平均广331.6；厚200.9</t>
+          <t>构件族8组实测均值：广331.6；厚200.9</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>由装配端点求长</t>
+          <t>由装配端点求长；historical full length remains UNKNOWN</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
-      <c r="P26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="n">
+        <v>331.6</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>200.9</v>
+      </c>
       <c r="Q26" s="2" t="inlineStr"/>
       <c r="R26" s="2" t="inlineStr"/>
       <c r="S26" s="2" t="inlineStr"/>
-      <c r="T26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN"}</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2027,7 +2051,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>总数+南北丁栿构造关系明确</t>
+          <t>数量/位置直接确认 + 构件族8组截面实测｜SRC-ZG-WF-001 PDF p81/83 / 印刷p66/68 / §2.3.1 + §2.3.1.3 / 表2-40；8组样本与8根实例逐一映射UNKNOWN</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -2036,22 +2060,30 @@
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>平均广331.6；厚200.9</t>
+          <t>构件族8组实测均值：广331.6；厚200.9</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>由装配端点求长</t>
+          <t>由装配端点求长；historical full length remains UNKNOWN</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="n">
+        <v>331.6</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>200.9</v>
+      </c>
       <c r="Q27" s="2" t="inlineStr"/>
       <c r="R27" s="2" t="inlineStr"/>
       <c r="S27" s="2" t="inlineStr"/>
-      <c r="T27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN"}</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2081,7 +2113,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>总数+南北丁栿构造关系明确</t>
+          <t>数量/位置直接确认 + 构件族8组截面实测｜SRC-ZG-WF-001 PDF p81/83 / 印刷p66/68 / §2.3.1 + §2.3.1.3 / 表2-40；8组样本与8根实例逐一映射UNKNOWN</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -2090,22 +2122,30 @@
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>平均广331.6；厚200.9</t>
+          <t>构件族8组实测均值：广331.6；厚200.9</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>由装配端点求长</t>
+          <t>由装配端点求长；historical full length remains UNKNOWN</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
-      <c r="P28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="n">
+        <v>331.6</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>200.9</v>
+      </c>
       <c r="Q28" s="2" t="inlineStr"/>
       <c r="R28" s="2" t="inlineStr"/>
       <c r="S28" s="2" t="inlineStr"/>
-      <c r="T28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN"}</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2135,7 +2175,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>总数+南北丁栿构造关系明确</t>
+          <t>数量/位置直接确认 + 构件族8组截面实测｜SRC-ZG-WF-001 PDF p81/83 / 印刷p66/68 / §2.3.1 + §2.3.1.3 / 表2-40；8组样本与8根实例逐一映射UNKNOWN</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -2144,22 +2184,30 @@
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>平均广331.6；厚200.9</t>
+          <t>构件族8组实测均值：广331.6；厚200.9</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>由装配端点求长</t>
+          <t>由装配端点求长；historical full length remains UNKNOWN</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr"/>
-      <c r="P29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="n">
+        <v>331.6</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>200.9</v>
+      </c>
       <c r="Q29" s="2" t="inlineStr"/>
       <c r="R29" s="2" t="inlineStr"/>
       <c r="S29" s="2" t="inlineStr"/>
-      <c r="T29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN"}</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2189,7 +2237,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>总数+南北丁栿构造关系明确</t>
+          <t>数量/位置直接确认 + 构件族8组截面实测｜SRC-ZG-WF-001 PDF p81/83 / 印刷p66/68 / §2.3.1 + §2.3.1.3 / 表2-40；8组样本与8根实例逐一映射UNKNOWN</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -2198,22 +2246,30 @@
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>平均广331.6；厚200.9</t>
+          <t>构件族8组实测均值：广331.6；厚200.9</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>由装配端点求长</t>
+          <t>由装配端点求长；historical full length remains UNKNOWN</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr"/>
-      <c r="P30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="n">
+        <v>331.6</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>200.9</v>
+      </c>
       <c r="Q30" s="2" t="inlineStr"/>
       <c r="R30" s="2" t="inlineStr"/>
       <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN"}</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2243,7 +2299,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>总数+南北丁栿构造关系明确</t>
+          <t>数量/位置直接确认 + 构件族8组截面实测｜SRC-ZG-WF-001 PDF p81/83 / 印刷p66/68 / §2.3.1 + §2.3.1.3 / 表2-40；8组样本与8根实例逐一映射UNKNOWN</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -2252,22 +2308,30 @@
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>平均广331.6；厚200.9</t>
+          <t>构件族8组实测均值：广331.6；厚200.9</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>由装配端点求长</t>
+          <t>由装配端点求长；historical full length remains UNKNOWN</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="2" t="inlineStr"/>
-      <c r="P31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="n">
+        <v>331.6</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>200.9</v>
+      </c>
       <c r="Q31" s="2" t="inlineStr"/>
       <c r="R31" s="2" t="inlineStr"/>
       <c r="S31" s="2" t="inlineStr"/>
-      <c r="T31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN"}</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -27907,7 +27971,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>db2578b291547ed5816d095bdc543f2c51aede86</t>
+          <t>eac26994df8d12be8c3fdf48c85a77700bced42f</t>
         </is>
       </c>
     </row>
@@ -27919,7 +27983,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>6709d7c9940368c51ac43b903e96ce442ed958f8b2385ed8825099a885f2dddf</t>
+          <t>41a73a20883036f70b7b441ff2d9f16450ad6ddb553dc098db9d851ca39c7acb</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -2361,7 +2361,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>报告直接说明四角上、下斜乳栿共8根</t>
+          <t>数量/位置直接确认 + 构件族6组完整截面实测 + 同建筑交接照片｜SRC-ZG-WF-001 PDF p83-84 / 印刷p68-69 / §2.3.1.3 / 表2-40 / 图2-42；表中8行对应8根实例的逐一映射UNKNOWN，其中2行未及</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -2370,18 +2370,30 @@
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>平均广330.5；厚187.2</t>
+          <t>构件族6组完整实测均值：广330.5；厚187.2</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr"/>
-      <c r="M32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>由装配端点求长；historical full length remains UNKNOWN</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr"/>
-      <c r="P32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="n">
+        <v>330.5</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>187.2</v>
+      </c>
       <c r="Q32" s="2" t="inlineStr"/>
       <c r="R32" s="2" t="inlineStr"/>
       <c r="S32" s="2" t="inlineStr"/>
-      <c r="T32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"NE","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"UPPER"},"sample_to_instance_mapping":"UNKNOWN","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -2411,7 +2423,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>报告直接说明四角上、下斜乳栿共8根</t>
+          <t>数量/位置直接确认 + 构件族6组完整截面实测 + 同建筑交接照片｜SRC-ZG-WF-001 PDF p83-84 / 印刷p68-69 / §2.3.1.3 / 表2-40 / 图2-42；表中8行对应8根实例的逐一映射UNKNOWN，其中2行未及</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -2420,18 +2432,30 @@
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>平均广330.5；厚187.2</t>
+          <t>构件族6组完整实测均值：广330.5；厚187.2</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr"/>
-      <c r="M33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>由装配端点求长；historical full length remains UNKNOWN</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr"/>
-      <c r="O33" s="2" t="inlineStr"/>
-      <c r="P33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="n">
+        <v>330.5</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>187.2</v>
+      </c>
       <c r="Q33" s="2" t="inlineStr"/>
       <c r="R33" s="2" t="inlineStr"/>
       <c r="S33" s="2" t="inlineStr"/>
-      <c r="T33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"NE","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"LOWER"},"sample_to_instance_mapping":"UNKNOWN","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2461,7 +2485,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>报告直接说明四角上、下斜乳栿共8根</t>
+          <t>数量/位置直接确认 + 构件族6组完整截面实测 + 同建筑交接照片｜SRC-ZG-WF-001 PDF p83-84 / 印刷p68-69 / §2.3.1.3 / 表2-40 / 图2-42；表中8行对应8根实例的逐一映射UNKNOWN，其中2行未及</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
@@ -2470,18 +2494,30 @@
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>平均广330.5；厚187.2</t>
+          <t>构件族6组完整实测均值：广330.5；厚187.2</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr"/>
-      <c r="M34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>由装配端点求长；historical full length remains UNKNOWN</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr"/>
-      <c r="P34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="n">
+        <v>330.5</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>187.2</v>
+      </c>
       <c r="Q34" s="2" t="inlineStr"/>
       <c r="R34" s="2" t="inlineStr"/>
       <c r="S34" s="2" t="inlineStr"/>
-      <c r="T34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"SE","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"UPPER"},"sample_to_instance_mapping":"UNKNOWN","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2511,7 +2547,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>报告直接说明四角上、下斜乳栿共8根</t>
+          <t>数量/位置直接确认 + 构件族6组完整截面实测 + 同建筑交接照片｜SRC-ZG-WF-001 PDF p83-84 / 印刷p68-69 / §2.3.1.3 / 表2-40 / 图2-42；表中8行对应8根实例的逐一映射UNKNOWN，其中2行未及</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
@@ -2520,18 +2556,30 @@
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>平均广330.5；厚187.2</t>
+          <t>构件族6组完整实测均值：广330.5；厚187.2</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr"/>
-      <c r="M35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>由装配端点求长；historical full length remains UNKNOWN</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr"/>
-      <c r="O35" s="2" t="inlineStr"/>
-      <c r="P35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="n">
+        <v>330.5</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>187.2</v>
+      </c>
       <c r="Q35" s="2" t="inlineStr"/>
       <c r="R35" s="2" t="inlineStr"/>
       <c r="S35" s="2" t="inlineStr"/>
-      <c r="T35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"SE","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"LOWER"},"sample_to_instance_mapping":"UNKNOWN","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2561,7 +2609,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>报告直接说明四角上、下斜乳栿共8根</t>
+          <t>数量/位置直接确认 + 构件族6组完整截面实测 + 同建筑交接照片｜SRC-ZG-WF-001 PDF p83-84 / 印刷p68-69 / §2.3.1.3 / 表2-40 / 图2-42；表中8行对应8根实例的逐一映射UNKNOWN，其中2行未及</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
@@ -2570,18 +2618,30 @@
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>平均广330.5；厚187.2</t>
+          <t>构件族6组完整实测均值：广330.5；厚187.2</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr"/>
-      <c r="M36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>由装配端点求长；historical full length remains UNKNOWN</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="2" t="inlineStr"/>
-      <c r="P36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="n">
+        <v>330.5</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>187.2</v>
+      </c>
       <c r="Q36" s="2" t="inlineStr"/>
       <c r="R36" s="2" t="inlineStr"/>
       <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"SW","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"UPPER"},"sample_to_instance_mapping":"UNKNOWN","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2611,7 +2671,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>报告直接说明四角上、下斜乳栿共8根</t>
+          <t>数量/位置直接确认 + 构件族6组完整截面实测 + 同建筑交接照片｜SRC-ZG-WF-001 PDF p83-84 / 印刷p68-69 / §2.3.1.3 / 表2-40 / 图2-42；表中8行对应8根实例的逐一映射UNKNOWN，其中2行未及</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
@@ -2620,18 +2680,30 @@
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>平均广330.5；厚187.2</t>
+          <t>构件族6组完整实测均值：广330.5；厚187.2</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr"/>
-      <c r="M37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>由装配端点求长；historical full length remains UNKNOWN</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr"/>
-      <c r="O37" s="2" t="inlineStr"/>
-      <c r="P37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="n">
+        <v>330.5</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>187.2</v>
+      </c>
       <c r="Q37" s="2" t="inlineStr"/>
       <c r="R37" s="2" t="inlineStr"/>
       <c r="S37" s="2" t="inlineStr"/>
-      <c r="T37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"SW","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"LOWER"},"sample_to_instance_mapping":"UNKNOWN","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2661,7 +2733,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>报告直接说明四角上、下斜乳栿共8根</t>
+          <t>数量/位置直接确认 + 构件族6组完整截面实测 + 同建筑交接照片｜SRC-ZG-WF-001 PDF p83-84 / 印刷p68-69 / §2.3.1.3 / 表2-40 / 图2-42；表中8行对应8根实例的逐一映射UNKNOWN，其中2行未及</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -2670,18 +2742,30 @@
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>平均广330.5；厚187.2</t>
+          <t>构件族6组完整实测均值：广330.5；厚187.2</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr"/>
-      <c r="M38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>由装配端点求长；historical full length remains UNKNOWN</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="2" t="inlineStr"/>
-      <c r="P38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="n">
+        <v>330.5</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>187.2</v>
+      </c>
       <c r="Q38" s="2" t="inlineStr"/>
       <c r="R38" s="2" t="inlineStr"/>
       <c r="S38" s="2" t="inlineStr"/>
-      <c r="T38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"NW","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"UPPER"},"sample_to_instance_mapping":"UNKNOWN","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2711,7 +2795,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>报告直接说明四角上、下斜乳栿共8根</t>
+          <t>数量/位置直接确认 + 构件族6组完整截面实测 + 同建筑交接照片｜SRC-ZG-WF-001 PDF p83-84 / 印刷p68-69 / §2.3.1.3 / 表2-40 / 图2-42；表中8行对应8根实例的逐一映射UNKNOWN，其中2行未及</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -2720,18 +2804,30 @@
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>平均广330.5；厚187.2</t>
+          <t>构件族6组完整实测均值：广330.5；厚187.2</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>由装配端点求长；historical full length remains UNKNOWN</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr"/>
-      <c r="O39" s="2" t="inlineStr"/>
-      <c r="P39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="n">
+        <v>330.5</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>187.2</v>
+      </c>
       <c r="Q39" s="2" t="inlineStr"/>
       <c r="R39" s="2" t="inlineStr"/>
       <c r="S39" s="2" t="inlineStr"/>
-      <c r="T39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"NW","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"LOWER"},"sample_to_instance_mapping":"UNKNOWN","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -27971,7 +28067,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>eac26994df8d12be8c3fdf48c85a77700bced42f</t>
+          <t>411778c2f80a0fd506e15381c06aac21433c394d</t>
         </is>
       </c>
     </row>
@@ -27983,7 +28079,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>41a73a20883036f70b7b441ff2d9f16450ad6ddb553dc098db9d851ca39c7acb</t>
+          <t>32ca8de69b9f6b2878f591dccceb9beac76c7e712462f216a69d61949490233a</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -665,7 +665,11 @@
       <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr"/>
       <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -719,7 +723,11 @@
       <c r="Q3" s="2" t="inlineStr"/>
       <c r="R3" s="2" t="inlineStr"/>
       <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -773,7 +781,11 @@
       <c r="Q4" s="2" t="inlineStr"/>
       <c r="R4" s="2" t="inlineStr"/>
       <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -827,7 +839,11 @@
       <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="inlineStr"/>
       <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -881,7 +897,11 @@
       <c r="Q6" s="2" t="inlineStr"/>
       <c r="R6" s="2" t="inlineStr"/>
       <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -935,7 +955,11 @@
       <c r="Q7" s="2" t="inlineStr"/>
       <c r="R7" s="2" t="inlineStr"/>
       <c r="S7" s="2" t="inlineStr"/>
-      <c r="T7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -989,7 +1013,11 @@
       <c r="Q8" s="2" t="inlineStr"/>
       <c r="R8" s="2" t="inlineStr"/>
       <c r="S8" s="2" t="inlineStr"/>
-      <c r="T8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1043,7 +1071,11 @@
       <c r="Q9" s="2" t="inlineStr"/>
       <c r="R9" s="2" t="inlineStr"/>
       <c r="S9" s="2" t="inlineStr"/>
-      <c r="T9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1097,7 +1129,11 @@
       <c r="Q10" s="2" t="inlineStr"/>
       <c r="R10" s="2" t="inlineStr"/>
       <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1151,7 +1187,11 @@
       <c r="Q11" s="2" t="inlineStr"/>
       <c r="R11" s="2" t="inlineStr"/>
       <c r="S11" s="2" t="inlineStr"/>
-      <c r="T11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1205,7 +1245,11 @@
       <c r="Q12" s="2" t="inlineStr"/>
       <c r="R12" s="2" t="inlineStr"/>
       <c r="S12" s="2" t="inlineStr"/>
-      <c r="T12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1259,7 +1303,11 @@
       <c r="Q13" s="2" t="inlineStr"/>
       <c r="R13" s="2" t="inlineStr"/>
       <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1309,7 +1357,11 @@
       <c r="Q14" s="2" t="inlineStr"/>
       <c r="R14" s="2" t="inlineStr"/>
       <c r="S14" s="2" t="inlineStr"/>
-      <c r="T14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-LOWER-SIX-CHUANFU-001_MASTER","stage1_disposition":"已有Master｜需长度桥"}</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1359,7 +1411,11 @@
       <c r="Q15" s="2" t="inlineStr"/>
       <c r="R15" s="2" t="inlineStr"/>
       <c r="S15" s="2" t="inlineStr"/>
-      <c r="T15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-UPPER-SIX-CHUANFU-001_MASTER","stage1_disposition":"已有Master｜需长度桥"}</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1409,7 +1465,11 @@
       <c r="Q16" s="2" t="inlineStr"/>
       <c r="R16" s="2" t="inlineStr"/>
       <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-FOUR-CHUANFU-001_MASTER","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1459,7 +1519,11 @@
       <c r="Q17" s="2" t="inlineStr"/>
       <c r="R17" s="2" t="inlineStr"/>
       <c r="S17" s="2" t="inlineStr"/>
-      <c r="T17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-LOWER-SIX-CHUANFU-001_MASTER","stage1_disposition":"已有Master｜需长度桥"}</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1509,7 +1573,11 @@
       <c r="Q18" s="2" t="inlineStr"/>
       <c r="R18" s="2" t="inlineStr"/>
       <c r="S18" s="2" t="inlineStr"/>
-      <c r="T18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-UPPER-SIX-CHUANFU-001_MASTER","stage1_disposition":"已有Master｜需长度桥"}</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1559,7 +1627,11 @@
       <c r="Q19" s="2" t="inlineStr"/>
       <c r="R19" s="2" t="inlineStr"/>
       <c r="S19" s="2" t="inlineStr"/>
-      <c r="T19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-FOUR-CHUANFU-001_MASTER","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1627,7 +1699,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>{"modeling_disposition":"DIRECT_MEASURED_SECTION / BUILDABLE","observed_section_samples_mm":[{"thickness":280,"width":390},{"thickness":281,"width":401}],"sample_to_instance_mapping":"UNKNOWN"}</t>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-PINGLIANG-001_MASTER","modeling_disposition":"DIRECT_MEASURED_SECTION / BUILDABLE","observed_section_samples_mm":[{"thickness":280,"width":390},{"thickness":281,"width":401}],"sample_to_instance_mapping":"UNKNOWN","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1769,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>{"modeling_disposition":"DIRECT_MEASURED_SECTION / BUILDABLE","observed_section_samples_mm":[{"thickness":280,"width":390},{"thickness":281,"width":401}],"sample_to_instance_mapping":"UNKNOWN"}</t>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-PINGLIANG-001_MASTER","modeling_disposition":"DIRECT_MEASURED_SECTION / BUILDABLE","observed_section_samples_mm":[{"thickness":280,"width":390},{"thickness":281,"width":401}],"sample_to_instance_mapping":"UNKNOWN","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1837,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>{"modeling_disposition":"PARAMETRIC_COMPLETION / BUILDABLE / REPLACEABLE","observed_section_samples_mm":[{"thickness":null,"width":346}],"parametric_completion":{"classification":"PARAMETRIC_COMPLETION","field":"thickness_mm","formula":"346 * 280.5 / 395.5","historical_claim":false,"method":"preserve_east_west_seam_mean_section_aspect_ratio","note":"仅用于完整建模；不是报告实测厚度，也不是963年历史设计值。若后续取得山面平梁厚度直接证据，替换本值。","production_value_mm":245.4,"replaceable":true,"source_inputs_mm":{"east_west_mean_thickness_observed":280.5,"east_west_mean_width_observed":395.5,"gable_width_observed":346},"width_mm":{"classification":"PARAMETRIC_COMPLETION","historical_claim":false,"method":"generalize_single_observed_gable_sample_to_both_gable_instances","production_value_mm":346,"replaceable":true}},"sample_to_instance_mapping":"UNKNOWN"}</t>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-PINGLIANG-001_MASTER","modeling_disposition":"PARAMETRIC_COMPLETION / BUILDABLE / REPLACEABLE","observed_section_samples_mm":[{"thickness":null,"width":346}],"parametric_completion":{"classification":"PARAMETRIC_COMPLETION","field":"thickness_mm","formula":"346 * 280.5 / 395.5","historical_claim":false,"method":"preserve_east_west_seam_mean_section_aspect_ratio","note":"仅用于完整建模；不是报告实测厚度，也不是963年历史设计值。若后续取得山面平梁厚度直接证据，替换本值。","production_value_mm":245.4,"replaceable":true,"source_inputs_mm":{"east_west_mean_thickness_observed":280.5,"east_west_mean_width_observed":395.5,"gable_width_observed":346},"width_mm":{"classification":"PARAMETRIC_COMPLETION","historical_claim":false,"method":"generalize_single_observed_gable_sample_to_both_gable_instances","production_value_mm":346,"replaceable":true}},"sample_to_instance_mapping":"UNKNOWN","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1905,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>{"modeling_disposition":"PARAMETRIC_COMPLETION / BUILDABLE / REPLACEABLE","observed_section_samples_mm":[{"thickness":null,"width":346}],"parametric_completion":{"classification":"PARAMETRIC_COMPLETION","field":"thickness_mm","formula":"346 * 280.5 / 395.5","historical_claim":false,"method":"preserve_east_west_seam_mean_section_aspect_ratio","note":"仅用于完整建模；不是报告实测厚度，也不是963年历史设计值。若后续取得山面平梁厚度直接证据，替换本值。","production_value_mm":245.4,"replaceable":true,"source_inputs_mm":{"east_west_mean_thickness_observed":280.5,"east_west_mean_width_observed":395.5,"gable_width_observed":346},"width_mm":{"classification":"PARAMETRIC_COMPLETION","historical_claim":false,"method":"generalize_single_observed_gable_sample_to_both_gable_instances","production_value_mm":346,"replaceable":true}},"sample_to_instance_mapping":"UNKNOWN"}</t>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-PINGLIANG-001_MASTER","modeling_disposition":"PARAMETRIC_COMPLETION / BUILDABLE / REPLACEABLE","observed_section_samples_mm":[{"thickness":null,"width":346}],"parametric_completion":{"classification":"PARAMETRIC_COMPLETION","field":"thickness_mm","formula":"346 * 280.5 / 395.5","historical_claim":false,"method":"preserve_east_west_seam_mean_section_aspect_ratio","note":"仅用于完整建模；不是报告实测厚度，也不是963年历史设计值。若后续取得山面平梁厚度直接证据，替换本值。","production_value_mm":245.4,"replaceable":true,"source_inputs_mm":{"east_west_mean_thickness_observed":280.5,"east_west_mean_width_observed":395.5,"gable_width_observed":346},"width_mm":{"classification":"PARAMETRIC_COMPLETION","historical_claim":false,"method":"generalize_single_observed_gable_sample_to_both_gable_instances","production_value_mm":346,"replaceable":true}},"sample_to_instance_mapping":"UNKNOWN","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1967,7 @@
       <c r="S24" s="2" t="inlineStr"/>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN"}</t>
+          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-DINGFU-001_MASTER","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -1957,7 +2029,7 @@
       <c r="S25" s="2" t="inlineStr"/>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN"}</t>
+          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-DINGFU-001_MASTER","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2091,7 @@
       <c r="S26" s="2" t="inlineStr"/>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN"}</t>
+          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-DINGFU-001_MASTER","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2153,7 @@
       <c r="S27" s="2" t="inlineStr"/>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN"}</t>
+          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-DINGFU-001_MASTER","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2215,7 @@
       <c r="S28" s="2" t="inlineStr"/>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN"}</t>
+          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-DINGFU-001_MASTER","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2277,7 @@
       <c r="S29" s="2" t="inlineStr"/>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN"}</t>
+          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-DINGFU-001_MASTER","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2339,7 @@
       <c r="S30" s="2" t="inlineStr"/>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN"}</t>
+          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-DINGFU-001_MASTER","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2401,7 @@
       <c r="S31" s="2" t="inlineStr"/>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN"}</t>
+          <t>{"assembly_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC","paired_spacing_note":"组合构造中两根丁栿、斜乳栿间距一材一栔，垫单材栿一层","role":"山面梁架联系构件；前后各一道；上承两山承椽枋和太平梁"},"end_semantics":{"classification":"DIRECT_SOURCE_SEMANTIC / EXACT_JOINERY_GEOMETRY_UNRESOLVED","inboard":"内端削成骑栿栱与榑交构","outboard":"外端入山面柱头铺作"},"joinery_note":"报告明确提到丁栿入斗栱处刻出槽口；槽口存在性有直接文字依据，但精确位置/尺寸/轮廓未闭合，Stage1不得静默精细化。","master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-DINGFU-001_MASTER","modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":208,"width":346},{"thickness":199,"width":324},{"thickness":205,"width":335},{"note":"source table marks this thickness with （含）","thickness":174,"width":324},{"thickness":203,"width":330},{"thickness":195,"width":330},{"thickness":203,"width":336},{"thickness":193,"width":328}],"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":13.1,"width":21.7},"rounded_fen":{"thickness":13,"width":22}},"sample_to_instance_mapping":"UNKNOWN","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2463,7 @@
       <c r="S32" s="2" t="inlineStr"/>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"NE","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"UPPER"},"sample_to_instance_mapping":"UNKNOWN","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
+          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-RUFU-001_MASTER","measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"NE","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"UPPER"},"sample_to_instance_mapping":"UNKNOWN","stage1_disposition":"需新建Master","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2525,7 @@
       <c r="S33" s="2" t="inlineStr"/>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"NE","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"LOWER"},"sample_to_instance_mapping":"UNKNOWN","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
+          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-RUFU-001_MASTER","measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"NE","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"LOWER"},"sample_to_instance_mapping":"UNKNOWN","stage1_disposition":"需新建Master","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2587,7 @@
       <c r="S34" s="2" t="inlineStr"/>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"SE","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"UPPER"},"sample_to_instance_mapping":"UNKNOWN","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
+          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-RUFU-001_MASTER","measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"SE","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"UPPER"},"sample_to_instance_mapping":"UNKNOWN","stage1_disposition":"需新建Master","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2649,7 @@
       <c r="S35" s="2" t="inlineStr"/>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"SE","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"LOWER"},"sample_to_instance_mapping":"UNKNOWN","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
+          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-RUFU-001_MASTER","measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"SE","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"LOWER"},"sample_to_instance_mapping":"UNKNOWN","stage1_disposition":"需新建Master","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2711,7 @@
       <c r="S36" s="2" t="inlineStr"/>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"SW","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"UPPER"},"sample_to_instance_mapping":"UNKNOWN","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
+          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-RUFU-001_MASTER","measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"SW","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"UPPER"},"sample_to_instance_mapping":"UNKNOWN","stage1_disposition":"需新建Master","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2773,7 @@
       <c r="S37" s="2" t="inlineStr"/>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"SW","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"LOWER"},"sample_to_instance_mapping":"UNKNOWN","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
+          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-RUFU-001_MASTER","measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"SW","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"LOWER"},"sample_to_instance_mapping":"UNKNOWN","stage1_disposition":"需新建Master","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2835,7 @@
       <c r="S38" s="2" t="inlineStr"/>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"NW","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"UPPER"},"sample_to_instance_mapping":"UNKNOWN","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
+          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-RUFU-001_MASTER","measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"NW","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"UPPER"},"sample_to_instance_mapping":"UNKNOWN","stage1_disposition":"需新建Master","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2897,7 @@
       <c r="S39" s="2" t="inlineStr"/>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"NW","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"LOWER"},"sample_to_instance_mapping":"UNKNOWN","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
+          <t>{"complete_measured_sample_count":6,"groove_boundary":{"exact_dimensions":null,"exact_position":null,"source_note":"报告正文明确提到斜乳栿入斗栱处刻出槽口","stage1_cut_geometry":false,"status":"DIRECT_EXISTENCE / GEOMETRY_DEFERRED"},"historical_full_length_mm":null,"interface_semantics":{"bracket_end":"与斗栱交接","classification":"DIRECT_SOURCE_SEMANTIC + DIRECT_GAP","opposite_end":"UNKNOWN / ASSEMBLY_ENDPOINT_TO_BE_RESOLVED"},"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-FRAME-RUFU-001_MASTER","measurement_table_row_count":8,"modeling_disposition":"DIRECT_MEASURED_FAMILY_MEAN / BUILDABLE","observed_section_samples_mm":[{"thickness":185,"width":331},{"thickness":186,"width":337},{"thickness":193,"width":323},{"thickness":185,"width":342},{"thickness":188,"width":325},{"thickness":186,"width":325}],"placement_rule":{"classification":"ASSEMBLY_OWNED / DEFERRED_TO_STAGE2_OR_LATER","exact_length_mm":null,"exact_plan_angle_deg":null,"member_type":"DIAGONAL_FRAME_MEMBER","rule":"derive orientation and length later from explicit assembly endpoints; do not bake 45 degrees or canonical reference length into building"},"report_analysis":{"classification":"REPORT_INFERRED / METADATA_ONLY / NOT_963_DESIGN_FACT","converted_fen":{"thickness":12.2,"width":21.6},"rounded_fen":{"thickness":12,"width":22}},"role_semantics":{"corner":"NW","geometry_policy":"ASSEMBLY_ROLE_ONLY / NO GEOMETRY_DIFFERENCE_YET","vertical_role":"LOWER"},"sample_to_instance_mapping":"UNKNOWN","stage1_disposition":"需新建Master","unmeasured_table_row_count":2,"visual_reference":{"caption":"万佛殿斜乳栿与斗栱交接关系","classification":"SAME_BUILDING_DIRECT_PHOTO","locator":"PDF p84 / printed p69 / Fig.2-42","source_id":"SRC-ZG-WF-001"}}</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2949,11 @@
       <c r="Q40" s="2" t="inlineStr"/>
       <c r="R40" s="2" t="inlineStr"/>
       <c r="S40" s="2" t="inlineStr"/>
-      <c r="T40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2927,7 +3003,11 @@
       <c r="Q41" s="2" t="inlineStr"/>
       <c r="R41" s="2" t="inlineStr"/>
       <c r="S41" s="2" t="inlineStr"/>
-      <c r="T41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2977,7 +3057,11 @@
       <c r="Q42" s="2" t="inlineStr"/>
       <c r="R42" s="2" t="inlineStr"/>
       <c r="S42" s="2" t="inlineStr"/>
-      <c r="T42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3027,7 +3111,11 @@
       <c r="Q43" s="2" t="inlineStr"/>
       <c r="R43" s="2" t="inlineStr"/>
       <c r="S43" s="2" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3077,7 +3165,11 @@
       <c r="Q44" s="2" t="inlineStr"/>
       <c r="R44" s="2" t="inlineStr"/>
       <c r="S44" s="2" t="inlineStr"/>
-      <c r="T44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3127,7 +3219,11 @@
       <c r="Q45" s="2" t="inlineStr"/>
       <c r="R45" s="2" t="inlineStr"/>
       <c r="S45" s="2" t="inlineStr"/>
-      <c r="T45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3177,7 +3273,11 @@
       <c r="Q46" s="2" t="inlineStr"/>
       <c r="R46" s="2" t="inlineStr"/>
       <c r="S46" s="2" t="inlineStr"/>
-      <c r="T46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3227,7 +3327,11 @@
       <c r="Q47" s="2" t="inlineStr"/>
       <c r="R47" s="2" t="inlineStr"/>
       <c r="S47" s="2" t="inlineStr"/>
-      <c r="T47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3277,7 +3381,11 @@
       <c r="Q48" s="2" t="inlineStr"/>
       <c r="R48" s="2" t="inlineStr"/>
       <c r="S48" s="2" t="inlineStr"/>
-      <c r="T48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3327,7 +3435,11 @@
       <c r="Q49" s="2" t="inlineStr"/>
       <c r="R49" s="2" t="inlineStr"/>
       <c r="S49" s="2" t="inlineStr"/>
-      <c r="T49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3377,7 +3489,11 @@
       <c r="Q50" s="2" t="inlineStr"/>
       <c r="R50" s="2" t="inlineStr"/>
       <c r="S50" s="2" t="inlineStr"/>
-      <c r="T50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3427,7 +3543,11 @@
       <c r="Q51" s="2" t="inlineStr"/>
       <c r="R51" s="2" t="inlineStr"/>
       <c r="S51" s="2" t="inlineStr"/>
-      <c r="T51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3477,7 +3597,11 @@
       <c r="Q52" s="2" t="inlineStr"/>
       <c r="R52" s="2" t="inlineStr"/>
       <c r="S52" s="2" t="inlineStr"/>
-      <c r="T52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3527,7 +3651,11 @@
       <c r="Q53" s="2" t="inlineStr"/>
       <c r="R53" s="2" t="inlineStr"/>
       <c r="S53" s="2" t="inlineStr"/>
-      <c r="T53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3577,7 +3705,11 @@
       <c r="Q54" s="2" t="inlineStr"/>
       <c r="R54" s="2" t="inlineStr"/>
       <c r="S54" s="2" t="inlineStr"/>
-      <c r="T54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3627,7 +3759,11 @@
       <c r="Q55" s="2" t="inlineStr"/>
       <c r="R55" s="2" t="inlineStr"/>
       <c r="S55" s="2" t="inlineStr"/>
-      <c r="T55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3677,7 +3813,11 @@
       <c r="Q56" s="2" t="inlineStr"/>
       <c r="R56" s="2" t="inlineStr"/>
       <c r="S56" s="2" t="inlineStr"/>
-      <c r="T56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3727,7 +3867,11 @@
       <c r="Q57" s="2" t="inlineStr"/>
       <c r="R57" s="2" t="inlineStr"/>
       <c r="S57" s="2" t="inlineStr"/>
-      <c r="T57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3777,7 +3921,11 @@
       <c r="Q58" s="2" t="inlineStr"/>
       <c r="R58" s="2" t="inlineStr"/>
       <c r="S58" s="2" t="inlineStr"/>
-      <c r="T58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3827,7 +3975,11 @@
       <c r="Q59" s="2" t="inlineStr"/>
       <c r="R59" s="2" t="inlineStr"/>
       <c r="S59" s="2" t="inlineStr"/>
-      <c r="T59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3877,7 +4029,11 @@
       <c r="Q60" s="2" t="inlineStr"/>
       <c r="R60" s="2" t="inlineStr"/>
       <c r="S60" s="2" t="inlineStr"/>
-      <c r="T60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3927,7 +4083,11 @@
       <c r="Q61" s="2" t="inlineStr"/>
       <c r="R61" s="2" t="inlineStr"/>
       <c r="S61" s="2" t="inlineStr"/>
-      <c r="T61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3977,7 +4137,11 @@
       <c r="Q62" s="2" t="inlineStr"/>
       <c r="R62" s="2" t="inlineStr"/>
       <c r="S62" s="2" t="inlineStr"/>
-      <c r="T62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4027,7 +4191,11 @@
       <c r="Q63" s="2" t="inlineStr"/>
       <c r="R63" s="2" t="inlineStr"/>
       <c r="S63" s="2" t="inlineStr"/>
-      <c r="T63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4077,7 +4245,11 @@
       <c r="Q64" s="2" t="inlineStr"/>
       <c r="R64" s="2" t="inlineStr"/>
       <c r="S64" s="2" t="inlineStr"/>
-      <c r="T64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4127,7 +4299,11 @@
       <c r="Q65" s="2" t="inlineStr"/>
       <c r="R65" s="2" t="inlineStr"/>
       <c r="S65" s="2" t="inlineStr"/>
-      <c r="T65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4177,7 +4353,11 @@
       <c r="Q66" s="2" t="inlineStr"/>
       <c r="R66" s="2" t="inlineStr"/>
       <c r="S66" s="2" t="inlineStr"/>
-      <c r="T66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4227,7 +4407,11 @@
       <c r="Q67" s="2" t="inlineStr"/>
       <c r="R67" s="2" t="inlineStr"/>
       <c r="S67" s="2" t="inlineStr"/>
-      <c r="T67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4277,7 +4461,11 @@
       <c r="Q68" s="2" t="inlineStr"/>
       <c r="R68" s="2" t="inlineStr"/>
       <c r="S68" s="2" t="inlineStr"/>
-      <c r="T68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4327,7 +4515,11 @@
       <c r="Q69" s="2" t="inlineStr"/>
       <c r="R69" s="2" t="inlineStr"/>
       <c r="S69" s="2" t="inlineStr"/>
-      <c r="T69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4377,7 +4569,11 @@
       <c r="Q70" s="2" t="inlineStr"/>
       <c r="R70" s="2" t="inlineStr"/>
       <c r="S70" s="2" t="inlineStr"/>
-      <c r="T70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4427,7 +4623,11 @@
       <c r="Q71" s="2" t="inlineStr"/>
       <c r="R71" s="2" t="inlineStr"/>
       <c r="S71" s="2" t="inlineStr"/>
-      <c r="T71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4477,7 +4677,11 @@
       <c r="Q72" s="2" t="inlineStr"/>
       <c r="R72" s="2" t="inlineStr"/>
       <c r="S72" s="2" t="inlineStr"/>
-      <c r="T72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4527,7 +4731,11 @@
       <c r="Q73" s="2" t="inlineStr"/>
       <c r="R73" s="2" t="inlineStr"/>
       <c r="S73" s="2" t="inlineStr"/>
-      <c r="T73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -4577,7 +4785,11 @@
       <c r="Q74" s="2" t="inlineStr"/>
       <c r="R74" s="2" t="inlineStr"/>
       <c r="S74" s="2" t="inlineStr"/>
-      <c r="T74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4627,7 +4839,11 @@
       <c r="Q75" s="2" t="inlineStr"/>
       <c r="R75" s="2" t="inlineStr"/>
       <c r="S75" s="2" t="inlineStr"/>
-      <c r="T75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4677,7 +4893,11 @@
       <c r="Q76" s="2" t="inlineStr"/>
       <c r="R76" s="2" t="inlineStr"/>
       <c r="S76" s="2" t="inlineStr"/>
-      <c r="T76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4727,7 +4947,11 @@
       <c r="Q77" s="2" t="inlineStr"/>
       <c r="R77" s="2" t="inlineStr"/>
       <c r="S77" s="2" t="inlineStr"/>
-      <c r="T77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4777,7 +5001,11 @@
       <c r="Q78" s="2" t="inlineStr"/>
       <c r="R78" s="2" t="inlineStr"/>
       <c r="S78" s="2" t="inlineStr"/>
-      <c r="T78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -4827,7 +5055,11 @@
       <c r="Q79" s="2" t="inlineStr"/>
       <c r="R79" s="2" t="inlineStr"/>
       <c r="S79" s="2" t="inlineStr"/>
-      <c r="T79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4877,7 +5109,11 @@
       <c r="Q80" s="2" t="inlineStr"/>
       <c r="R80" s="2" t="inlineStr"/>
       <c r="S80" s="2" t="inlineStr"/>
-      <c r="T80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4927,7 +5163,11 @@
       <c r="Q81" s="2" t="inlineStr"/>
       <c r="R81" s="2" t="inlineStr"/>
       <c r="S81" s="2" t="inlineStr"/>
-      <c r="T81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4977,7 +5217,11 @@
       <c r="Q82" s="2" t="inlineStr"/>
       <c r="R82" s="2" t="inlineStr"/>
       <c r="S82" s="2" t="inlineStr"/>
-      <c r="T82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5027,7 +5271,11 @@
       <c r="Q83" s="2" t="inlineStr"/>
       <c r="R83" s="2" t="inlineStr"/>
       <c r="S83" s="2" t="inlineStr"/>
-      <c r="T83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5077,7 +5325,11 @@
       <c r="Q84" s="2" t="inlineStr"/>
       <c r="R84" s="2" t="inlineStr"/>
       <c r="S84" s="2" t="inlineStr"/>
-      <c r="T84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5127,7 +5379,11 @@
       <c r="Q85" s="2" t="inlineStr"/>
       <c r="R85" s="2" t="inlineStr"/>
       <c r="S85" s="2" t="inlineStr"/>
-      <c r="T85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5177,7 +5433,11 @@
       <c r="Q86" s="2" t="inlineStr"/>
       <c r="R86" s="2" t="inlineStr"/>
       <c r="S86" s="2" t="inlineStr"/>
-      <c r="T86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5229,7 +5489,7 @@
       <c r="S87" s="2" t="inlineStr"/>
       <c r="T87" s="2" t="inlineStr">
         <is>
-          <t>{"section_rule":"有单件实测则用单件，否则参数化/未知"}</t>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","section_rule":"有单件实测则用单件，否则参数化/未知","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5543,7 @@
       <c r="S88" s="2" t="inlineStr"/>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>{"section_rule":"有单件实测则用单件，否则参数化/未知"}</t>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","section_rule":"有单件实测则用单件，否则参数化/未知","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5597,7 @@
       <c r="S89" s="2" t="inlineStr"/>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>{"section_rule":"有单件实测则用单件，否则参数化/未知"}</t>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","section_rule":"有单件实测则用单件，否则参数化/未知","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5651,7 @@
       <c r="S90" s="2" t="inlineStr"/>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>{"section_rule":"有单件实测则用单件，否则参数化/未知"}</t>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","section_rule":"有单件实测则用单件，否则参数化/未知","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5705,7 @@
       <c r="S91" s="2" t="inlineStr"/>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>{"section_rule":"有单件实测则用单件，否则参数化/未知"}</t>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","section_rule":"有单件实测则用单件，否则参数化/未知","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5759,7 @@
       <c r="S92" s="2" t="inlineStr"/>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>{"section_rule":"有单件实测则用单件，否则参数化/未知"}</t>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","section_rule":"有单件实测则用单件，否则参数化/未知","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5813,7 @@
       <c r="S93" s="2" t="inlineStr"/>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>{"section_rule":"有单件实测则用单件，否则参数化/未知"}</t>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","section_rule":"有单件实测则用单件，否则参数化/未知","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5867,7 @@
       <c r="S94" s="2" t="inlineStr"/>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>{"section_rule":"有单件实测则用单件，否则参数化/未知"}</t>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","section_rule":"有单件实测则用单件，否则参数化/未知","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5921,7 @@
       <c r="S95" s="2" t="inlineStr"/>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>{"section_rule":"有单件实测则用单件，否则参数化/未知"}</t>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","section_rule":"有单件实测则用单件，否则参数化/未知","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -5715,7 +5975,7 @@
       <c r="S96" s="2" t="inlineStr"/>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>{"section_rule":"有单件实测则用单件，否则参数化/未知"}</t>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","section_rule":"有单件实测则用单件，否则参数化/未知","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -5769,7 +6029,7 @@
       <c r="S97" s="2" t="inlineStr"/>
       <c r="T97" s="2" t="inlineStr">
         <is>
-          <t>{"section_rule":"有单件实测则用单件，否则参数化/未知"}</t>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","section_rule":"有单件实测则用单件，否则参数化/未知","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -5823,7 +6083,7 @@
       <c r="S98" s="2" t="inlineStr"/>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>{"section_rule":"有单件实测则用单件，否则参数化/未知"}</t>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","section_rule":"有单件实测则用单件，否则参数化/未知","stage1_disposition":"需新建Master"}</t>
         </is>
       </c>
     </row>
@@ -5875,7 +6135,11 @@
       <c r="Q99" s="2" t="inlineStr"/>
       <c r="R99" s="2" t="inlineStr"/>
       <c r="S99" s="2" t="inlineStr"/>
-      <c r="T99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -5925,7 +6189,11 @@
       <c r="Q100" s="2" t="inlineStr"/>
       <c r="R100" s="2" t="inlineStr"/>
       <c r="S100" s="2" t="inlineStr"/>
-      <c r="T100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -5975,7 +6243,11 @@
       <c r="Q101" s="2" t="inlineStr"/>
       <c r="R101" s="2" t="inlineStr"/>
       <c r="S101" s="2" t="inlineStr"/>
-      <c r="T101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -6025,7 +6297,11 @@
       <c r="Q102" s="2" t="inlineStr"/>
       <c r="R102" s="2" t="inlineStr"/>
       <c r="S102" s="2" t="inlineStr"/>
-      <c r="T102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -6075,7 +6351,11 @@
       <c r="Q103" s="2" t="inlineStr"/>
       <c r="R103" s="2" t="inlineStr"/>
       <c r="S103" s="2" t="inlineStr"/>
-      <c r="T103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -6125,7 +6405,11 @@
       <c r="Q104" s="2" t="inlineStr"/>
       <c r="R104" s="2" t="inlineStr"/>
       <c r="S104" s="2" t="inlineStr"/>
-      <c r="T104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -6175,7 +6459,11 @@
       <c r="Q105" s="2" t="inlineStr"/>
       <c r="R105" s="2" t="inlineStr"/>
       <c r="S105" s="2" t="inlineStr"/>
-      <c r="T105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6225,7 +6513,11 @@
       <c r="Q106" s="2" t="inlineStr"/>
       <c r="R106" s="2" t="inlineStr"/>
       <c r="S106" s="2" t="inlineStr"/>
-      <c r="T106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -6275,7 +6567,11 @@
       <c r="Q107" s="2" t="inlineStr"/>
       <c r="R107" s="2" t="inlineStr"/>
       <c r="S107" s="2" t="inlineStr"/>
-      <c r="T107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6325,7 +6621,11 @@
       <c r="Q108" s="2" t="inlineStr"/>
       <c r="R108" s="2" t="inlineStr"/>
       <c r="S108" s="2" t="inlineStr"/>
-      <c r="T108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -6375,7 +6675,11 @@
       <c r="Q109" s="2" t="inlineStr"/>
       <c r="R109" s="2" t="inlineStr"/>
       <c r="S109" s="2" t="inlineStr"/>
-      <c r="T109" s="2" t="inlineStr"/>
+      <c r="T109" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -6425,7 +6729,11 @@
       <c r="Q110" s="2" t="inlineStr"/>
       <c r="R110" s="2" t="inlineStr"/>
       <c r="S110" s="2" t="inlineStr"/>
-      <c r="T110" s="2" t="inlineStr"/>
+      <c r="T110" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6475,7 +6783,11 @@
       <c r="Q111" s="2" t="inlineStr"/>
       <c r="R111" s="2" t="inlineStr"/>
       <c r="S111" s="2" t="inlineStr"/>
-      <c r="T111" s="2" t="inlineStr"/>
+      <c r="T111" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -6525,7 +6837,11 @@
       <c r="Q112" s="2" t="inlineStr"/>
       <c r="R112" s="2" t="inlineStr"/>
       <c r="S112" s="2" t="inlineStr"/>
-      <c r="T112" s="2" t="inlineStr"/>
+      <c r="T112" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -6575,7 +6891,11 @@
       <c r="Q113" s="2" t="inlineStr"/>
       <c r="R113" s="2" t="inlineStr"/>
       <c r="S113" s="2" t="inlineStr"/>
-      <c r="T113" s="2" t="inlineStr"/>
+      <c r="T113" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -6625,7 +6945,11 @@
       <c r="Q114" s="2" t="inlineStr"/>
       <c r="R114" s="2" t="inlineStr"/>
       <c r="S114" s="2" t="inlineStr"/>
-      <c r="T114" s="2" t="inlineStr"/>
+      <c r="T114" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -6675,7 +6999,11 @@
       <c r="Q115" s="2" t="inlineStr"/>
       <c r="R115" s="2" t="inlineStr"/>
       <c r="S115" s="2" t="inlineStr"/>
-      <c r="T115" s="2" t="inlineStr"/>
+      <c r="T115" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -6725,7 +7053,11 @@
       <c r="Q116" s="2" t="inlineStr"/>
       <c r="R116" s="2" t="inlineStr"/>
       <c r="S116" s="2" t="inlineStr"/>
-      <c r="T116" s="2" t="inlineStr"/>
+      <c r="T116" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -6775,7 +7107,11 @@
       <c r="Q117" s="2" t="inlineStr"/>
       <c r="R117" s="2" t="inlineStr"/>
       <c r="S117" s="2" t="inlineStr"/>
-      <c r="T117" s="2" t="inlineStr"/>
+      <c r="T117" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -6825,7 +7161,11 @@
       <c r="Q118" s="2" t="inlineStr"/>
       <c r="R118" s="2" t="inlineStr"/>
       <c r="S118" s="2" t="inlineStr"/>
-      <c r="T118" s="2" t="inlineStr"/>
+      <c r="T118" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -6875,7 +7215,11 @@
       <c r="Q119" s="2" t="inlineStr"/>
       <c r="R119" s="2" t="inlineStr"/>
       <c r="S119" s="2" t="inlineStr"/>
-      <c r="T119" s="2" t="inlineStr"/>
+      <c r="T119" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -6925,7 +7269,11 @@
       <c r="Q120" s="2" t="inlineStr"/>
       <c r="R120" s="2" t="inlineStr"/>
       <c r="S120" s="2" t="inlineStr"/>
-      <c r="T120" s="2" t="inlineStr"/>
+      <c r="T120" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -6975,7 +7323,11 @@
       <c r="Q121" s="2" t="inlineStr"/>
       <c r="R121" s="2" t="inlineStr"/>
       <c r="S121" s="2" t="inlineStr"/>
-      <c r="T121" s="2" t="inlineStr"/>
+      <c r="T121" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -7025,7 +7377,11 @@
       <c r="Q122" s="2" t="inlineStr"/>
       <c r="R122" s="2" t="inlineStr"/>
       <c r="S122" s="2" t="inlineStr"/>
-      <c r="T122" s="2" t="inlineStr"/>
+      <c r="T122" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -7075,7 +7431,11 @@
       <c r="Q123" s="2" t="inlineStr"/>
       <c r="R123" s="2" t="inlineStr"/>
       <c r="S123" s="2" t="inlineStr"/>
-      <c r="T123" s="2" t="inlineStr"/>
+      <c r="T123" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -7125,7 +7485,11 @@
       <c r="Q124" s="2" t="inlineStr"/>
       <c r="R124" s="2" t="inlineStr"/>
       <c r="S124" s="2" t="inlineStr"/>
-      <c r="T124" s="2" t="inlineStr"/>
+      <c r="T124" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -7175,7 +7539,11 @@
       <c r="Q125" s="2" t="inlineStr"/>
       <c r="R125" s="2" t="inlineStr"/>
       <c r="S125" s="2" t="inlineStr"/>
-      <c r="T125" s="2" t="inlineStr"/>
+      <c r="T125" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -7225,7 +7593,11 @@
       <c r="Q126" s="2" t="inlineStr"/>
       <c r="R126" s="2" t="inlineStr"/>
       <c r="S126" s="2" t="inlineStr"/>
-      <c r="T126" s="2" t="inlineStr"/>
+      <c r="T126" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -7275,7 +7647,11 @@
       <c r="Q127" s="2" t="inlineStr"/>
       <c r="R127" s="2" t="inlineStr"/>
       <c r="S127" s="2" t="inlineStr"/>
-      <c r="T127" s="2" t="inlineStr"/>
+      <c r="T127" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -7325,7 +7701,11 @@
       <c r="Q128" s="2" t="inlineStr"/>
       <c r="R128" s="2" t="inlineStr"/>
       <c r="S128" s="2" t="inlineStr"/>
-      <c r="T128" s="2" t="inlineStr"/>
+      <c r="T128" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -7375,7 +7755,11 @@
       <c r="Q129" s="2" t="inlineStr"/>
       <c r="R129" s="2" t="inlineStr"/>
       <c r="S129" s="2" t="inlineStr"/>
-      <c r="T129" s="2" t="inlineStr"/>
+      <c r="T129" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -7425,7 +7809,11 @@
       <c r="Q130" s="2" t="inlineStr"/>
       <c r="R130" s="2" t="inlineStr"/>
       <c r="S130" s="2" t="inlineStr"/>
-      <c r="T130" s="2" t="inlineStr"/>
+      <c r="T130" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -7475,7 +7863,11 @@
       <c r="Q131" s="2" t="inlineStr"/>
       <c r="R131" s="2" t="inlineStr"/>
       <c r="S131" s="2" t="inlineStr"/>
-      <c r="T131" s="2" t="inlineStr"/>
+      <c r="T131" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -7525,7 +7917,11 @@
       <c r="Q132" s="2" t="inlineStr"/>
       <c r="R132" s="2" t="inlineStr"/>
       <c r="S132" s="2" t="inlineStr"/>
-      <c r="T132" s="2" t="inlineStr"/>
+      <c r="T132" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -7575,7 +7971,11 @@
       <c r="Q133" s="2" t="inlineStr"/>
       <c r="R133" s="2" t="inlineStr"/>
       <c r="S133" s="2" t="inlineStr"/>
-      <c r="T133" s="2" t="inlineStr"/>
+      <c r="T133" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -7625,7 +8025,11 @@
       <c r="Q134" s="2" t="inlineStr"/>
       <c r="R134" s="2" t="inlineStr"/>
       <c r="S134" s="2" t="inlineStr"/>
-      <c r="T134" s="2" t="inlineStr"/>
+      <c r="T134" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -7675,7 +8079,11 @@
       <c r="Q135" s="2" t="inlineStr"/>
       <c r="R135" s="2" t="inlineStr"/>
       <c r="S135" s="2" t="inlineStr"/>
-      <c r="T135" s="2" t="inlineStr"/>
+      <c r="T135" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -7725,7 +8133,11 @@
       <c r="Q136" s="2" t="inlineStr"/>
       <c r="R136" s="2" t="inlineStr"/>
       <c r="S136" s="2" t="inlineStr"/>
-      <c r="T136" s="2" t="inlineStr"/>
+      <c r="T136" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -7775,7 +8187,11 @@
       <c r="Q137" s="2" t="inlineStr"/>
       <c r="R137" s="2" t="inlineStr"/>
       <c r="S137" s="2" t="inlineStr"/>
-      <c r="T137" s="2" t="inlineStr"/>
+      <c r="T137" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -7825,7 +8241,11 @@
       <c r="Q138" s="2" t="inlineStr"/>
       <c r="R138" s="2" t="inlineStr"/>
       <c r="S138" s="2" t="inlineStr"/>
-      <c r="T138" s="2" t="inlineStr"/>
+      <c r="T138" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -7875,7 +8295,11 @@
       <c r="Q139" s="2" t="inlineStr"/>
       <c r="R139" s="2" t="inlineStr"/>
       <c r="S139" s="2" t="inlineStr"/>
-      <c r="T139" s="2" t="inlineStr"/>
+      <c r="T139" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -7925,7 +8349,11 @@
       <c r="Q140" s="2" t="inlineStr"/>
       <c r="R140" s="2" t="inlineStr"/>
       <c r="S140" s="2" t="inlineStr"/>
-      <c r="T140" s="2" t="inlineStr"/>
+      <c r="T140" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -7975,7 +8403,11 @@
       <c r="Q141" s="2" t="inlineStr"/>
       <c r="R141" s="2" t="inlineStr"/>
       <c r="S141" s="2" t="inlineStr"/>
-      <c r="T141" s="2" t="inlineStr"/>
+      <c r="T141" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -8025,7 +8457,11 @@
       <c r="Q142" s="2" t="inlineStr"/>
       <c r="R142" s="2" t="inlineStr"/>
       <c r="S142" s="2" t="inlineStr"/>
-      <c r="T142" s="2" t="inlineStr"/>
+      <c r="T142" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -8075,7 +8511,11 @@
       <c r="Q143" s="2" t="inlineStr"/>
       <c r="R143" s="2" t="inlineStr"/>
       <c r="S143" s="2" t="inlineStr"/>
-      <c r="T143" s="2" t="inlineStr"/>
+      <c r="T143" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -8125,7 +8565,11 @@
       <c r="Q144" s="2" t="inlineStr"/>
       <c r="R144" s="2" t="inlineStr"/>
       <c r="S144" s="2" t="inlineStr"/>
-      <c r="T144" s="2" t="inlineStr"/>
+      <c r="T144" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -8175,7 +8619,11 @@
       <c r="Q145" s="2" t="inlineStr"/>
       <c r="R145" s="2" t="inlineStr"/>
       <c r="S145" s="2" t="inlineStr"/>
-      <c r="T145" s="2" t="inlineStr"/>
+      <c r="T145" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -8225,7 +8673,11 @@
       <c r="Q146" s="2" t="inlineStr"/>
       <c r="R146" s="2" t="inlineStr"/>
       <c r="S146" s="2" t="inlineStr"/>
-      <c r="T146" s="2" t="inlineStr"/>
+      <c r="T146" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -8275,7 +8727,11 @@
       <c r="Q147" s="2" t="inlineStr"/>
       <c r="R147" s="2" t="inlineStr"/>
       <c r="S147" s="2" t="inlineStr"/>
-      <c r="T147" s="2" t="inlineStr"/>
+      <c r="T147" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -8325,7 +8781,11 @@
       <c r="Q148" s="2" t="inlineStr"/>
       <c r="R148" s="2" t="inlineStr"/>
       <c r="S148" s="2" t="inlineStr"/>
-      <c r="T148" s="2" t="inlineStr"/>
+      <c r="T148" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -8375,7 +8835,11 @@
       <c r="Q149" s="2" t="inlineStr"/>
       <c r="R149" s="2" t="inlineStr"/>
       <c r="S149" s="2" t="inlineStr"/>
-      <c r="T149" s="2" t="inlineStr"/>
+      <c r="T149" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -8425,7 +8889,11 @@
       <c r="Q150" s="2" t="inlineStr"/>
       <c r="R150" s="2" t="inlineStr"/>
       <c r="S150" s="2" t="inlineStr"/>
-      <c r="T150" s="2" t="inlineStr"/>
+      <c r="T150" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -8475,7 +8943,11 @@
       <c r="Q151" s="2" t="inlineStr"/>
       <c r="R151" s="2" t="inlineStr"/>
       <c r="S151" s="2" t="inlineStr"/>
-      <c r="T151" s="2" t="inlineStr"/>
+      <c r="T151" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -8525,7 +8997,11 @@
       <c r="Q152" s="2" t="inlineStr"/>
       <c r="R152" s="2" t="inlineStr"/>
       <c r="S152" s="2" t="inlineStr"/>
-      <c r="T152" s="2" t="inlineStr"/>
+      <c r="T152" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -8575,7 +9051,11 @@
       <c r="Q153" s="2" t="inlineStr"/>
       <c r="R153" s="2" t="inlineStr"/>
       <c r="S153" s="2" t="inlineStr"/>
-      <c r="T153" s="2" t="inlineStr"/>
+      <c r="T153" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -8625,7 +9105,11 @@
       <c r="Q154" s="2" t="inlineStr"/>
       <c r="R154" s="2" t="inlineStr"/>
       <c r="S154" s="2" t="inlineStr"/>
-      <c r="T154" s="2" t="inlineStr"/>
+      <c r="T154" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -8675,7 +9159,11 @@
       <c r="Q155" s="2" t="inlineStr"/>
       <c r="R155" s="2" t="inlineStr"/>
       <c r="S155" s="2" t="inlineStr"/>
-      <c r="T155" s="2" t="inlineStr"/>
+      <c r="T155" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -8725,7 +9213,11 @@
       <c r="Q156" s="2" t="inlineStr"/>
       <c r="R156" s="2" t="inlineStr"/>
       <c r="S156" s="2" t="inlineStr"/>
-      <c r="T156" s="2" t="inlineStr"/>
+      <c r="T156" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -8775,7 +9267,11 @@
       <c r="Q157" s="2" t="inlineStr"/>
       <c r="R157" s="2" t="inlineStr"/>
       <c r="S157" s="2" t="inlineStr"/>
-      <c r="T157" s="2" t="inlineStr"/>
+      <c r="T157" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -8825,7 +9321,11 @@
       <c r="Q158" s="2" t="inlineStr"/>
       <c r="R158" s="2" t="inlineStr"/>
       <c r="S158" s="2" t="inlineStr"/>
-      <c r="T158" s="2" t="inlineStr"/>
+      <c r="T158" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -8875,7 +9375,11 @@
       <c r="Q159" s="2" t="inlineStr"/>
       <c r="R159" s="2" t="inlineStr"/>
       <c r="S159" s="2" t="inlineStr"/>
-      <c r="T159" s="2" t="inlineStr"/>
+      <c r="T159" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -8925,7 +9429,11 @@
       <c r="Q160" s="2" t="inlineStr"/>
       <c r="R160" s="2" t="inlineStr"/>
       <c r="S160" s="2" t="inlineStr"/>
-      <c r="T160" s="2" t="inlineStr"/>
+      <c r="T160" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -8975,7 +9483,11 @@
       <c r="Q161" s="2" t="inlineStr"/>
       <c r="R161" s="2" t="inlineStr"/>
       <c r="S161" s="2" t="inlineStr"/>
-      <c r="T161" s="2" t="inlineStr"/>
+      <c r="T161" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -9025,7 +9537,11 @@
       <c r="Q162" s="2" t="inlineStr"/>
       <c r="R162" s="2" t="inlineStr"/>
       <c r="S162" s="2" t="inlineStr"/>
-      <c r="T162" s="2" t="inlineStr"/>
+      <c r="T162" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -9075,7 +9591,11 @@
       <c r="Q163" s="2" t="inlineStr"/>
       <c r="R163" s="2" t="inlineStr"/>
       <c r="S163" s="2" t="inlineStr"/>
-      <c r="T163" s="2" t="inlineStr"/>
+      <c r="T163" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -9125,7 +9645,11 @@
       <c r="Q164" s="2" t="inlineStr"/>
       <c r="R164" s="2" t="inlineStr"/>
       <c r="S164" s="2" t="inlineStr"/>
-      <c r="T164" s="2" t="inlineStr"/>
+      <c r="T164" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -9175,7 +9699,11 @@
       <c r="Q165" s="2" t="inlineStr"/>
       <c r="R165" s="2" t="inlineStr"/>
       <c r="S165" s="2" t="inlineStr"/>
-      <c r="T165" s="2" t="inlineStr"/>
+      <c r="T165" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -9225,7 +9753,11 @@
       <c r="Q166" s="2" t="inlineStr"/>
       <c r="R166" s="2" t="inlineStr"/>
       <c r="S166" s="2" t="inlineStr"/>
-      <c r="T166" s="2" t="inlineStr"/>
+      <c r="T166" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -9275,7 +9807,11 @@
       <c r="Q167" s="2" t="inlineStr"/>
       <c r="R167" s="2" t="inlineStr"/>
       <c r="S167" s="2" t="inlineStr"/>
-      <c r="T167" s="2" t="inlineStr"/>
+      <c r="T167" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -9325,7 +9861,11 @@
       <c r="Q168" s="2" t="inlineStr"/>
       <c r="R168" s="2" t="inlineStr"/>
       <c r="S168" s="2" t="inlineStr"/>
-      <c r="T168" s="2" t="inlineStr"/>
+      <c r="T168" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -9375,7 +9915,11 @@
       <c r="Q169" s="2" t="inlineStr"/>
       <c r="R169" s="2" t="inlineStr"/>
       <c r="S169" s="2" t="inlineStr"/>
-      <c r="T169" s="2" t="inlineStr"/>
+      <c r="T169" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -9425,7 +9969,11 @@
       <c r="Q170" s="2" t="inlineStr"/>
       <c r="R170" s="2" t="inlineStr"/>
       <c r="S170" s="2" t="inlineStr"/>
-      <c r="T170" s="2" t="inlineStr"/>
+      <c r="T170" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -9475,7 +10023,11 @@
       <c r="Q171" s="2" t="inlineStr"/>
       <c r="R171" s="2" t="inlineStr"/>
       <c r="S171" s="2" t="inlineStr"/>
-      <c r="T171" s="2" t="inlineStr"/>
+      <c r="T171" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -9525,7 +10077,11 @@
       <c r="Q172" s="2" t="inlineStr"/>
       <c r="R172" s="2" t="inlineStr"/>
       <c r="S172" s="2" t="inlineStr"/>
-      <c r="T172" s="2" t="inlineStr"/>
+      <c r="T172" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -9575,7 +10131,11 @@
       <c r="Q173" s="2" t="inlineStr"/>
       <c r="R173" s="2" t="inlineStr"/>
       <c r="S173" s="2" t="inlineStr"/>
-      <c r="T173" s="2" t="inlineStr"/>
+      <c r="T173" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -9625,7 +10185,11 @@
       <c r="Q174" s="2" t="inlineStr"/>
       <c r="R174" s="2" t="inlineStr"/>
       <c r="S174" s="2" t="inlineStr"/>
-      <c r="T174" s="2" t="inlineStr"/>
+      <c r="T174" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -9675,7 +10239,11 @@
       <c r="Q175" s="2" t="inlineStr"/>
       <c r="R175" s="2" t="inlineStr"/>
       <c r="S175" s="2" t="inlineStr"/>
-      <c r="T175" s="2" t="inlineStr"/>
+      <c r="T175" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -9725,7 +10293,11 @@
       <c r="Q176" s="2" t="inlineStr"/>
       <c r="R176" s="2" t="inlineStr"/>
       <c r="S176" s="2" t="inlineStr"/>
-      <c r="T176" s="2" t="inlineStr"/>
+      <c r="T176" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -9775,7 +10347,11 @@
       <c r="Q177" s="2" t="inlineStr"/>
       <c r="R177" s="2" t="inlineStr"/>
       <c r="S177" s="2" t="inlineStr"/>
-      <c r="T177" s="2" t="inlineStr"/>
+      <c r="T177" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -9825,7 +10401,11 @@
       <c r="Q178" s="2" t="inlineStr"/>
       <c r="R178" s="2" t="inlineStr"/>
       <c r="S178" s="2" t="inlineStr"/>
-      <c r="T178" s="2" t="inlineStr"/>
+      <c r="T178" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -9875,7 +10455,11 @@
       <c r="Q179" s="2" t="inlineStr"/>
       <c r="R179" s="2" t="inlineStr"/>
       <c r="S179" s="2" t="inlineStr"/>
-      <c r="T179" s="2" t="inlineStr"/>
+      <c r="T179" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -9925,7 +10509,11 @@
       <c r="Q180" s="2" t="inlineStr"/>
       <c r="R180" s="2" t="inlineStr"/>
       <c r="S180" s="2" t="inlineStr"/>
-      <c r="T180" s="2" t="inlineStr"/>
+      <c r="T180" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -9975,7 +10563,11 @@
       <c r="Q181" s="2" t="inlineStr"/>
       <c r="R181" s="2" t="inlineStr"/>
       <c r="S181" s="2" t="inlineStr"/>
-      <c r="T181" s="2" t="inlineStr"/>
+      <c r="T181" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -10025,7 +10617,11 @@
       <c r="Q182" s="2" t="inlineStr"/>
       <c r="R182" s="2" t="inlineStr"/>
       <c r="S182" s="2" t="inlineStr"/>
-      <c r="T182" s="2" t="inlineStr"/>
+      <c r="T182" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -10075,7 +10671,11 @@
       <c r="Q183" s="2" t="inlineStr"/>
       <c r="R183" s="2" t="inlineStr"/>
       <c r="S183" s="2" t="inlineStr"/>
-      <c r="T183" s="2" t="inlineStr"/>
+      <c r="T183" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -10125,7 +10725,11 @@
       <c r="Q184" s="2" t="inlineStr"/>
       <c r="R184" s="2" t="inlineStr"/>
       <c r="S184" s="2" t="inlineStr"/>
-      <c r="T184" s="2" t="inlineStr"/>
+      <c r="T184" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -10175,7 +10779,11 @@
       <c r="Q185" s="2" t="inlineStr"/>
       <c r="R185" s="2" t="inlineStr"/>
       <c r="S185" s="2" t="inlineStr"/>
-      <c r="T185" s="2" t="inlineStr"/>
+      <c r="T185" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -10225,7 +10833,11 @@
       <c r="Q186" s="2" t="inlineStr"/>
       <c r="R186" s="2" t="inlineStr"/>
       <c r="S186" s="2" t="inlineStr"/>
-      <c r="T186" s="2" t="inlineStr"/>
+      <c r="T186" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -10275,7 +10887,11 @@
       <c r="Q187" s="2" t="inlineStr"/>
       <c r="R187" s="2" t="inlineStr"/>
       <c r="S187" s="2" t="inlineStr"/>
-      <c r="T187" s="2" t="inlineStr"/>
+      <c r="T187" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -10325,7 +10941,11 @@
       <c r="Q188" s="2" t="inlineStr"/>
       <c r="R188" s="2" t="inlineStr"/>
       <c r="S188" s="2" t="inlineStr"/>
-      <c r="T188" s="2" t="inlineStr"/>
+      <c r="T188" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -10375,7 +10995,11 @@
       <c r="Q189" s="2" t="inlineStr"/>
       <c r="R189" s="2" t="inlineStr"/>
       <c r="S189" s="2" t="inlineStr"/>
-      <c r="T189" s="2" t="inlineStr"/>
+      <c r="T189" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -10425,7 +11049,11 @@
       <c r="Q190" s="2" t="inlineStr"/>
       <c r="R190" s="2" t="inlineStr"/>
       <c r="S190" s="2" t="inlineStr"/>
-      <c r="T190" s="2" t="inlineStr"/>
+      <c r="T190" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -10475,7 +11103,11 @@
       <c r="Q191" s="2" t="inlineStr"/>
       <c r="R191" s="2" t="inlineStr"/>
       <c r="S191" s="2" t="inlineStr"/>
-      <c r="T191" s="2" t="inlineStr"/>
+      <c r="T191" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-LUDOU-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -10525,7 +11157,11 @@
       <c r="Q192" s="2" t="inlineStr"/>
       <c r="R192" s="2" t="inlineStr"/>
       <c r="S192" s="2" t="inlineStr"/>
-      <c r="T192" s="2" t="inlineStr"/>
+      <c r="T192" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-LUDOU-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -10575,7 +11211,11 @@
       <c r="Q193" s="2" t="inlineStr"/>
       <c r="R193" s="2" t="inlineStr"/>
       <c r="S193" s="2" t="inlineStr"/>
-      <c r="T193" s="2" t="inlineStr"/>
+      <c r="T193" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-LUDOU-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -10625,7 +11265,11 @@
       <c r="Q194" s="2" t="inlineStr"/>
       <c r="R194" s="2" t="inlineStr"/>
       <c r="S194" s="2" t="inlineStr"/>
-      <c r="T194" s="2" t="inlineStr"/>
+      <c r="T194" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-LUDOU-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -10675,7 +11319,11 @@
       <c r="Q195" s="2" t="inlineStr"/>
       <c r="R195" s="2" t="inlineStr"/>
       <c r="S195" s="2" t="inlineStr"/>
-      <c r="T195" s="2" t="inlineStr"/>
+      <c r="T195" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-LUDOU-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -10725,7 +11373,11 @@
       <c r="Q196" s="2" t="inlineStr"/>
       <c r="R196" s="2" t="inlineStr"/>
       <c r="S196" s="2" t="inlineStr"/>
-      <c r="T196" s="2" t="inlineStr"/>
+      <c r="T196" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-LUDOU-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -10775,7 +11427,11 @@
       <c r="Q197" s="2" t="inlineStr"/>
       <c r="R197" s="2" t="inlineStr"/>
       <c r="S197" s="2" t="inlineStr"/>
-      <c r="T197" s="2" t="inlineStr"/>
+      <c r="T197" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-LUDOU-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -10825,7 +11481,11 @@
       <c r="Q198" s="2" t="inlineStr"/>
       <c r="R198" s="2" t="inlineStr"/>
       <c r="S198" s="2" t="inlineStr"/>
-      <c r="T198" s="2" t="inlineStr"/>
+      <c r="T198" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-LUDOU-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -10875,7 +11535,11 @@
       <c r="Q199" s="2" t="inlineStr"/>
       <c r="R199" s="2" t="inlineStr"/>
       <c r="S199" s="2" t="inlineStr"/>
-      <c r="T199" s="2" t="inlineStr"/>
+      <c r="T199" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-LUDOU-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -10925,7 +11589,11 @@
       <c r="Q200" s="2" t="inlineStr"/>
       <c r="R200" s="2" t="inlineStr"/>
       <c r="S200" s="2" t="inlineStr"/>
-      <c r="T200" s="2" t="inlineStr"/>
+      <c r="T200" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-LUDOU-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -10975,7 +11643,11 @@
       <c r="Q201" s="2" t="inlineStr"/>
       <c r="R201" s="2" t="inlineStr"/>
       <c r="S201" s="2" t="inlineStr"/>
-      <c r="T201" s="2" t="inlineStr"/>
+      <c r="T201" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-LUDOU-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -11025,7 +11697,11 @@
       <c r="Q202" s="2" t="inlineStr"/>
       <c r="R202" s="2" t="inlineStr"/>
       <c r="S202" s="2" t="inlineStr"/>
-      <c r="T202" s="2" t="inlineStr"/>
+      <c r="T202" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-LUDOU-COLUMN-001_MASTER","stage1_disposition":"已有Master｜可直接绑定"}</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -11075,7 +11751,11 @@
       <c r="Q203" s="2" t="inlineStr"/>
       <c r="R203" s="2" t="inlineStr"/>
       <c r="S203" s="2" t="inlineStr"/>
-      <c r="T203" s="2" t="inlineStr"/>
+      <c r="T203" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -11125,7 +11805,11 @@
       <c r="Q204" s="2" t="inlineStr"/>
       <c r="R204" s="2" t="inlineStr"/>
       <c r="S204" s="2" t="inlineStr"/>
-      <c r="T204" s="2" t="inlineStr"/>
+      <c r="T204" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -11175,7 +11859,11 @@
       <c r="Q205" s="2" t="inlineStr"/>
       <c r="R205" s="2" t="inlineStr"/>
       <c r="S205" s="2" t="inlineStr"/>
-      <c r="T205" s="2" t="inlineStr"/>
+      <c r="T205" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -11225,7 +11913,11 @@
       <c r="Q206" s="2" t="inlineStr"/>
       <c r="R206" s="2" t="inlineStr"/>
       <c r="S206" s="2" t="inlineStr"/>
-      <c r="T206" s="2" t="inlineStr"/>
+      <c r="T206" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -11275,7 +11967,11 @@
       <c r="Q207" s="2" t="inlineStr"/>
       <c r="R207" s="2" t="inlineStr"/>
       <c r="S207" s="2" t="inlineStr"/>
-      <c r="T207" s="2" t="inlineStr"/>
+      <c r="T207" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -11325,7 +12021,11 @@
       <c r="Q208" s="2" t="inlineStr"/>
       <c r="R208" s="2" t="inlineStr"/>
       <c r="S208" s="2" t="inlineStr"/>
-      <c r="T208" s="2" t="inlineStr"/>
+      <c r="T208" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -11375,7 +12075,11 @@
       <c r="Q209" s="2" t="inlineStr"/>
       <c r="R209" s="2" t="inlineStr"/>
       <c r="S209" s="2" t="inlineStr"/>
-      <c r="T209" s="2" t="inlineStr"/>
+      <c r="T209" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -11425,7 +12129,11 @@
       <c r="Q210" s="2" t="inlineStr"/>
       <c r="R210" s="2" t="inlineStr"/>
       <c r="S210" s="2" t="inlineStr"/>
-      <c r="T210" s="2" t="inlineStr"/>
+      <c r="T210" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -11475,7 +12183,11 @@
       <c r="Q211" s="2" t="inlineStr"/>
       <c r="R211" s="2" t="inlineStr"/>
       <c r="S211" s="2" t="inlineStr"/>
-      <c r="T211" s="2" t="inlineStr"/>
+      <c r="T211" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -11525,7 +12237,11 @@
       <c r="Q212" s="2" t="inlineStr"/>
       <c r="R212" s="2" t="inlineStr"/>
       <c r="S212" s="2" t="inlineStr"/>
-      <c r="T212" s="2" t="inlineStr"/>
+      <c r="T212" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -11575,7 +12291,11 @@
       <c r="Q213" s="2" t="inlineStr"/>
       <c r="R213" s="2" t="inlineStr"/>
       <c r="S213" s="2" t="inlineStr"/>
-      <c r="T213" s="2" t="inlineStr"/>
+      <c r="T213" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -11625,7 +12345,11 @@
       <c r="Q214" s="2" t="inlineStr"/>
       <c r="R214" s="2" t="inlineStr"/>
       <c r="S214" s="2" t="inlineStr"/>
-      <c r="T214" s="2" t="inlineStr"/>
+      <c r="T214" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -11675,7 +12399,11 @@
       </c>
       <c r="R215" s="2" t="inlineStr"/>
       <c r="S215" s="2" t="inlineStr"/>
-      <c r="T215" s="2" t="inlineStr"/>
+      <c r="T215" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -11725,7 +12453,11 @@
       </c>
       <c r="R216" s="2" t="inlineStr"/>
       <c r="S216" s="2" t="inlineStr"/>
-      <c r="T216" s="2" t="inlineStr"/>
+      <c r="T216" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -11775,7 +12507,11 @@
       </c>
       <c r="R217" s="2" t="inlineStr"/>
       <c r="S217" s="2" t="inlineStr"/>
-      <c r="T217" s="2" t="inlineStr"/>
+      <c r="T217" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -11825,7 +12561,11 @@
       </c>
       <c r="R218" s="2" t="inlineStr"/>
       <c r="S218" s="2" t="inlineStr"/>
-      <c r="T218" s="2" t="inlineStr"/>
+      <c r="T218" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -11875,7 +12615,11 @@
       </c>
       <c r="R219" s="2" t="inlineStr"/>
       <c r="S219" s="2" t="inlineStr"/>
-      <c r="T219" s="2" t="inlineStr"/>
+      <c r="T219" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -11925,7 +12669,11 @@
       </c>
       <c r="R220" s="2" t="inlineStr"/>
       <c r="S220" s="2" t="inlineStr"/>
-      <c r="T220" s="2" t="inlineStr"/>
+      <c r="T220" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -11975,7 +12723,11 @@
       </c>
       <c r="R221" s="2" t="inlineStr"/>
       <c r="S221" s="2" t="inlineStr"/>
-      <c r="T221" s="2" t="inlineStr"/>
+      <c r="T221" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -12025,7 +12777,11 @@
       </c>
       <c r="R222" s="2" t="inlineStr"/>
       <c r="S222" s="2" t="inlineStr"/>
-      <c r="T222" s="2" t="inlineStr"/>
+      <c r="T222" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -12075,7 +12831,11 @@
       </c>
       <c r="R223" s="2" t="inlineStr"/>
       <c r="S223" s="2" t="inlineStr"/>
-      <c r="T223" s="2" t="inlineStr"/>
+      <c r="T223" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -12125,7 +12885,11 @@
       </c>
       <c r="R224" s="2" t="inlineStr"/>
       <c r="S224" s="2" t="inlineStr"/>
-      <c r="T224" s="2" t="inlineStr"/>
+      <c r="T224" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -12175,7 +12939,11 @@
       </c>
       <c r="R225" s="2" t="inlineStr"/>
       <c r="S225" s="2" t="inlineStr"/>
-      <c r="T225" s="2" t="inlineStr"/>
+      <c r="T225" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -12225,7 +12993,11 @@
       </c>
       <c r="R226" s="2" t="inlineStr"/>
       <c r="S226" s="2" t="inlineStr"/>
-      <c r="T226" s="2" t="inlineStr"/>
+      <c r="T226" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -12275,7 +13047,11 @@
       </c>
       <c r="R227" s="2" t="inlineStr"/>
       <c r="S227" s="2" t="inlineStr"/>
-      <c r="T227" s="2" t="inlineStr"/>
+      <c r="T227" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -12325,7 +13101,11 @@
       </c>
       <c r="R228" s="2" t="inlineStr"/>
       <c r="S228" s="2" t="inlineStr"/>
-      <c r="T228" s="2" t="inlineStr"/>
+      <c r="T228" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -12375,7 +13155,11 @@
       </c>
       <c r="R229" s="2" t="inlineStr"/>
       <c r="S229" s="2" t="inlineStr"/>
-      <c r="T229" s="2" t="inlineStr"/>
+      <c r="T229" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -12425,7 +13209,11 @@
       </c>
       <c r="R230" s="2" t="inlineStr"/>
       <c r="S230" s="2" t="inlineStr"/>
-      <c r="T230" s="2" t="inlineStr"/>
+      <c r="T230" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -12475,7 +13263,11 @@
       </c>
       <c r="R231" s="2" t="inlineStr"/>
       <c r="S231" s="2" t="inlineStr"/>
-      <c r="T231" s="2" t="inlineStr"/>
+      <c r="T231" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -12525,7 +13317,11 @@
       </c>
       <c r="R232" s="2" t="inlineStr"/>
       <c r="S232" s="2" t="inlineStr"/>
-      <c r="T232" s="2" t="inlineStr"/>
+      <c r="T232" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -12575,7 +13371,11 @@
       </c>
       <c r="R233" s="2" t="inlineStr"/>
       <c r="S233" s="2" t="inlineStr"/>
-      <c r="T233" s="2" t="inlineStr"/>
+      <c r="T233" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -12625,7 +13425,11 @@
       </c>
       <c r="R234" s="2" t="inlineStr"/>
       <c r="S234" s="2" t="inlineStr"/>
-      <c r="T234" s="2" t="inlineStr"/>
+      <c r="T234" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -12675,7 +13479,11 @@
       </c>
       <c r="R235" s="2" t="inlineStr"/>
       <c r="S235" s="2" t="inlineStr"/>
-      <c r="T235" s="2" t="inlineStr"/>
+      <c r="T235" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -12725,7 +13533,11 @@
       </c>
       <c r="R236" s="2" t="inlineStr"/>
       <c r="S236" s="2" t="inlineStr"/>
-      <c r="T236" s="2" t="inlineStr"/>
+      <c r="T236" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -12775,7 +13587,11 @@
       </c>
       <c r="R237" s="2" t="inlineStr"/>
       <c r="S237" s="2" t="inlineStr"/>
-      <c r="T237" s="2" t="inlineStr"/>
+      <c r="T237" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -12825,7 +13641,11 @@
       </c>
       <c r="R238" s="2" t="inlineStr"/>
       <c r="S238" s="2" t="inlineStr"/>
-      <c r="T238" s="2" t="inlineStr"/>
+      <c r="T238" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -12875,7 +13695,11 @@
       </c>
       <c r="R239" s="2" t="inlineStr"/>
       <c r="S239" s="2" t="inlineStr"/>
-      <c r="T239" s="2" t="inlineStr"/>
+      <c r="T239" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -12925,7 +13749,11 @@
       </c>
       <c r="R240" s="2" t="inlineStr"/>
       <c r="S240" s="2" t="inlineStr"/>
-      <c r="T240" s="2" t="inlineStr"/>
+      <c r="T240" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -12975,7 +13803,11 @@
       </c>
       <c r="R241" s="2" t="inlineStr"/>
       <c r="S241" s="2" t="inlineStr"/>
-      <c r="T241" s="2" t="inlineStr"/>
+      <c r="T241" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -13025,7 +13857,11 @@
       </c>
       <c r="R242" s="2" t="inlineStr"/>
       <c r="S242" s="2" t="inlineStr"/>
-      <c r="T242" s="2" t="inlineStr"/>
+      <c r="T242" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -13075,7 +13911,11 @@
       </c>
       <c r="R243" s="2" t="inlineStr"/>
       <c r="S243" s="2" t="inlineStr"/>
-      <c r="T243" s="2" t="inlineStr"/>
+      <c r="T243" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -13125,7 +13965,11 @@
       </c>
       <c r="R244" s="2" t="inlineStr"/>
       <c r="S244" s="2" t="inlineStr"/>
-      <c r="T244" s="2" t="inlineStr"/>
+      <c r="T244" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -13175,7 +14019,11 @@
       </c>
       <c r="R245" s="2" t="inlineStr"/>
       <c r="S245" s="2" t="inlineStr"/>
-      <c r="T245" s="2" t="inlineStr"/>
+      <c r="T245" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -13225,7 +14073,11 @@
       </c>
       <c r="R246" s="2" t="inlineStr"/>
       <c r="S246" s="2" t="inlineStr"/>
-      <c r="T246" s="2" t="inlineStr"/>
+      <c r="T246" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -13275,7 +14127,11 @@
       </c>
       <c r="R247" s="2" t="inlineStr"/>
       <c r="S247" s="2" t="inlineStr"/>
-      <c r="T247" s="2" t="inlineStr"/>
+      <c r="T247" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -13325,7 +14181,11 @@
       </c>
       <c r="R248" s="2" t="inlineStr"/>
       <c r="S248" s="2" t="inlineStr"/>
-      <c r="T248" s="2" t="inlineStr"/>
+      <c r="T248" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -13375,7 +14235,11 @@
       </c>
       <c r="R249" s="2" t="inlineStr"/>
       <c r="S249" s="2" t="inlineStr"/>
-      <c r="T249" s="2" t="inlineStr"/>
+      <c r="T249" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -13425,7 +14289,11 @@
       </c>
       <c r="R250" s="2" t="inlineStr"/>
       <c r="S250" s="2" t="inlineStr"/>
-      <c r="T250" s="2" t="inlineStr"/>
+      <c r="T250" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -13475,7 +14343,11 @@
       </c>
       <c r="R251" s="2" t="inlineStr"/>
       <c r="S251" s="2" t="inlineStr"/>
-      <c r="T251" s="2" t="inlineStr"/>
+      <c r="T251" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -13525,7 +14397,11 @@
       </c>
       <c r="R252" s="2" t="inlineStr"/>
       <c r="S252" s="2" t="inlineStr"/>
-      <c r="T252" s="2" t="inlineStr"/>
+      <c r="T252" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -13575,7 +14451,11 @@
       </c>
       <c r="R253" s="2" t="inlineStr"/>
       <c r="S253" s="2" t="inlineStr"/>
-      <c r="T253" s="2" t="inlineStr"/>
+      <c r="T253" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -13625,7 +14505,11 @@
       </c>
       <c r="R254" s="2" t="inlineStr"/>
       <c r="S254" s="2" t="inlineStr"/>
-      <c r="T254" s="2" t="inlineStr"/>
+      <c r="T254" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -13675,7 +14559,11 @@
       </c>
       <c r="R255" s="2" t="inlineStr"/>
       <c r="S255" s="2" t="inlineStr"/>
-      <c r="T255" s="2" t="inlineStr"/>
+      <c r="T255" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -13725,7 +14613,11 @@
       </c>
       <c r="R256" s="2" t="inlineStr"/>
       <c r="S256" s="2" t="inlineStr"/>
-      <c r="T256" s="2" t="inlineStr"/>
+      <c r="T256" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -13775,7 +14667,11 @@
       </c>
       <c r="R257" s="2" t="inlineStr"/>
       <c r="S257" s="2" t="inlineStr"/>
-      <c r="T257" s="2" t="inlineStr"/>
+      <c r="T257" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -13825,7 +14721,11 @@
       </c>
       <c r="R258" s="2" t="inlineStr"/>
       <c r="S258" s="2" t="inlineStr"/>
-      <c r="T258" s="2" t="inlineStr"/>
+      <c r="T258" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -13875,7 +14775,11 @@
       </c>
       <c r="R259" s="2" t="inlineStr"/>
       <c r="S259" s="2" t="inlineStr"/>
-      <c r="T259" s="2" t="inlineStr"/>
+      <c r="T259" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -13925,7 +14829,11 @@
       </c>
       <c r="R260" s="2" t="inlineStr"/>
       <c r="S260" s="2" t="inlineStr"/>
-      <c r="T260" s="2" t="inlineStr"/>
+      <c r="T260" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -13975,7 +14883,11 @@
       </c>
       <c r="R261" s="2" t="inlineStr"/>
       <c r="S261" s="2" t="inlineStr"/>
-      <c r="T261" s="2" t="inlineStr"/>
+      <c r="T261" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -14025,7 +14937,11 @@
       </c>
       <c r="R262" s="2" t="inlineStr"/>
       <c r="S262" s="2" t="inlineStr"/>
-      <c r="T262" s="2" t="inlineStr"/>
+      <c r="T262" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -14075,7 +14991,11 @@
       </c>
       <c r="R263" s="2" t="inlineStr"/>
       <c r="S263" s="2" t="inlineStr"/>
-      <c r="T263" s="2" t="inlineStr"/>
+      <c r="T263" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -14125,7 +15045,11 @@
       </c>
       <c r="R264" s="2" t="inlineStr"/>
       <c r="S264" s="2" t="inlineStr"/>
-      <c r="T264" s="2" t="inlineStr"/>
+      <c r="T264" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -14175,7 +15099,11 @@
       </c>
       <c r="R265" s="2" t="inlineStr"/>
       <c r="S265" s="2" t="inlineStr"/>
-      <c r="T265" s="2" t="inlineStr"/>
+      <c r="T265" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -14225,7 +15153,11 @@
       </c>
       <c r="R266" s="2" t="inlineStr"/>
       <c r="S266" s="2" t="inlineStr"/>
-      <c r="T266" s="2" t="inlineStr"/>
+      <c r="T266" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -14275,7 +15207,11 @@
       </c>
       <c r="R267" s="2" t="inlineStr"/>
       <c r="S267" s="2" t="inlineStr"/>
-      <c r="T267" s="2" t="inlineStr"/>
+      <c r="T267" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -14325,7 +15261,11 @@
       </c>
       <c r="R268" s="2" t="inlineStr"/>
       <c r="S268" s="2" t="inlineStr"/>
-      <c r="T268" s="2" t="inlineStr"/>
+      <c r="T268" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -14375,7 +15315,11 @@
       </c>
       <c r="R269" s="2" t="inlineStr"/>
       <c r="S269" s="2" t="inlineStr"/>
-      <c r="T269" s="2" t="inlineStr"/>
+      <c r="T269" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -14425,7 +15369,11 @@
       </c>
       <c r="R270" s="2" t="inlineStr"/>
       <c r="S270" s="2" t="inlineStr"/>
-      <c r="T270" s="2" t="inlineStr"/>
+      <c r="T270" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -14477,7 +15425,11 @@
       <c r="Q271" s="2" t="inlineStr"/>
       <c r="R271" s="2" t="inlineStr"/>
       <c r="S271" s="2" t="inlineStr"/>
-      <c r="T271" s="2" t="inlineStr"/>
+      <c r="T271" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -14529,7 +15481,11 @@
       <c r="Q272" s="2" t="inlineStr"/>
       <c r="R272" s="2" t="inlineStr"/>
       <c r="S272" s="2" t="inlineStr"/>
-      <c r="T272" s="2" t="inlineStr"/>
+      <c r="T272" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -14581,7 +15537,11 @@
       <c r="Q273" s="2" t="inlineStr"/>
       <c r="R273" s="2" t="inlineStr"/>
       <c r="S273" s="2" t="inlineStr"/>
-      <c r="T273" s="2" t="inlineStr"/>
+      <c r="T273" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -14633,7 +15593,11 @@
       <c r="Q274" s="2" t="inlineStr"/>
       <c r="R274" s="2" t="inlineStr"/>
       <c r="S274" s="2" t="inlineStr"/>
-      <c r="T274" s="2" t="inlineStr"/>
+      <c r="T274" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -14685,7 +15649,11 @@
       <c r="Q275" s="2" t="inlineStr"/>
       <c r="R275" s="2" t="inlineStr"/>
       <c r="S275" s="2" t="inlineStr"/>
-      <c r="T275" s="2" t="inlineStr"/>
+      <c r="T275" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -14735,7 +15703,11 @@
       <c r="Q276" s="2" t="inlineStr"/>
       <c r="R276" s="2" t="inlineStr"/>
       <c r="S276" s="2" t="inlineStr"/>
-      <c r="T276" s="2" t="inlineStr"/>
+      <c r="T276" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -14785,7 +15757,11 @@
       <c r="Q277" s="2" t="inlineStr"/>
       <c r="R277" s="2" t="inlineStr"/>
       <c r="S277" s="2" t="inlineStr"/>
-      <c r="T277" s="2" t="inlineStr"/>
+      <c r="T277" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -14837,7 +15813,11 @@
       <c r="Q278" s="2" t="inlineStr"/>
       <c r="R278" s="2" t="inlineStr"/>
       <c r="S278" s="2" t="inlineStr"/>
-      <c r="T278" s="2" t="inlineStr"/>
+      <c r="T278" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -14889,7 +15869,11 @@
       <c r="Q279" s="2" t="inlineStr"/>
       <c r="R279" s="2" t="inlineStr"/>
       <c r="S279" s="2" t="inlineStr"/>
-      <c r="T279" s="2" t="inlineStr"/>
+      <c r="T279" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -14941,7 +15925,11 @@
       <c r="Q280" s="2" t="inlineStr"/>
       <c r="R280" s="2" t="inlineStr"/>
       <c r="S280" s="2" t="inlineStr"/>
-      <c r="T280" s="2" t="inlineStr"/>
+      <c r="T280" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -14993,7 +15981,11 @@
       <c r="Q281" s="2" t="inlineStr"/>
       <c r="R281" s="2" t="inlineStr"/>
       <c r="S281" s="2" t="inlineStr"/>
-      <c r="T281" s="2" t="inlineStr"/>
+      <c r="T281" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -15045,7 +16037,11 @@
       <c r="Q282" s="2" t="inlineStr"/>
       <c r="R282" s="2" t="inlineStr"/>
       <c r="S282" s="2" t="inlineStr"/>
-      <c r="T282" s="2" t="inlineStr"/>
+      <c r="T282" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -15097,7 +16093,11 @@
       <c r="Q283" s="2" t="inlineStr"/>
       <c r="R283" s="2" t="inlineStr"/>
       <c r="S283" s="2" t="inlineStr"/>
-      <c r="T283" s="2" t="inlineStr"/>
+      <c r="T283" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -15149,7 +16149,11 @@
       <c r="Q284" s="2" t="inlineStr"/>
       <c r="R284" s="2" t="inlineStr"/>
       <c r="S284" s="2" t="inlineStr"/>
-      <c r="T284" s="2" t="inlineStr"/>
+      <c r="T284" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -15201,7 +16205,11 @@
       <c r="Q285" s="2" t="inlineStr"/>
       <c r="R285" s="2" t="inlineStr"/>
       <c r="S285" s="2" t="inlineStr"/>
-      <c r="T285" s="2" t="inlineStr"/>
+      <c r="T285" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -15251,7 +16259,11 @@
       <c r="Q286" s="2" t="inlineStr"/>
       <c r="R286" s="2" t="inlineStr"/>
       <c r="S286" s="2" t="inlineStr"/>
-      <c r="T286" s="2" t="inlineStr"/>
+      <c r="T286" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -15301,7 +16313,11 @@
       <c r="Q287" s="2" t="inlineStr"/>
       <c r="R287" s="2" t="inlineStr"/>
       <c r="S287" s="2" t="inlineStr"/>
-      <c r="T287" s="2" t="inlineStr"/>
+      <c r="T287" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -15353,7 +16369,11 @@
       <c r="Q288" s="2" t="inlineStr"/>
       <c r="R288" s="2" t="inlineStr"/>
       <c r="S288" s="2" t="inlineStr"/>
-      <c r="T288" s="2" t="inlineStr"/>
+      <c r="T288" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -15405,7 +16425,11 @@
       <c r="Q289" s="2" t="inlineStr"/>
       <c r="R289" s="2" t="inlineStr"/>
       <c r="S289" s="2" t="inlineStr"/>
-      <c r="T289" s="2" t="inlineStr"/>
+      <c r="T289" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -15457,7 +16481,11 @@
       <c r="Q290" s="2" t="inlineStr"/>
       <c r="R290" s="2" t="inlineStr"/>
       <c r="S290" s="2" t="inlineStr"/>
-      <c r="T290" s="2" t="inlineStr"/>
+      <c r="T290" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -15509,7 +16537,11 @@
       <c r="Q291" s="2" t="inlineStr"/>
       <c r="R291" s="2" t="inlineStr"/>
       <c r="S291" s="2" t="inlineStr"/>
-      <c r="T291" s="2" t="inlineStr"/>
+      <c r="T291" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -15561,7 +16593,11 @@
       <c r="Q292" s="2" t="inlineStr"/>
       <c r="R292" s="2" t="inlineStr"/>
       <c r="S292" s="2" t="inlineStr"/>
-      <c r="T292" s="2" t="inlineStr"/>
+      <c r="T292" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -15613,7 +16649,11 @@
       <c r="Q293" s="2" t="inlineStr"/>
       <c r="R293" s="2" t="inlineStr"/>
       <c r="S293" s="2" t="inlineStr"/>
-      <c r="T293" s="2" t="inlineStr"/>
+      <c r="T293" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -15665,7 +16705,11 @@
       <c r="Q294" s="2" t="inlineStr"/>
       <c r="R294" s="2" t="inlineStr"/>
       <c r="S294" s="2" t="inlineStr"/>
-      <c r="T294" s="2" t="inlineStr"/>
+      <c r="T294" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -15717,7 +16761,11 @@
       <c r="Q295" s="2" t="inlineStr"/>
       <c r="R295" s="2" t="inlineStr"/>
       <c r="S295" s="2" t="inlineStr"/>
-      <c r="T295" s="2" t="inlineStr"/>
+      <c r="T295" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -15767,7 +16815,11 @@
       <c r="Q296" s="2" t="inlineStr"/>
       <c r="R296" s="2" t="inlineStr"/>
       <c r="S296" s="2" t="inlineStr"/>
-      <c r="T296" s="2" t="inlineStr"/>
+      <c r="T296" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -15817,7 +16869,11 @@
       <c r="Q297" s="2" t="inlineStr"/>
       <c r="R297" s="2" t="inlineStr"/>
       <c r="S297" s="2" t="inlineStr"/>
-      <c r="T297" s="2" t="inlineStr"/>
+      <c r="T297" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -15869,7 +16925,11 @@
       <c r="Q298" s="2" t="inlineStr"/>
       <c r="R298" s="2" t="inlineStr"/>
       <c r="S298" s="2" t="inlineStr"/>
-      <c r="T298" s="2" t="inlineStr"/>
+      <c r="T298" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -15921,7 +16981,11 @@
       <c r="Q299" s="2" t="inlineStr"/>
       <c r="R299" s="2" t="inlineStr"/>
       <c r="S299" s="2" t="inlineStr"/>
-      <c r="T299" s="2" t="inlineStr"/>
+      <c r="T299" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -15973,7 +17037,11 @@
       <c r="Q300" s="2" t="inlineStr"/>
       <c r="R300" s="2" t="inlineStr"/>
       <c r="S300" s="2" t="inlineStr"/>
-      <c r="T300" s="2" t="inlineStr"/>
+      <c r="T300" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -16025,7 +17093,11 @@
       <c r="Q301" s="2" t="inlineStr"/>
       <c r="R301" s="2" t="inlineStr"/>
       <c r="S301" s="2" t="inlineStr"/>
-      <c r="T301" s="2" t="inlineStr"/>
+      <c r="T301" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -16077,7 +17149,11 @@
       <c r="Q302" s="2" t="inlineStr"/>
       <c r="R302" s="2" t="inlineStr"/>
       <c r="S302" s="2" t="inlineStr"/>
-      <c r="T302" s="2" t="inlineStr"/>
+      <c r="T302" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -16129,7 +17205,11 @@
       <c r="Q303" s="2" t="inlineStr"/>
       <c r="R303" s="2" t="inlineStr"/>
       <c r="S303" s="2" t="inlineStr"/>
-      <c r="T303" s="2" t="inlineStr"/>
+      <c r="T303" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -16181,7 +17261,11 @@
       <c r="Q304" s="2" t="inlineStr"/>
       <c r="R304" s="2" t="inlineStr"/>
       <c r="S304" s="2" t="inlineStr"/>
-      <c r="T304" s="2" t="inlineStr"/>
+      <c r="T304" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -16233,7 +17317,11 @@
       <c r="Q305" s="2" t="inlineStr"/>
       <c r="R305" s="2" t="inlineStr"/>
       <c r="S305" s="2" t="inlineStr"/>
-      <c r="T305" s="2" t="inlineStr"/>
+      <c r="T305" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -16283,7 +17371,11 @@
       <c r="Q306" s="2" t="inlineStr"/>
       <c r="R306" s="2" t="inlineStr"/>
       <c r="S306" s="2" t="inlineStr"/>
-      <c r="T306" s="2" t="inlineStr"/>
+      <c r="T306" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -16333,7 +17425,11 @@
       <c r="Q307" s="2" t="inlineStr"/>
       <c r="R307" s="2" t="inlineStr"/>
       <c r="S307" s="2" t="inlineStr"/>
-      <c r="T307" s="2" t="inlineStr"/>
+      <c r="T307" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -16385,7 +17481,11 @@
       <c r="Q308" s="2" t="inlineStr"/>
       <c r="R308" s="2" t="inlineStr"/>
       <c r="S308" s="2" t="inlineStr"/>
-      <c r="T308" s="2" t="inlineStr"/>
+      <c r="T308" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -16437,7 +17537,11 @@
       <c r="Q309" s="2" t="inlineStr"/>
       <c r="R309" s="2" t="inlineStr"/>
       <c r="S309" s="2" t="inlineStr"/>
-      <c r="T309" s="2" t="inlineStr"/>
+      <c r="T309" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -16489,7 +17593,11 @@
       <c r="Q310" s="2" t="inlineStr"/>
       <c r="R310" s="2" t="inlineStr"/>
       <c r="S310" s="2" t="inlineStr"/>
-      <c r="T310" s="2" t="inlineStr"/>
+      <c r="T310" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -16541,7 +17649,11 @@
       <c r="Q311" s="2" t="inlineStr"/>
       <c r="R311" s="2" t="inlineStr"/>
       <c r="S311" s="2" t="inlineStr"/>
-      <c r="T311" s="2" t="inlineStr"/>
+      <c r="T311" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -16593,7 +17705,11 @@
       <c r="Q312" s="2" t="inlineStr"/>
       <c r="R312" s="2" t="inlineStr"/>
       <c r="S312" s="2" t="inlineStr"/>
-      <c r="T312" s="2" t="inlineStr"/>
+      <c r="T312" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -16643,7 +17759,11 @@
       <c r="Q313" s="2" t="inlineStr"/>
       <c r="R313" s="2" t="inlineStr"/>
       <c r="S313" s="2" t="inlineStr"/>
-      <c r="T313" s="2" t="inlineStr"/>
+      <c r="T313" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -16693,7 +17813,11 @@
       <c r="Q314" s="2" t="inlineStr"/>
       <c r="R314" s="2" t="inlineStr"/>
       <c r="S314" s="2" t="inlineStr"/>
-      <c r="T314" s="2" t="inlineStr"/>
+      <c r="T314" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -16745,7 +17869,11 @@
       <c r="Q315" s="2" t="inlineStr"/>
       <c r="R315" s="2" t="inlineStr"/>
       <c r="S315" s="2" t="inlineStr"/>
-      <c r="T315" s="2" t="inlineStr"/>
+      <c r="T315" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -16797,7 +17925,11 @@
       <c r="Q316" s="2" t="inlineStr"/>
       <c r="R316" s="2" t="inlineStr"/>
       <c r="S316" s="2" t="inlineStr"/>
-      <c r="T316" s="2" t="inlineStr"/>
+      <c r="T316" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -16849,7 +17981,11 @@
       <c r="Q317" s="2" t="inlineStr"/>
       <c r="R317" s="2" t="inlineStr"/>
       <c r="S317" s="2" t="inlineStr"/>
-      <c r="T317" s="2" t="inlineStr"/>
+      <c r="T317" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -16901,7 +18037,11 @@
       <c r="Q318" s="2" t="inlineStr"/>
       <c r="R318" s="2" t="inlineStr"/>
       <c r="S318" s="2" t="inlineStr"/>
-      <c r="T318" s="2" t="inlineStr"/>
+      <c r="T318" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -16953,7 +18093,11 @@
       <c r="Q319" s="2" t="inlineStr"/>
       <c r="R319" s="2" t="inlineStr"/>
       <c r="S319" s="2" t="inlineStr"/>
-      <c r="T319" s="2" t="inlineStr"/>
+      <c r="T319" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -17005,7 +18149,11 @@
       <c r="Q320" s="2" t="inlineStr"/>
       <c r="R320" s="2" t="inlineStr"/>
       <c r="S320" s="2" t="inlineStr"/>
-      <c r="T320" s="2" t="inlineStr"/>
+      <c r="T320" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -17057,7 +18205,11 @@
       <c r="Q321" s="2" t="inlineStr"/>
       <c r="R321" s="2" t="inlineStr"/>
       <c r="S321" s="2" t="inlineStr"/>
-      <c r="T321" s="2" t="inlineStr"/>
+      <c r="T321" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -17109,7 +18261,11 @@
       <c r="Q322" s="2" t="inlineStr"/>
       <c r="R322" s="2" t="inlineStr"/>
       <c r="S322" s="2" t="inlineStr"/>
-      <c r="T322" s="2" t="inlineStr"/>
+      <c r="T322" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -17159,7 +18315,11 @@
       <c r="Q323" s="2" t="inlineStr"/>
       <c r="R323" s="2" t="inlineStr"/>
       <c r="S323" s="2" t="inlineStr"/>
-      <c r="T323" s="2" t="inlineStr"/>
+      <c r="T323" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -17209,7 +18369,11 @@
       <c r="Q324" s="2" t="inlineStr"/>
       <c r="R324" s="2" t="inlineStr"/>
       <c r="S324" s="2" t="inlineStr"/>
-      <c r="T324" s="2" t="inlineStr"/>
+      <c r="T324" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -17261,7 +18425,11 @@
       <c r="Q325" s="2" t="inlineStr"/>
       <c r="R325" s="2" t="inlineStr"/>
       <c r="S325" s="2" t="inlineStr"/>
-      <c r="T325" s="2" t="inlineStr"/>
+      <c r="T325" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -17313,7 +18481,11 @@
       <c r="Q326" s="2" t="inlineStr"/>
       <c r="R326" s="2" t="inlineStr"/>
       <c r="S326" s="2" t="inlineStr"/>
-      <c r="T326" s="2" t="inlineStr"/>
+      <c r="T326" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
@@ -17365,7 +18537,11 @@
       <c r="Q327" s="2" t="inlineStr"/>
       <c r="R327" s="2" t="inlineStr"/>
       <c r="S327" s="2" t="inlineStr"/>
-      <c r="T327" s="2" t="inlineStr"/>
+      <c r="T327" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -17417,7 +18593,11 @@
       <c r="Q328" s="2" t="inlineStr"/>
       <c r="R328" s="2" t="inlineStr"/>
       <c r="S328" s="2" t="inlineStr"/>
-      <c r="T328" s="2" t="inlineStr"/>
+      <c r="T328" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -17469,7 +18649,11 @@
       <c r="Q329" s="2" t="inlineStr"/>
       <c r="R329" s="2" t="inlineStr"/>
       <c r="S329" s="2" t="inlineStr"/>
-      <c r="T329" s="2" t="inlineStr"/>
+      <c r="T329" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -17521,7 +18705,11 @@
       <c r="Q330" s="2" t="inlineStr"/>
       <c r="R330" s="2" t="inlineStr"/>
       <c r="S330" s="2" t="inlineStr"/>
-      <c r="T330" s="2" t="inlineStr"/>
+      <c r="T330" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -17573,7 +18761,11 @@
       <c r="Q331" s="2" t="inlineStr"/>
       <c r="R331" s="2" t="inlineStr"/>
       <c r="S331" s="2" t="inlineStr"/>
-      <c r="T331" s="2" t="inlineStr"/>
+      <c r="T331" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -17625,7 +18817,11 @@
       <c r="Q332" s="2" t="inlineStr"/>
       <c r="R332" s="2" t="inlineStr"/>
       <c r="S332" s="2" t="inlineStr"/>
-      <c r="T332" s="2" t="inlineStr"/>
+      <c r="T332" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -17675,7 +18871,11 @@
       <c r="Q333" s="2" t="inlineStr"/>
       <c r="R333" s="2" t="inlineStr"/>
       <c r="S333" s="2" t="inlineStr"/>
-      <c r="T333" s="2" t="inlineStr"/>
+      <c r="T333" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -17725,7 +18925,11 @@
       <c r="Q334" s="2" t="inlineStr"/>
       <c r="R334" s="2" t="inlineStr"/>
       <c r="S334" s="2" t="inlineStr"/>
-      <c r="T334" s="2" t="inlineStr"/>
+      <c r="T334" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -17777,7 +18981,11 @@
       <c r="Q335" s="2" t="inlineStr"/>
       <c r="R335" s="2" t="inlineStr"/>
       <c r="S335" s="2" t="inlineStr"/>
-      <c r="T335" s="2" t="inlineStr"/>
+      <c r="T335" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -17829,7 +19037,11 @@
       <c r="Q336" s="2" t="inlineStr"/>
       <c r="R336" s="2" t="inlineStr"/>
       <c r="S336" s="2" t="inlineStr"/>
-      <c r="T336" s="2" t="inlineStr"/>
+      <c r="T336" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -17881,7 +19093,11 @@
       <c r="Q337" s="2" t="inlineStr"/>
       <c r="R337" s="2" t="inlineStr"/>
       <c r="S337" s="2" t="inlineStr"/>
-      <c r="T337" s="2" t="inlineStr"/>
+      <c r="T337" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -17933,7 +19149,11 @@
       <c r="Q338" s="2" t="inlineStr"/>
       <c r="R338" s="2" t="inlineStr"/>
       <c r="S338" s="2" t="inlineStr"/>
-      <c r="T338" s="2" t="inlineStr"/>
+      <c r="T338" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -17985,7 +19205,11 @@
       <c r="Q339" s="2" t="inlineStr"/>
       <c r="R339" s="2" t="inlineStr"/>
       <c r="S339" s="2" t="inlineStr"/>
-      <c r="T339" s="2" t="inlineStr"/>
+      <c r="T339" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -18037,7 +19261,11 @@
       <c r="Q340" s="2" t="inlineStr"/>
       <c r="R340" s="2" t="inlineStr"/>
       <c r="S340" s="2" t="inlineStr"/>
-      <c r="T340" s="2" t="inlineStr"/>
+      <c r="T340" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -18089,7 +19317,11 @@
       <c r="Q341" s="2" t="inlineStr"/>
       <c r="R341" s="2" t="inlineStr"/>
       <c r="S341" s="2" t="inlineStr"/>
-      <c r="T341" s="2" t="inlineStr"/>
+      <c r="T341" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -18141,7 +19373,11 @@
       <c r="Q342" s="2" t="inlineStr"/>
       <c r="R342" s="2" t="inlineStr"/>
       <c r="S342" s="2" t="inlineStr"/>
-      <c r="T342" s="2" t="inlineStr"/>
+      <c r="T342" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -18191,7 +19427,11 @@
       <c r="Q343" s="2" t="inlineStr"/>
       <c r="R343" s="2" t="inlineStr"/>
       <c r="S343" s="2" t="inlineStr"/>
-      <c r="T343" s="2" t="inlineStr"/>
+      <c r="T343" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -18241,7 +19481,11 @@
       <c r="Q344" s="2" t="inlineStr"/>
       <c r="R344" s="2" t="inlineStr"/>
       <c r="S344" s="2" t="inlineStr"/>
-      <c r="T344" s="2" t="inlineStr"/>
+      <c r="T344" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -18293,7 +19537,11 @@
       <c r="Q345" s="2" t="inlineStr"/>
       <c r="R345" s="2" t="inlineStr"/>
       <c r="S345" s="2" t="inlineStr"/>
-      <c r="T345" s="2" t="inlineStr"/>
+      <c r="T345" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -18345,7 +19593,11 @@
       <c r="Q346" s="2" t="inlineStr"/>
       <c r="R346" s="2" t="inlineStr"/>
       <c r="S346" s="2" t="inlineStr"/>
-      <c r="T346" s="2" t="inlineStr"/>
+      <c r="T346" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -18397,7 +19649,11 @@
       <c r="Q347" s="2" t="inlineStr"/>
       <c r="R347" s="2" t="inlineStr"/>
       <c r="S347" s="2" t="inlineStr"/>
-      <c r="T347" s="2" t="inlineStr"/>
+      <c r="T347" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -18449,7 +19705,11 @@
       <c r="Q348" s="2" t="inlineStr"/>
       <c r="R348" s="2" t="inlineStr"/>
       <c r="S348" s="2" t="inlineStr"/>
-      <c r="T348" s="2" t="inlineStr"/>
+      <c r="T348" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
@@ -18501,7 +19761,11 @@
       <c r="Q349" s="2" t="inlineStr"/>
       <c r="R349" s="2" t="inlineStr"/>
       <c r="S349" s="2" t="inlineStr"/>
-      <c r="T349" s="2" t="inlineStr"/>
+      <c r="T349" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -18551,7 +19815,11 @@
       <c r="Q350" s="2" t="inlineStr"/>
       <c r="R350" s="2" t="inlineStr"/>
       <c r="S350" s="2" t="inlineStr"/>
-      <c r="T350" s="2" t="inlineStr"/>
+      <c r="T350" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -18601,7 +19869,11 @@
       <c r="Q351" s="2" t="inlineStr"/>
       <c r="R351" s="2" t="inlineStr"/>
       <c r="S351" s="2" t="inlineStr"/>
-      <c r="T351" s="2" t="inlineStr"/>
+      <c r="T351" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -18653,7 +19925,11 @@
       <c r="Q352" s="2" t="inlineStr"/>
       <c r="R352" s="2" t="inlineStr"/>
       <c r="S352" s="2" t="inlineStr"/>
-      <c r="T352" s="2" t="inlineStr"/>
+      <c r="T352" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -18705,7 +19981,11 @@
       <c r="Q353" s="2" t="inlineStr"/>
       <c r="R353" s="2" t="inlineStr"/>
       <c r="S353" s="2" t="inlineStr"/>
-      <c r="T353" s="2" t="inlineStr"/>
+      <c r="T353" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -18757,7 +20037,11 @@
       <c r="Q354" s="2" t="inlineStr"/>
       <c r="R354" s="2" t="inlineStr"/>
       <c r="S354" s="2" t="inlineStr"/>
-      <c r="T354" s="2" t="inlineStr"/>
+      <c r="T354" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
@@ -18809,7 +20093,11 @@
       <c r="Q355" s="2" t="inlineStr"/>
       <c r="R355" s="2" t="inlineStr"/>
       <c r="S355" s="2" t="inlineStr"/>
-      <c r="T355" s="2" t="inlineStr"/>
+      <c r="T355" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -18861,7 +20149,11 @@
       <c r="Q356" s="2" t="inlineStr"/>
       <c r="R356" s="2" t="inlineStr"/>
       <c r="S356" s="2" t="inlineStr"/>
-      <c r="T356" s="2" t="inlineStr"/>
+      <c r="T356" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -18913,7 +20205,11 @@
       <c r="Q357" s="2" t="inlineStr"/>
       <c r="R357" s="2" t="inlineStr"/>
       <c r="S357" s="2" t="inlineStr"/>
-      <c r="T357" s="2" t="inlineStr"/>
+      <c r="T357" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -18965,7 +20261,11 @@
       <c r="Q358" s="2" t="inlineStr"/>
       <c r="R358" s="2" t="inlineStr"/>
       <c r="S358" s="2" t="inlineStr"/>
-      <c r="T358" s="2" t="inlineStr"/>
+      <c r="T358" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -19017,7 +20317,11 @@
       <c r="Q359" s="2" t="inlineStr"/>
       <c r="R359" s="2" t="inlineStr"/>
       <c r="S359" s="2" t="inlineStr"/>
-      <c r="T359" s="2" t="inlineStr"/>
+      <c r="T359" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -19067,7 +20371,11 @@
       <c r="Q360" s="2" t="inlineStr"/>
       <c r="R360" s="2" t="inlineStr"/>
       <c r="S360" s="2" t="inlineStr"/>
-      <c r="T360" s="2" t="inlineStr"/>
+      <c r="T360" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
@@ -19117,7 +20425,11 @@
       <c r="Q361" s="2" t="inlineStr"/>
       <c r="R361" s="2" t="inlineStr"/>
       <c r="S361" s="2" t="inlineStr"/>
-      <c r="T361" s="2" t="inlineStr"/>
+      <c r="T361" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -19169,7 +20481,11 @@
       <c r="Q362" s="2" t="inlineStr"/>
       <c r="R362" s="2" t="inlineStr"/>
       <c r="S362" s="2" t="inlineStr"/>
-      <c r="T362" s="2" t="inlineStr"/>
+      <c r="T362" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
@@ -19221,7 +20537,11 @@
       <c r="Q363" s="2" t="inlineStr"/>
       <c r="R363" s="2" t="inlineStr"/>
       <c r="S363" s="2" t="inlineStr"/>
-      <c r="T363" s="2" t="inlineStr"/>
+      <c r="T363" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -19273,7 +20593,11 @@
       <c r="Q364" s="2" t="inlineStr"/>
       <c r="R364" s="2" t="inlineStr"/>
       <c r="S364" s="2" t="inlineStr"/>
-      <c r="T364" s="2" t="inlineStr"/>
+      <c r="T364" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
@@ -19325,7 +20649,11 @@
       <c r="Q365" s="2" t="inlineStr"/>
       <c r="R365" s="2" t="inlineStr"/>
       <c r="S365" s="2" t="inlineStr"/>
-      <c r="T365" s="2" t="inlineStr"/>
+      <c r="T365" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -19377,7 +20705,11 @@
       <c r="Q366" s="2" t="inlineStr"/>
       <c r="R366" s="2" t="inlineStr"/>
       <c r="S366" s="2" t="inlineStr"/>
-      <c r="T366" s="2" t="inlineStr"/>
+      <c r="T366" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -19429,7 +20761,11 @@
       <c r="Q367" s="2" t="inlineStr"/>
       <c r="R367" s="2" t="inlineStr"/>
       <c r="S367" s="2" t="inlineStr"/>
-      <c r="T367" s="2" t="inlineStr"/>
+      <c r="T367" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -19481,7 +20817,11 @@
       <c r="Q368" s="2" t="inlineStr"/>
       <c r="R368" s="2" t="inlineStr"/>
       <c r="S368" s="2" t="inlineStr"/>
-      <c r="T368" s="2" t="inlineStr"/>
+      <c r="T368" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
@@ -19533,7 +20873,11 @@
       <c r="Q369" s="2" t="inlineStr"/>
       <c r="R369" s="2" t="inlineStr"/>
       <c r="S369" s="2" t="inlineStr"/>
-      <c r="T369" s="2" t="inlineStr"/>
+      <c r="T369" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -19583,7 +20927,11 @@
       <c r="Q370" s="2" t="inlineStr"/>
       <c r="R370" s="2" t="inlineStr"/>
       <c r="S370" s="2" t="inlineStr"/>
-      <c r="T370" s="2" t="inlineStr"/>
+      <c r="T370" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
@@ -19633,7 +20981,11 @@
       <c r="Q371" s="2" t="inlineStr"/>
       <c r="R371" s="2" t="inlineStr"/>
       <c r="S371" s="2" t="inlineStr"/>
-      <c r="T371" s="2" t="inlineStr"/>
+      <c r="T371" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -19685,7 +21037,11 @@
       <c r="Q372" s="2" t="inlineStr"/>
       <c r="R372" s="2" t="inlineStr"/>
       <c r="S372" s="2" t="inlineStr"/>
-      <c r="T372" s="2" t="inlineStr"/>
+      <c r="T372" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -19737,7 +21093,11 @@
       <c r="Q373" s="2" t="inlineStr"/>
       <c r="R373" s="2" t="inlineStr"/>
       <c r="S373" s="2" t="inlineStr"/>
-      <c r="T373" s="2" t="inlineStr"/>
+      <c r="T373" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -19789,7 +21149,11 @@
       <c r="Q374" s="2" t="inlineStr"/>
       <c r="R374" s="2" t="inlineStr"/>
       <c r="S374" s="2" t="inlineStr"/>
-      <c r="T374" s="2" t="inlineStr"/>
+      <c r="T374" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
@@ -19841,7 +21205,11 @@
       <c r="Q375" s="2" t="inlineStr"/>
       <c r="R375" s="2" t="inlineStr"/>
       <c r="S375" s="2" t="inlineStr"/>
-      <c r="T375" s="2" t="inlineStr"/>
+      <c r="T375" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -19893,7 +21261,11 @@
       <c r="Q376" s="2" t="inlineStr"/>
       <c r="R376" s="2" t="inlineStr"/>
       <c r="S376" s="2" t="inlineStr"/>
-      <c r="T376" s="2" t="inlineStr"/>
+      <c r="T376" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -19945,7 +21317,11 @@
       <c r="Q377" s="2" t="inlineStr"/>
       <c r="R377" s="2" t="inlineStr"/>
       <c r="S377" s="2" t="inlineStr"/>
-      <c r="T377" s="2" t="inlineStr"/>
+      <c r="T377" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
@@ -19997,7 +21373,11 @@
       <c r="Q378" s="2" t="inlineStr"/>
       <c r="R378" s="2" t="inlineStr"/>
       <c r="S378" s="2" t="inlineStr"/>
-      <c r="T378" s="2" t="inlineStr"/>
+      <c r="T378" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
@@ -20049,7 +21429,11 @@
       <c r="Q379" s="2" t="inlineStr"/>
       <c r="R379" s="2" t="inlineStr"/>
       <c r="S379" s="2" t="inlineStr"/>
-      <c r="T379" s="2" t="inlineStr"/>
+      <c r="T379" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
@@ -20099,7 +21483,11 @@
       <c r="Q380" s="2" t="inlineStr"/>
       <c r="R380" s="2" t="inlineStr"/>
       <c r="S380" s="2" t="inlineStr"/>
-      <c r="T380" s="2" t="inlineStr"/>
+      <c r="T380" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
@@ -20149,7 +21537,11 @@
       <c r="Q381" s="2" t="inlineStr"/>
       <c r="R381" s="2" t="inlineStr"/>
       <c r="S381" s="2" t="inlineStr"/>
-      <c r="T381" s="2" t="inlineStr"/>
+      <c r="T381" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -20201,7 +21593,11 @@
       <c r="Q382" s="2" t="inlineStr"/>
       <c r="R382" s="2" t="inlineStr"/>
       <c r="S382" s="2" t="inlineStr"/>
-      <c r="T382" s="2" t="inlineStr"/>
+      <c r="T382" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -20253,7 +21649,11 @@
       <c r="Q383" s="2" t="inlineStr"/>
       <c r="R383" s="2" t="inlineStr"/>
       <c r="S383" s="2" t="inlineStr"/>
-      <c r="T383" s="2" t="inlineStr"/>
+      <c r="T383" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -20305,7 +21705,11 @@
       <c r="Q384" s="2" t="inlineStr"/>
       <c r="R384" s="2" t="inlineStr"/>
       <c r="S384" s="2" t="inlineStr"/>
-      <c r="T384" s="2" t="inlineStr"/>
+      <c r="T384" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -20357,7 +21761,11 @@
       <c r="Q385" s="2" t="inlineStr"/>
       <c r="R385" s="2" t="inlineStr"/>
       <c r="S385" s="2" t="inlineStr"/>
-      <c r="T385" s="2" t="inlineStr"/>
+      <c r="T385" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -20409,7 +21817,11 @@
       <c r="Q386" s="2" t="inlineStr"/>
       <c r="R386" s="2" t="inlineStr"/>
       <c r="S386" s="2" t="inlineStr"/>
-      <c r="T386" s="2" t="inlineStr"/>
+      <c r="T386" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
@@ -20459,7 +21871,11 @@
       <c r="Q387" s="2" t="inlineStr"/>
       <c r="R387" s="2" t="inlineStr"/>
       <c r="S387" s="2" t="inlineStr"/>
-      <c r="T387" s="2" t="inlineStr"/>
+      <c r="T387" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -20509,7 +21925,11 @@
       <c r="Q388" s="2" t="inlineStr"/>
       <c r="R388" s="2" t="inlineStr"/>
       <c r="S388" s="2" t="inlineStr"/>
-      <c r="T388" s="2" t="inlineStr"/>
+      <c r="T388" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -20561,7 +21981,11 @@
       <c r="Q389" s="2" t="inlineStr"/>
       <c r="R389" s="2" t="inlineStr"/>
       <c r="S389" s="2" t="inlineStr"/>
-      <c r="T389" s="2" t="inlineStr"/>
+      <c r="T389" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -20613,7 +22037,11 @@
       <c r="Q390" s="2" t="inlineStr"/>
       <c r="R390" s="2" t="inlineStr"/>
       <c r="S390" s="2" t="inlineStr"/>
-      <c r="T390" s="2" t="inlineStr"/>
+      <c r="T390" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
@@ -20665,7 +22093,11 @@
       <c r="Q391" s="2" t="inlineStr"/>
       <c r="R391" s="2" t="inlineStr"/>
       <c r="S391" s="2" t="inlineStr"/>
-      <c r="T391" s="2" t="inlineStr"/>
+      <c r="T391" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -20717,7 +22149,11 @@
       <c r="Q392" s="2" t="inlineStr"/>
       <c r="R392" s="2" t="inlineStr"/>
       <c r="S392" s="2" t="inlineStr"/>
-      <c r="T392" s="2" t="inlineStr"/>
+      <c r="T392" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
@@ -20769,7 +22205,11 @@
       <c r="Q393" s="2" t="inlineStr"/>
       <c r="R393" s="2" t="inlineStr"/>
       <c r="S393" s="2" t="inlineStr"/>
-      <c r="T393" s="2" t="inlineStr"/>
+      <c r="T393" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -20821,7 +22261,11 @@
       <c r="Q394" s="2" t="inlineStr"/>
       <c r="R394" s="2" t="inlineStr"/>
       <c r="S394" s="2" t="inlineStr"/>
-      <c r="T394" s="2" t="inlineStr"/>
+      <c r="T394" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
@@ -20873,7 +22317,11 @@
       <c r="Q395" s="2" t="inlineStr"/>
       <c r="R395" s="2" t="inlineStr"/>
       <c r="S395" s="2" t="inlineStr"/>
-      <c r="T395" s="2" t="inlineStr"/>
+      <c r="T395" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -20925,7 +22373,11 @@
       <c r="Q396" s="2" t="inlineStr"/>
       <c r="R396" s="2" t="inlineStr"/>
       <c r="S396" s="2" t="inlineStr"/>
-      <c r="T396" s="2" t="inlineStr"/>
+      <c r="T396" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -20975,7 +22427,11 @@
       <c r="Q397" s="2" t="inlineStr"/>
       <c r="R397" s="2" t="inlineStr"/>
       <c r="S397" s="2" t="inlineStr"/>
-      <c r="T397" s="2" t="inlineStr"/>
+      <c r="T397" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -21025,7 +22481,11 @@
       <c r="Q398" s="2" t="inlineStr"/>
       <c r="R398" s="2" t="inlineStr"/>
       <c r="S398" s="2" t="inlineStr"/>
-      <c r="T398" s="2" t="inlineStr"/>
+      <c r="T398" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
@@ -21077,7 +22537,11 @@
       <c r="Q399" s="2" t="inlineStr"/>
       <c r="R399" s="2" t="inlineStr"/>
       <c r="S399" s="2" t="inlineStr"/>
-      <c r="T399" s="2" t="inlineStr"/>
+      <c r="T399" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -21129,7 +22593,11 @@
       <c r="Q400" s="2" t="inlineStr"/>
       <c r="R400" s="2" t="inlineStr"/>
       <c r="S400" s="2" t="inlineStr"/>
-      <c r="T400" s="2" t="inlineStr"/>
+      <c r="T400" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
@@ -21181,7 +22649,11 @@
       <c r="Q401" s="2" t="inlineStr"/>
       <c r="R401" s="2" t="inlineStr"/>
       <c r="S401" s="2" t="inlineStr"/>
-      <c r="T401" s="2" t="inlineStr"/>
+      <c r="T401" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -21233,7 +22705,11 @@
       <c r="Q402" s="2" t="inlineStr"/>
       <c r="R402" s="2" t="inlineStr"/>
       <c r="S402" s="2" t="inlineStr"/>
-      <c r="T402" s="2" t="inlineStr"/>
+      <c r="T402" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -21285,7 +22761,11 @@
       <c r="Q403" s="2" t="inlineStr"/>
       <c r="R403" s="2" t="inlineStr"/>
       <c r="S403" s="2" t="inlineStr"/>
-      <c r="T403" s="2" t="inlineStr"/>
+      <c r="T403" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -21337,7 +22817,11 @@
       <c r="Q404" s="2" t="inlineStr"/>
       <c r="R404" s="2" t="inlineStr"/>
       <c r="S404" s="2" t="inlineStr"/>
-      <c r="T404" s="2" t="inlineStr"/>
+      <c r="T404" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
@@ -21389,7 +22873,11 @@
       <c r="Q405" s="2" t="inlineStr"/>
       <c r="R405" s="2" t="inlineStr"/>
       <c r="S405" s="2" t="inlineStr"/>
-      <c r="T405" s="2" t="inlineStr"/>
+      <c r="T405" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -21441,7 +22929,11 @@
       <c r="Q406" s="2" t="inlineStr"/>
       <c r="R406" s="2" t="inlineStr"/>
       <c r="S406" s="2" t="inlineStr"/>
-      <c r="T406" s="2" t="inlineStr"/>
+      <c r="T406" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
@@ -21491,7 +22983,11 @@
       <c r="Q407" s="2" t="inlineStr"/>
       <c r="R407" s="2" t="inlineStr"/>
       <c r="S407" s="2" t="inlineStr"/>
-      <c r="T407" s="2" t="inlineStr"/>
+      <c r="T407" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -21541,7 +23037,11 @@
       <c r="Q408" s="2" t="inlineStr"/>
       <c r="R408" s="2" t="inlineStr"/>
       <c r="S408" s="2" t="inlineStr"/>
-      <c r="T408" s="2" t="inlineStr"/>
+      <c r="T408" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -21593,7 +23093,11 @@
       <c r="Q409" s="2" t="inlineStr"/>
       <c r="R409" s="2" t="inlineStr"/>
       <c r="S409" s="2" t="inlineStr"/>
-      <c r="T409" s="2" t="inlineStr"/>
+      <c r="T409" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -21645,7 +23149,11 @@
       <c r="Q410" s="2" t="inlineStr"/>
       <c r="R410" s="2" t="inlineStr"/>
       <c r="S410" s="2" t="inlineStr"/>
-      <c r="T410" s="2" t="inlineStr"/>
+      <c r="T410" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -21697,7 +23205,11 @@
       <c r="Q411" s="2" t="inlineStr"/>
       <c r="R411" s="2" t="inlineStr"/>
       <c r="S411" s="2" t="inlineStr"/>
-      <c r="T411" s="2" t="inlineStr"/>
+      <c r="T411" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -21749,7 +23261,11 @@
       <c r="Q412" s="2" t="inlineStr"/>
       <c r="R412" s="2" t="inlineStr"/>
       <c r="S412" s="2" t="inlineStr"/>
-      <c r="T412" s="2" t="inlineStr"/>
+      <c r="T412" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
@@ -21801,7 +23317,11 @@
       <c r="Q413" s="2" t="inlineStr"/>
       <c r="R413" s="2" t="inlineStr"/>
       <c r="S413" s="2" t="inlineStr"/>
-      <c r="T413" s="2" t="inlineStr"/>
+      <c r="T413" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -21853,7 +23373,11 @@
       <c r="Q414" s="2" t="inlineStr"/>
       <c r="R414" s="2" t="inlineStr"/>
       <c r="S414" s="2" t="inlineStr"/>
-      <c r="T414" s="2" t="inlineStr"/>
+      <c r="T414" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
@@ -21905,7 +23429,11 @@
       <c r="Q415" s="2" t="inlineStr"/>
       <c r="R415" s="2" t="inlineStr"/>
       <c r="S415" s="2" t="inlineStr"/>
-      <c r="T415" s="2" t="inlineStr"/>
+      <c r="T415" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -21957,7 +23485,11 @@
       <c r="Q416" s="2" t="inlineStr"/>
       <c r="R416" s="2" t="inlineStr"/>
       <c r="S416" s="2" t="inlineStr"/>
-      <c r="T416" s="2" t="inlineStr"/>
+      <c r="T416" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
@@ -22007,7 +23539,11 @@
       <c r="Q417" s="2" t="inlineStr"/>
       <c r="R417" s="2" t="inlineStr"/>
       <c r="S417" s="2" t="inlineStr"/>
-      <c r="T417" s="2" t="inlineStr"/>
+      <c r="T417" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -22057,7 +23593,11 @@
       <c r="Q418" s="2" t="inlineStr"/>
       <c r="R418" s="2" t="inlineStr"/>
       <c r="S418" s="2" t="inlineStr"/>
-      <c r="T418" s="2" t="inlineStr"/>
+      <c r="T418" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"MASTER_REQUIRED_PENDING","stage1_disposition":"需新建Master"}</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
@@ -22111,7 +23651,11 @@
           <t>215.0×153.6mm不属于襻间枋统一截面</t>
         </is>
       </c>
-      <c r="T419" s="2" t="inlineStr"/>
+      <c r="T419" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -22165,7 +23709,11 @@
           <t>215.0×153.6mm不属于襻间枋统一截面</t>
         </is>
       </c>
-      <c r="T420" s="2" t="inlineStr"/>
+      <c r="T420" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
@@ -22219,7 +23767,11 @@
           <t>215.0×153.6mm不属于襻间枋统一截面</t>
         </is>
       </c>
-      <c r="T421" s="2" t="inlineStr"/>
+      <c r="T421" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -22273,7 +23825,11 @@
           <t>215.0×153.6mm不属于襻间枋统一截面</t>
         </is>
       </c>
-      <c r="T422" s="2" t="inlineStr"/>
+      <c r="T422" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -22327,7 +23883,11 @@
           <t>215.0×153.6mm不属于襻间枋统一截面</t>
         </is>
       </c>
-      <c r="T423" s="2" t="inlineStr"/>
+      <c r="T423" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -22381,7 +23941,11 @@
           <t>215.0×153.6mm不属于襻间枋统一截面</t>
         </is>
       </c>
-      <c r="T424" s="2" t="inlineStr"/>
+      <c r="T424" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
@@ -22435,7 +23999,11 @@
           <t>215.0×153.6mm不属于襻间枋统一截面</t>
         </is>
       </c>
-      <c r="T425" s="2" t="inlineStr"/>
+      <c r="T425" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -22489,7 +24057,11 @@
           <t>215.0×153.6mm不属于襻间枋统一截面</t>
         </is>
       </c>
-      <c r="T426" s="2" t="inlineStr"/>
+      <c r="T426" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
@@ -22543,7 +24115,11 @@
           <t>215.0×153.6mm不属于襻间枋统一截面</t>
         </is>
       </c>
-      <c r="T427" s="2" t="inlineStr"/>
+      <c r="T427" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -22597,7 +24173,11 @@
           <t>215.0×153.6mm不属于襻间枋统一截面</t>
         </is>
       </c>
-      <c r="T428" s="2" t="inlineStr"/>
+      <c r="T428" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
@@ -22651,7 +24231,11 @@
           <t>215.0×153.6mm不属于襻间枋统一截面</t>
         </is>
       </c>
-      <c r="T429" s="2" t="inlineStr"/>
+      <c r="T429" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -22705,7 +24289,11 @@
           <t>215.0×153.6mm不属于襻间枋统一截面</t>
         </is>
       </c>
-      <c r="T430" s="2" t="inlineStr"/>
+      <c r="T430" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
@@ -22753,7 +24341,7 @@
       <c r="S431" s="2" t="inlineStr"/>
       <c r="T431" s="2" t="inlineStr">
         <is>
-          <t>{"breakdown":"上下六椽栿间4；上六椽栿与四椽栿间4；下平槫下8；上平槫下4；脊槫下4"}</t>
+          <t>{"breakdown":"上下六椽栿间4；上六椽栿与四椽栿间4；下平槫下8；上平槫下4；脊槫下4","master_coverage_status":"NOT_PHYSICAL_MASTER","stage1_disposition":"非实体装配/拓扑"}</t>
         </is>
       </c>
     </row>
@@ -22803,7 +24391,7 @@
       <c r="S432" s="2" t="inlineStr"/>
       <c r="T432" s="2" t="inlineStr">
         <is>
-          <t>{"mean_mm":{"asymmetric_half_exposed_length":680.1,"symmetric_length":1757,"thickness":151.8,"width":150.4},"measured_records":23,"total_count":"UNKNOWN"}</t>
+          <t>{"master_coverage_status":"UNKNOWN_REFERENCE_BOUNDARY","mean_mm":{"asymmetric_half_exposed_length":680.1,"symmetric_length":1757,"thickness":151.8,"width":150.4},"measured_records":23,"stage1_disposition":"UNKNOWN/参考边界","total_count":"UNKNOWN"}</t>
         </is>
       </c>
     </row>
@@ -22857,7 +24445,7 @@
       <c r="S433" s="2" t="inlineStr"/>
       <c r="T433" s="2" t="inlineStr">
         <is>
-          <t>{"real_count":"UNKNOWN","spacing":"UNKNOWN"}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","real_count":"UNKNOWN","spacing":"UNKNOWN","stage1_disposition":"参数化补全"}</t>
         </is>
       </c>
     </row>
@@ -22909,7 +24497,11 @@
         </is>
       </c>
       <c r="S434" s="2" t="inlineStr"/>
-      <c r="T434" s="2" t="inlineStr"/>
+      <c r="T434" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -22959,7 +24551,11 @@
         </is>
       </c>
       <c r="S435" s="2" t="inlineStr"/>
-      <c r="T435" s="2" t="inlineStr"/>
+      <c r="T435" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -23009,7 +24605,11 @@
         </is>
       </c>
       <c r="S436" s="2" t="inlineStr"/>
-      <c r="T436" s="2" t="inlineStr"/>
+      <c r="T436" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
@@ -23059,7 +24659,11 @@
         </is>
       </c>
       <c r="S437" s="2" t="inlineStr"/>
-      <c r="T437" s="2" t="inlineStr"/>
+      <c r="T437" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -23107,7 +24711,7 @@
       <c r="S438" s="2" t="inlineStr"/>
       <c r="T438" s="2" t="inlineStr">
         <is>
-          <t>{"chijiao_tongji":17,"count":1}</t>
+          <t>{"chijiao_tongji":17,"count":1,"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
         </is>
       </c>
     </row>
@@ -23157,7 +24761,7 @@
       <c r="S439" s="2" t="inlineStr"/>
       <c r="T439" s="2" t="inlineStr">
         <is>
-          <t>{"tongji_per_ridge":20}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全","tongji_per_ridge":20}</t>
         </is>
       </c>
     </row>
@@ -23207,7 +24811,7 @@
       <c r="S440" s="2" t="inlineStr"/>
       <c r="T440" s="2" t="inlineStr">
         <is>
-          <t>{"tongji_per_ridge":20}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全","tongji_per_ridge":20}</t>
         </is>
       </c>
     </row>
@@ -23257,7 +24861,7 @@
       <c r="S441" s="2" t="inlineStr"/>
       <c r="T441" s="2" t="inlineStr">
         <is>
-          <t>{"tongji_per_ridge":20}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全","tongji_per_ridge":20}</t>
         </is>
       </c>
     </row>
@@ -23307,7 +24911,7 @@
       <c r="S442" s="2" t="inlineStr"/>
       <c r="T442" s="2" t="inlineStr">
         <is>
-          <t>{"tongji_per_ridge":20}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全","tongji_per_ridge":20}</t>
         </is>
       </c>
     </row>
@@ -23357,7 +24961,7 @@
       <c r="S443" s="2" t="inlineStr"/>
       <c r="T443" s="2" t="inlineStr">
         <is>
-          <t>{"tongji_per_ridge":"5-6 + 找头"}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全","tongji_per_ridge":"5-6 + 找头"}</t>
         </is>
       </c>
     </row>
@@ -23407,7 +25011,7 @@
       <c r="S444" s="2" t="inlineStr"/>
       <c r="T444" s="2" t="inlineStr">
         <is>
-          <t>{"tongji_per_ridge":"5-6 + 找头"}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全","tongji_per_ridge":"5-6 + 找头"}</t>
         </is>
       </c>
     </row>
@@ -23457,7 +25061,7 @@
       <c r="S445" s="2" t="inlineStr"/>
       <c r="T445" s="2" t="inlineStr">
         <is>
-          <t>{"tongji_per_ridge":"5-6 + 找头"}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全","tongji_per_ridge":"5-6 + 找头"}</t>
         </is>
       </c>
     </row>
@@ -23507,7 +25111,7 @@
       <c r="S446" s="2" t="inlineStr"/>
       <c r="T446" s="2" t="inlineStr">
         <is>
-          <t>{"tongji_per_ridge":"5-6 + 找头"}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全","tongji_per_ridge":"5-6 + 找头"}</t>
         </is>
       </c>
     </row>
@@ -23557,7 +25161,7 @@
       <c r="S447" s="2" t="inlineStr"/>
       <c r="T447" s="2" t="inlineStr">
         <is>
-          <t>{"internal_structure":"UNKNOWN"}</t>
+          <t>{"internal_structure":"UNKNOWN","master_coverage_status":"SIMPLIFIED_PROXY","stage1_disposition":"简化Proxy"}</t>
         </is>
       </c>
     </row>
@@ -23605,7 +25209,11 @@
       <c r="Q448" s="2" t="inlineStr"/>
       <c r="R448" s="2" t="inlineStr"/>
       <c r="S448" s="2" t="inlineStr"/>
-      <c r="T448" s="2" t="inlineStr"/>
+      <c r="T448" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"SIMPLIFIED_PROXY","stage1_disposition":"简化Proxy"}</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
@@ -23651,7 +25259,11 @@
       <c r="Q449" s="2" t="inlineStr"/>
       <c r="R449" s="2" t="inlineStr"/>
       <c r="S449" s="2" t="inlineStr"/>
-      <c r="T449" s="2" t="inlineStr"/>
+      <c r="T449" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"SIMPLIFIED_PROXY","stage1_disposition":"简化Proxy"}</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -23697,7 +25309,11 @@
       <c r="Q450" s="2" t="inlineStr"/>
       <c r="R450" s="2" t="inlineStr"/>
       <c r="S450" s="2" t="inlineStr"/>
-      <c r="T450" s="2" t="inlineStr"/>
+      <c r="T450" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"SIMPLIFIED_PROXY","stage1_disposition":"简化Proxy"}</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
@@ -23743,7 +25359,11 @@
       <c r="Q451" s="2" t="inlineStr"/>
       <c r="R451" s="2" t="inlineStr"/>
       <c r="S451" s="2" t="inlineStr"/>
-      <c r="T451" s="2" t="inlineStr"/>
+      <c r="T451" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"SIMPLIFIED_PROXY","stage1_disposition":"简化Proxy"}</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
@@ -23791,7 +25411,7 @@
       <c r="S452" s="2" t="inlineStr"/>
       <c r="T452" s="2" t="inlineStr">
         <is>
-          <t>{"woodwork":"VISUAL_MODEL + PARAMETRIC_SECTION"}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全","woodwork":"VISUAL_MODEL + PARAMETRIC_SECTION"}</t>
         </is>
       </c>
     </row>
@@ -23841,7 +25461,7 @@
       <c r="S453" s="2" t="inlineStr"/>
       <c r="T453" s="2" t="inlineStr">
         <is>
-          <t>{"woodwork":"VISUAL_MODEL + PARAMETRIC_SECTION"}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全","woodwork":"VISUAL_MODEL + PARAMETRIC_SECTION"}</t>
         </is>
       </c>
     </row>
@@ -23891,7 +25511,7 @@
       <c r="S454" s="2" t="inlineStr"/>
       <c r="T454" s="2" t="inlineStr">
         <is>
-          <t>{"outer_wall_cm":84}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","outer_wall_cm":84,"stage1_disposition":"参数化补全"}</t>
         </is>
       </c>
     </row>
@@ -23941,7 +25561,7 @@
       <c r="S455" s="2" t="inlineStr"/>
       <c r="T455" s="2" t="inlineStr">
         <is>
-          <t>{"outer_wall_cm":101}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","outer_wall_cm":101,"stage1_disposition":"参数化补全"}</t>
         </is>
       </c>
     </row>
@@ -23989,7 +25609,11 @@
       <c r="Q456" s="2" t="inlineStr"/>
       <c r="R456" s="2" t="inlineStr"/>
       <c r="S456" s="2" t="inlineStr"/>
-      <c r="T456" s="2" t="inlineStr"/>
+      <c r="T456" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
@@ -24035,7 +25659,11 @@
       <c r="Q457" s="2" t="inlineStr"/>
       <c r="R457" s="2" t="inlineStr"/>
       <c r="S457" s="2" t="inlineStr"/>
-      <c r="T457" s="2" t="inlineStr"/>
+      <c r="T457" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
@@ -24081,7 +25709,11 @@
       <c r="Q458" s="2" t="inlineStr"/>
       <c r="R458" s="2" t="inlineStr"/>
       <c r="S458" s="2" t="inlineStr"/>
-      <c r="T458" s="2" t="inlineStr"/>
+      <c r="T458" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
@@ -24127,7 +25759,11 @@
       <c r="Q459" s="2" t="inlineStr"/>
       <c r="R459" s="2" t="inlineStr"/>
       <c r="S459" s="2" t="inlineStr"/>
-      <c r="T459" s="2" t="inlineStr"/>
+      <c r="T459" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
@@ -24173,7 +25809,11 @@
       <c r="Q460" s="2" t="inlineStr"/>
       <c r="R460" s="2" t="inlineStr"/>
       <c r="S460" s="2" t="inlineStr"/>
-      <c r="T460" s="2" t="inlineStr"/>
+      <c r="T460" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
@@ -24219,7 +25859,11 @@
       <c r="Q461" s="2" t="inlineStr"/>
       <c r="R461" s="2" t="inlineStr"/>
       <c r="S461" s="2" t="inlineStr"/>
-      <c r="T461" s="2" t="inlineStr"/>
+      <c r="T461" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
@@ -24265,7 +25909,11 @@
       <c r="Q462" s="2" t="inlineStr"/>
       <c r="R462" s="2" t="inlineStr"/>
       <c r="S462" s="2" t="inlineStr"/>
-      <c r="T462" s="2" t="inlineStr"/>
+      <c r="T462" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
@@ -24311,7 +25959,11 @@
       <c r="Q463" s="2" t="inlineStr"/>
       <c r="R463" s="2" t="inlineStr"/>
       <c r="S463" s="2" t="inlineStr"/>
-      <c r="T463" s="2" t="inlineStr"/>
+      <c r="T463" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
@@ -24357,7 +26009,11 @@
       <c r="Q464" s="2" t="inlineStr"/>
       <c r="R464" s="2" t="inlineStr"/>
       <c r="S464" s="2" t="inlineStr"/>
-      <c r="T464" s="2" t="inlineStr"/>
+      <c r="T464" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
@@ -24403,7 +26059,11 @@
       <c r="Q465" s="2" t="inlineStr"/>
       <c r="R465" s="2" t="inlineStr"/>
       <c r="S465" s="2" t="inlineStr"/>
-      <c r="T465" s="2" t="inlineStr"/>
+      <c r="T465" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -24449,7 +26109,11 @@
       <c r="Q466" s="2" t="inlineStr"/>
       <c r="R466" s="2" t="inlineStr"/>
       <c r="S466" s="2" t="inlineStr"/>
-      <c r="T466" s="2" t="inlineStr"/>
+      <c r="T466" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
@@ -24495,7 +26159,11 @@
       <c r="Q467" s="2" t="inlineStr"/>
       <c r="R467" s="2" t="inlineStr"/>
       <c r="S467" s="2" t="inlineStr"/>
-      <c r="T467" s="2" t="inlineStr"/>
+      <c r="T467" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -24541,7 +26209,11 @@
       <c r="Q468" s="2" t="inlineStr"/>
       <c r="R468" s="2" t="inlineStr"/>
       <c r="S468" s="2" t="inlineStr"/>
-      <c r="T468" s="2" t="inlineStr"/>
+      <c r="T468" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
@@ -24587,7 +26259,11 @@
       <c r="Q469" s="2" t="inlineStr"/>
       <c r="R469" s="2" t="inlineStr"/>
       <c r="S469" s="2" t="inlineStr"/>
-      <c r="T469" s="2" t="inlineStr"/>
+      <c r="T469" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
@@ -24633,7 +26309,11 @@
       <c r="Q470" s="2" t="inlineStr"/>
       <c r="R470" s="2" t="inlineStr"/>
       <c r="S470" s="2" t="inlineStr"/>
-      <c r="T470" s="2" t="inlineStr"/>
+      <c r="T470" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
@@ -24679,7 +26359,11 @@
       <c r="Q471" s="2" t="inlineStr"/>
       <c r="R471" s="2" t="inlineStr"/>
       <c r="S471" s="2" t="inlineStr"/>
-      <c r="T471" s="2" t="inlineStr"/>
+      <c r="T471" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全"}</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -24725,7 +26409,11 @@
       <c r="Q472" s="2" t="inlineStr"/>
       <c r="R472" s="2" t="inlineStr"/>
       <c r="S472" s="2" t="inlineStr"/>
-      <c r="T472" s="2" t="inlineStr"/>
+      <c r="T472" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"SIMPLIFIED_PROXY","stage1_disposition":"简化Proxy"}</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
@@ -24771,7 +26459,11 @@
       <c r="Q473" s="2" t="inlineStr"/>
       <c r="R473" s="2" t="inlineStr"/>
       <c r="S473" s="2" t="inlineStr"/>
-      <c r="T473" s="2" t="inlineStr"/>
+      <c r="T473" s="2" t="inlineStr">
+        <is>
+          <t>{"master_coverage_status":"SIMPLIFIED_PROXY","stage1_disposition":"简化Proxy"}</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
@@ -24823,7 +26515,7 @@
       </c>
       <c r="T474" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"SYSTEM"}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","record_role":"SYSTEM","stage1_disposition":"参数化补全"}</t>
         </is>
       </c>
     </row>
@@ -24877,7 +26569,7 @@
       </c>
       <c r="T475" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"SYSTEM"}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","record_role":"SYSTEM","stage1_disposition":"参数化补全"}</t>
         </is>
       </c>
     </row>
@@ -24931,7 +26623,7 @@
       </c>
       <c r="T476" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"SYSTEM"}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","record_role":"SYSTEM","stage1_disposition":"参数化补全"}</t>
         </is>
       </c>
     </row>
@@ -24985,7 +26677,7 @@
       </c>
       <c r="T477" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"SYSTEM"}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","record_role":"SYSTEM","stage1_disposition":"参数化补全"}</t>
         </is>
       </c>
     </row>
@@ -25039,7 +26731,7 @@
       <c r="S478" s="2" t="inlineStr"/>
       <c r="T478" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"FAMILY_UNKNOWN_COUNT","total_count":"UNKNOWN"}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","record_role":"FAMILY_UNKNOWN_COUNT","stage1_disposition":"参数化补全","total_count":"UNKNOWN"}</t>
         </is>
       </c>
     </row>
@@ -25089,7 +26781,7 @@
       <c r="S479" s="2" t="inlineStr"/>
       <c r="T479" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"SYSTEM"}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","record_role":"SYSTEM","stage1_disposition":"参数化补全"}</t>
         </is>
       </c>
     </row>
@@ -25143,7 +26835,7 @@
       <c r="S480" s="2" t="inlineStr"/>
       <c r="T480" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"FAMILY_UNKNOWN_COUNT","total_count":"UNKNOWN"}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","record_role":"FAMILY_UNKNOWN_COUNT","stage1_disposition":"参数化补全","total_count":"UNKNOWN"}</t>
         </is>
       </c>
     </row>
@@ -25197,7 +26889,7 @@
       <c r="S481" s="2" t="inlineStr"/>
       <c r="T481" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"FAMILY_UNKNOWN_COUNT","total_count":"UNKNOWN"}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","record_role":"FAMILY_UNKNOWN_COUNT","stage1_disposition":"参数化补全","total_count":"UNKNOWN"}</t>
         </is>
       </c>
     </row>
@@ -25251,7 +26943,7 @@
       <c r="S482" s="2" t="inlineStr"/>
       <c r="T482" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"FAMILY_UNKNOWN_COUNT","total_count":"UNKNOWN"}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","record_role":"FAMILY_UNKNOWN_COUNT","stage1_disposition":"参数化补全","total_count":"UNKNOWN"}</t>
         </is>
       </c>
     </row>
@@ -25305,7 +26997,7 @@
       </c>
       <c r="T483" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"SYSTEM"}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","record_role":"SYSTEM","stage1_disposition":"参数化补全"}</t>
         </is>
       </c>
     </row>
@@ -25355,7 +27047,7 @@
       <c r="S484" s="2" t="inlineStr"/>
       <c r="T484" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"PARAMETRIC_COMPLETION","total_count":"UNKNOWN"}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","record_role":"PARAMETRIC_COMPLETION","stage1_disposition":"参数化补全","total_count":"UNKNOWN"}</t>
         </is>
       </c>
     </row>
@@ -25405,7 +27097,7 @@
       <c r="S485" s="2" t="inlineStr"/>
       <c r="T485" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"SIMPLIFIED_PROXY"}</t>
+          <t>{"master_coverage_status":"SIMPLIFIED_PROXY","record_role":"SIMPLIFIED_PROXY","stage1_disposition":"简化Proxy"}</t>
         </is>
       </c>
     </row>
@@ -25455,7 +27147,7 @@
       <c r="S486" s="2" t="inlineStr"/>
       <c r="T486" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"SIMPLIFIED_PROXY"}</t>
+          <t>{"master_coverage_status":"SIMPLIFIED_PROXY","record_role":"SIMPLIFIED_PROXY","stage1_disposition":"简化Proxy"}</t>
         </is>
       </c>
     </row>
@@ -25505,7 +27197,7 @@
       <c r="S487" s="2" t="inlineStr"/>
       <c r="T487" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"SIMPLIFIED_PROXY"}</t>
+          <t>{"master_coverage_status":"SIMPLIFIED_PROXY","record_role":"SIMPLIFIED_PROXY","stage1_disposition":"简化Proxy"}</t>
         </is>
       </c>
     </row>
@@ -25555,7 +27247,7 @@
       <c r="S488" s="2" t="inlineStr"/>
       <c r="T488" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"SIMPLIFIED_PROXY"}</t>
+          <t>{"master_coverage_status":"SIMPLIFIED_PROXY","record_role":"SIMPLIFIED_PROXY","stage1_disposition":"简化Proxy"}</t>
         </is>
       </c>
     </row>
@@ -25605,7 +27297,7 @@
       <c r="S489" s="2" t="inlineStr"/>
       <c r="T489" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"SIMPLIFIED_PROXY"}</t>
+          <t>{"master_coverage_status":"SIMPLIFIED_PROXY","record_role":"SIMPLIFIED_PROXY","stage1_disposition":"简化Proxy"}</t>
         </is>
       </c>
     </row>
@@ -25655,7 +27347,7 @@
       <c r="S490" s="2" t="inlineStr"/>
       <c r="T490" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"SIMPLIFIED_PROXY"}</t>
+          <t>{"master_coverage_status":"SIMPLIFIED_PROXY","record_role":"SIMPLIFIED_PROXY","stage1_disposition":"简化Proxy"}</t>
         </is>
       </c>
     </row>
@@ -25705,7 +27397,7 @@
       <c r="S491" s="2" t="inlineStr"/>
       <c r="T491" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"SIMPLIFIED_PROXY"}</t>
+          <t>{"master_coverage_status":"SIMPLIFIED_PROXY","record_role":"SIMPLIFIED_PROXY","stage1_disposition":"简化Proxy"}</t>
         </is>
       </c>
     </row>
@@ -25755,7 +27447,7 @@
       <c r="S492" s="2" t="inlineStr"/>
       <c r="T492" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"SIMPLIFIED_PROXY"}</t>
+          <t>{"master_coverage_status":"SIMPLIFIED_PROXY","record_role":"SIMPLIFIED_PROXY","stage1_disposition":"简化Proxy"}</t>
         </is>
       </c>
     </row>
@@ -25805,7 +27497,7 @@
       <c r="S493" s="2" t="inlineStr"/>
       <c r="T493" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"SIMPLIFIED_PROXY"}</t>
+          <t>{"master_coverage_status":"SIMPLIFIED_PROXY","record_role":"SIMPLIFIED_PROXY","stage1_disposition":"简化Proxy"}</t>
         </is>
       </c>
     </row>
@@ -25855,7 +27547,7 @@
       <c r="S494" s="2" t="inlineStr"/>
       <c r="T494" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"SIMPLIFIED_PROXY"}</t>
+          <t>{"master_coverage_status":"SIMPLIFIED_PROXY","record_role":"SIMPLIFIED_PROXY","stage1_disposition":"简化Proxy"}</t>
         </is>
       </c>
     </row>
@@ -25905,7 +27597,7 @@
       <c r="S495" s="2" t="inlineStr"/>
       <c r="T495" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"SIMPLIFIED_PROXY"}</t>
+          <t>{"master_coverage_status":"SIMPLIFIED_PROXY","record_role":"SIMPLIFIED_PROXY","stage1_disposition":"简化Proxy"}</t>
         </is>
       </c>
     </row>
@@ -25955,7 +27647,7 @@
       <c r="S496" s="2" t="inlineStr"/>
       <c r="T496" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"SIMPLIFIED_PROXY"}</t>
+          <t>{"master_coverage_status":"SIMPLIFIED_PROXY","record_role":"SIMPLIFIED_PROXY","stage1_disposition":"简化Proxy"}</t>
         </is>
       </c>
     </row>
@@ -26005,7 +27697,7 @@
       <c r="S497" s="2" t="inlineStr"/>
       <c r="T497" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"SIMPLIFIED_PROXY"}</t>
+          <t>{"master_coverage_status":"SIMPLIFIED_PROXY","record_role":"SIMPLIFIED_PROXY","stage1_disposition":"简化Proxy"}</t>
         </is>
       </c>
     </row>
@@ -26055,7 +27747,7 @@
       <c r="S498" s="2" t="inlineStr"/>
       <c r="T498" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"SIMPLIFIED_PROXY"}</t>
+          <t>{"master_coverage_status":"SIMPLIFIED_PROXY","record_role":"SIMPLIFIED_PROXY","stage1_disposition":"简化Proxy"}</t>
         </is>
       </c>
     </row>
@@ -26109,7 +27801,7 @@
       </c>
       <c r="T499" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"VISUAL_MODEL"}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","record_role":"VISUAL_MODEL","stage1_disposition":"参数化补全"}</t>
         </is>
       </c>
     </row>
@@ -26163,7 +27855,7 @@
       </c>
       <c r="T500" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"VISUAL_MODEL"}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","record_role":"VISUAL_MODEL","stage1_disposition":"参数化补全"}</t>
         </is>
       </c>
     </row>
@@ -26217,7 +27909,7 @@
       </c>
       <c r="T501" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"VISUAL_MODEL"}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","record_role":"VISUAL_MODEL","stage1_disposition":"参数化补全"}</t>
         </is>
       </c>
     </row>
@@ -26271,7 +27963,7 @@
       </c>
       <c r="T502" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"VISUAL_MODEL"}</t>
+          <t>{"master_coverage_status":"NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION","record_role":"VISUAL_MODEL","stage1_disposition":"参数化补全"}</t>
         </is>
       </c>
     </row>
@@ -26321,7 +28013,7 @@
       <c r="S503" s="2" t="inlineStr"/>
       <c r="T503" s="2" t="inlineStr">
         <is>
-          <t>{"master_reference":"CMP-DOU-SINGLE-LONGKAI-001_MASTER","record_role":"FAMILY_UNKNOWN_COUNT","total_count":"UNKNOWN"}</t>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-DOU-SINGLE-LONGKAI-001_MASTER","record_role":"FAMILY_UNKNOWN_COUNT","stage1_disposition":"已有Master｜族边界UNKNOWN","total_count":"UNKNOWN"}</t>
         </is>
       </c>
     </row>
@@ -26371,7 +28063,7 @@
       <c r="S504" s="2" t="inlineStr"/>
       <c r="T504" s="2" t="inlineStr">
         <is>
-          <t>{"master_reference":"CMP-DOU-INTERACTIVE-001_MASTER","record_role":"FAMILY_UNKNOWN_COUNT","total_count":"UNKNOWN"}</t>
+          <t>{"master_coverage_status":"APPROVED_MASTER_AVAILABLE","master_reference":"CMP-DOU-INTERACTIVE-001_MASTER","record_role":"FAMILY_UNKNOWN_COUNT","stage1_disposition":"已有Master｜族边界UNKNOWN","total_count":"UNKNOWN"}</t>
         </is>
       </c>
     </row>
@@ -26421,7 +28113,7 @@
       <c r="S505" s="2" t="inlineStr"/>
       <c r="T505" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"FAMILY_UNKNOWN_COUNT","total_count":"UNKNOWN"}</t>
+          <t>{"master_coverage_status":"UNKNOWN_REFERENCE_BOUNDARY","record_role":"FAMILY_UNKNOWN_COUNT","stage1_disposition":"UNKNOWN/参考边界","total_count":"UNKNOWN"}</t>
         </is>
       </c>
     </row>
@@ -26475,7 +28167,7 @@
       </c>
       <c r="T506" s="2" t="inlineStr">
         <is>
-          <t>{"record_role":"FAMILY_UNKNOWN_COUNT","total_count":"UNKNOWN"}</t>
+          <t>{"master_coverage_status":"UNKNOWN_REFERENCE_BOUNDARY","record_role":"FAMILY_UNKNOWN_COUNT","stage1_disposition":"UNKNOWN/参考边界","total_count":"UNKNOWN"}</t>
         </is>
       </c>
     </row>
@@ -28067,7 +29759,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>411778c2f80a0fd506e15381c06aac21433c394d</t>
+          <t>e10c5c375df2863df5b4b479feaf8e1e76a51fa9</t>
         </is>
       </c>
     </row>
@@ -28079,7 +29771,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>32ca8de69b9f6b2878f591dccceb9beac76c7e712462f216a69d61949490233a</t>
+          <t>c184152c5fc81d875c097980f4a1901eadf176ea0fd1a43a0b14a9113c78f299</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -29759,7 +29759,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>e10c5c375df2863df5b4b479feaf8e1e76a51fa9</t>
+          <t>9dd11724ba3a3f90ac22eed9849ee6a777ac5ee2</t>
         </is>
       </c>
     </row>
@@ -29771,7 +29771,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>c184152c5fc81d875c097980f4a1901eadf176ea0fd1a43a0b14a9113c78f299</t>
+          <t>64cebc163690e047e51d40f646a73c07e287d641db1d6a36751557dad3721fc8</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.357</v>
+        <v>0.393</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -999,12 +999,16 @@
           <t>需新建Master</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr"/>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-ZHAQIAN-001_MASTER</t>
+        </is>
+      </c>
       <c r="E25" s="3" t="n">
         <v>14</v>
       </c>
@@ -5163,10 +5167,14 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-ZHAQIAN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
           <t>山面数量直接确认</t>
@@ -5224,10 +5232,14 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-ZHAQIAN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
           <t>山面数量直接确认</t>
@@ -5285,10 +5297,14 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-ZHAQIAN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
           <t>山面数量直接确认</t>
@@ -5346,10 +5362,14 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-ZHAQIAN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
           <t>山面数量直接确认</t>
@@ -5407,10 +5427,14 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-ZHAQIAN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
           <t>剩余数量明确，位置未锁</t>
@@ -5468,10 +5492,14 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-ZHAQIAN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
           <t>剩余数量明确，位置未锁</t>
@@ -5529,10 +5557,14 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-ZHAQIAN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
           <t>剩余数量明确，位置未锁</t>
@@ -5590,10 +5622,14 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-ZHAQIAN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
           <t>剩余数量明确，位置未锁</t>
@@ -5651,10 +5687,14 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-ZHAQIAN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
           <t>剩余数量明确，位置未锁</t>
@@ -5712,10 +5752,14 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-ZHAQIAN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
           <t>剩余数量明确，位置未锁</t>
@@ -5773,10 +5817,14 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-ZHAQIAN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
           <t>剩余数量明确，位置未锁</t>
@@ -5834,10 +5882,14 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-ZHAQIAN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
           <t>剩余数量明确，位置未锁</t>
@@ -5895,10 +5947,14 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-ZHAQIAN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
           <t>剩余数量明确，位置未锁</t>
@@ -5956,10 +6012,14 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-ZHAQIAN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
           <t>剩余数量明确，位置未锁</t>
@@ -35527,7 +35587,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -35580,7 +35640,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -35590,7 +35650,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -35601,7 +35661,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>39.3%</t>
         </is>
       </c>
     </row>
@@ -35613,7 +35673,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>9dd11724ba3a3f90ac22eed9849ee6a777ac5ee2</t>
+          <t>8e92dc0c21f7582b356be53ffe444813d4de7acb</t>
         </is>
       </c>
     </row>
@@ -35625,7 +35685,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>64cebc163690e047e51d40f646a73c07e287d641db1d6a36751557dad3721fc8</t>
+          <t>53953cf2293dd77c1d597841eeca1afc55fcaadc8adaa6981bf7b627968f2f75</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.393</v>
+        <v>0.429</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -1821,12 +1821,16 @@
           <t>需新建Master</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr"/>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="E63" s="3" t="n">
         <v>33</v>
       </c>
@@ -6077,10 +6081,14 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
           <t>正身七道21根+三间拓扑</t>
@@ -6138,10 +6146,14 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
           <t>正身七道21根+三间拓扑</t>
@@ -6199,10 +6211,14 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
           <t>正身七道21根+三间拓扑</t>
@@ -6260,10 +6276,14 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
           <t>正身七道21根+三间拓扑</t>
@@ -6321,10 +6341,14 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H58" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
           <t>正身七道21根+三间拓扑</t>
@@ -6382,10 +6406,14 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H59" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
           <t>正身七道21根+三间拓扑</t>
@@ -6443,10 +6471,14 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
           <t>正身七道21根+三间拓扑</t>
@@ -6504,10 +6536,14 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
           <t>正身七道21根+三间拓扑</t>
@@ -6565,10 +6601,14 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H62" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
           <t>正身七道21根+三间拓扑</t>
@@ -6626,10 +6666,14 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
           <t>正身七道21根+三间拓扑</t>
@@ -6687,10 +6731,14 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
           <t>正身七道21根+三间拓扑</t>
@@ -6748,10 +6796,14 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
           <t>正身七道21根+三间拓扑</t>
@@ -6809,10 +6861,14 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
           <t>正身七道21根+三间拓扑</t>
@@ -6870,10 +6926,14 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
           <t>正身七道21根+三间拓扑</t>
@@ -6931,10 +6991,14 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
           <t>正身七道21根+三间拓扑</t>
@@ -6992,10 +7056,14 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
           <t>正身七道21根+三间拓扑</t>
@@ -7053,10 +7121,14 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
           <t>正身七道21根+三间拓扑</t>
@@ -7114,10 +7186,14 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H71" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
           <t>正身七道21根+三间拓扑</t>
@@ -7175,10 +7251,14 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H72" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
           <t>正身七道21根+三间拓扑</t>
@@ -7236,10 +7316,14 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H73" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
           <t>正身七道21根+三间拓扑</t>
@@ -7297,10 +7381,14 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
           <t>正身七道21根+三间拓扑</t>
@@ -7358,10 +7446,14 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H75" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I75" s="3" t="inlineStr">
         <is>
           <t>每山两道6根+三间拓扑</t>
@@ -7419,10 +7511,14 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
           <t>每山两道6根+三间拓扑</t>
@@ -7480,10 +7576,14 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H77" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I77" s="3" t="inlineStr">
         <is>
           <t>每山两道6根+三间拓扑</t>
@@ -7541,10 +7641,14 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H78" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
           <t>每山两道6根+三间拓扑</t>
@@ -7602,10 +7706,14 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
           <t>每山两道6根+三间拓扑</t>
@@ -7663,10 +7771,14 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
           <t>每山两道6根+三间拓扑</t>
@@ -7724,10 +7836,14 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H81" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
           <t>每山两道6根+三间拓扑</t>
@@ -7785,10 +7901,14 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H82" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
           <t>每山两道6根+三间拓扑</t>
@@ -7846,10 +7966,14 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H83" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
           <t>每山两道6根+三间拓扑</t>
@@ -7907,10 +8031,14 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
           <t>每山两道6根+三间拓扑</t>
@@ -7968,10 +8096,14 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H85" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
           <t>每山两道6根+三间拓扑</t>
@@ -8029,10 +8161,14 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H86" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="I86" s="3" t="inlineStr">
         <is>
           <t>每山两道6根+三间拓扑</t>
@@ -35640,7 +35776,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -35650,7 +35786,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -35661,7 +35797,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -35673,7 +35809,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>8e92dc0c21f7582b356be53ffe444813d4de7acb</t>
+          <t>9647e028f168c449fa86a2929181a577161faf4e</t>
         </is>
       </c>
     </row>
@@ -35685,7 +35821,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>53953cf2293dd77c1d597841eeca1afc55fcaadc8adaa6981bf7b627968f2f75</t>
+          <t>392419f5291b008e84320f9b4c31cebc8236ef77e2a676bbf5e32e8ba79d9b16</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.429</v>
+        <v>0.464</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -1624,12 +1624,16 @@
           <t>需新建Master</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr"/>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-TUOJIAO-001_MASTER</t>
+        </is>
+      </c>
       <c r="E54" s="3" t="n">
         <v>12</v>
       </c>
@@ -9982,10 +9986,14 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H115" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-TUOJIAO-001_MASTER</t>
+        </is>
+      </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
           <t>8根正身托脚+拓扑</t>
@@ -10043,10 +10051,14 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H116" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-TUOJIAO-001_MASTER</t>
+        </is>
+      </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
           <t>8根正身托脚+拓扑</t>
@@ -10104,10 +10116,14 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H117" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-TUOJIAO-001_MASTER</t>
+        </is>
+      </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
           <t>8根正身托脚+拓扑</t>
@@ -10165,10 +10181,14 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H118" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-TUOJIAO-001_MASTER</t>
+        </is>
+      </c>
       <c r="I118" s="3" t="inlineStr">
         <is>
           <t>8根正身托脚+拓扑</t>
@@ -10226,10 +10246,14 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H119" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-TUOJIAO-001_MASTER</t>
+        </is>
+      </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
           <t>8根正身托脚+拓扑</t>
@@ -10287,10 +10311,14 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H120" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-TUOJIAO-001_MASTER</t>
+        </is>
+      </c>
       <c r="I120" s="3" t="inlineStr">
         <is>
           <t>8根正身托脚+拓扑</t>
@@ -10348,10 +10376,14 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H121" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-TUOJIAO-001_MASTER</t>
+        </is>
+      </c>
       <c r="I121" s="3" t="inlineStr">
         <is>
           <t>8根正身托脚+拓扑</t>
@@ -10409,10 +10441,14 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H122" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-TUOJIAO-001_MASTER</t>
+        </is>
+      </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
           <t>8根正身托脚+拓扑</t>
@@ -10470,10 +10506,14 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H123" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-TUOJIAO-001_MASTER</t>
+        </is>
+      </c>
       <c r="I123" s="3" t="inlineStr">
         <is>
           <t>报告直接给出山面4根</t>
@@ -10531,10 +10571,14 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H124" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-TUOJIAO-001_MASTER</t>
+        </is>
+      </c>
       <c r="I124" s="3" t="inlineStr">
         <is>
           <t>报告直接给出山面4根</t>
@@ -10592,10 +10636,14 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H125" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-TUOJIAO-001_MASTER</t>
+        </is>
+      </c>
       <c r="I125" s="3" t="inlineStr">
         <is>
           <t>报告直接给出山面4根</t>
@@ -10653,10 +10701,14 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H126" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-TUOJIAO-001_MASTER</t>
+        </is>
+      </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
           <t>报告直接给出山面4根</t>
@@ -35723,7 +35775,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -35776,7 +35828,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -35786,7 +35838,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -35797,7 +35849,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>46.4%</t>
         </is>
       </c>
     </row>
@@ -35809,7 +35861,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>9647e028f168c449fa86a2929181a577161faf4e</t>
+          <t>6dfc7d9ed0846e8806ae1a17e6767884621c4bba</t>
         </is>
       </c>
     </row>
@@ -35821,7 +35873,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>392419f5291b008e84320f9b4c31cebc8236ef77e2a676bbf5e32e8ba79d9b16</t>
+          <t>8ac7078363346136359fdd876333b36fe650cf2230b1f29490e32c709b831141</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.464</v>
+        <v>0.5</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -1175,12 +1175,16 @@
           <t>需新建Master</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr"/>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-CHASHOU-001_MASTER</t>
+        </is>
+      </c>
       <c r="E33" s="3" t="n">
         <v>8</v>
       </c>
@@ -10766,10 +10770,14 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H127" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-CHASHOU-001_MASTER</t>
+        </is>
+      </c>
       <c r="I127" s="3" t="inlineStr">
         <is>
           <t>总数8+每榀一对构造关系</t>
@@ -10827,10 +10835,14 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H128" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-CHASHOU-001_MASTER</t>
+        </is>
+      </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
           <t>总数8+每榀一对构造关系</t>
@@ -10888,10 +10900,14 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H129" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-CHASHOU-001_MASTER</t>
+        </is>
+      </c>
       <c r="I129" s="3" t="inlineStr">
         <is>
           <t>总数8+每榀一对构造关系</t>
@@ -10949,10 +10965,14 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H130" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-CHASHOU-001_MASTER</t>
+        </is>
+      </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
           <t>总数8+每榀一对构造关系</t>
@@ -11010,10 +11030,14 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H131" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-CHASHOU-001_MASTER</t>
+        </is>
+      </c>
       <c r="I131" s="3" t="inlineStr">
         <is>
           <t>总数8+每榀一对构造关系</t>
@@ -11071,10 +11095,14 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H132" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-CHASHOU-001_MASTER</t>
+        </is>
+      </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
           <t>总数8+每榀一对构造关系</t>
@@ -11132,10 +11160,14 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H133" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-CHASHOU-001_MASTER</t>
+        </is>
+      </c>
       <c r="I133" s="3" t="inlineStr">
         <is>
           <t>总数8+每榀一对构造关系</t>
@@ -11193,10 +11225,14 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H134" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-CHASHOU-001_MASTER</t>
+        </is>
+      </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
           <t>总数8+每榀一对构造关系</t>
@@ -35828,7 +35864,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -35838,7 +35874,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -35849,7 +35885,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -35861,7 +35897,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>6dfc7d9ed0846e8806ae1a17e6767884621c4bba</t>
+          <t>5bcf61933aff9f14fe5f2f7f3c7f6b6d76861567</t>
         </is>
       </c>
     </row>
@@ -35873,7 +35909,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>8ac7078363346136359fdd876333b36fe650cf2230b1f29490e32c709b831141</t>
+          <t>b8a062c0d95c0424e561f591eb587cfa9a3b83c6c0af7c25eb51f2e058060114</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -35885,7 +35885,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
@@ -35897,7 +35897,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>5bcf61933aff9f14fe5f2f7f3c7f6b6d76861567</t>
+          <t>db857ff6c47b03ebe153433e59a4f6093b3028d6</t>
         </is>
       </c>
     </row>
@@ -35909,7 +35909,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>b8a062c0d95c0424e561f591eb587cfa9a3b83c6c0af7c25eb51f2e058060114</t>
+          <t>0abf02da338c90fa37185cb4bbf439121c4a1f0d4ebce1b461cc203e4e38d021</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.5</v>
+        <v>0.536</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -1959,12 +1959,16 @@
           <t>需新建Master</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr"/>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-SHUZHU-001_MASTER</t>
+        </is>
+      </c>
       <c r="E69" s="3" t="n">
         <v>4</v>
       </c>
@@ -11290,10 +11294,14 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H135" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-SHUZHU-001_MASTER</t>
+        </is>
+      </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
           <t>附件1-7实测位置+木结构测绘图闭合</t>
@@ -11351,10 +11359,14 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H136" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-SHUZHU-001_MASTER</t>
+        </is>
+      </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
           <t>附件1-7实测位置+木结构测绘图闭合</t>
@@ -11412,10 +11424,14 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H137" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-SHUZHU-001_MASTER</t>
+        </is>
+      </c>
       <c r="I137" s="3" t="inlineStr">
         <is>
           <t>附件1-7实测位置+木结构测绘图闭合</t>
@@ -11473,10 +11489,14 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H138" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-SHUZHU-001_MASTER</t>
+        </is>
+      </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
           <t>附件1-7实测位置+木结构测绘图闭合</t>
@@ -35864,7 +35884,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -35874,7 +35894,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -35885,7 +35905,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>53.6%</t>
         </is>
       </c>
     </row>
@@ -35897,7 +35917,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>db857ff6c47b03ebe153433e59a4f6093b3028d6</t>
+          <t>71bb1fef2d203dec87bab830f6a9a4e190407ef9</t>
         </is>
       </c>
     </row>
@@ -35909,7 +35929,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>0abf02da338c90fa37185cb4bbf439121c4a1f0d4ebce1b461cc203e4e38d021</t>
+          <t>86ed06874fd3e480698898f1d687f152c6270c94401ad8f6468b02d54e2121d5</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -35917,7 +35917,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>71bb1fef2d203dec87bab830f6a9a4e190407ef9</t>
+          <t>06cd63cc0baff6e1e96e7ea3f3c0583c32ec7bfc</t>
         </is>
       </c>
     </row>
@@ -35929,7 +35929,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>86ed06874fd3e480698898f1d687f152c6270c94401ad8f6468b02d54e2121d5</t>
+          <t>0f83d1b8143ac838bec86c0bbcaa21c6676ce2751975db561799c3154ac26e42</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.536</v>
+        <v>0.5710000000000001</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -1372,12 +1372,16 @@
           <t>需新建Master</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr"/>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-DAJIAOLIANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="E42" s="3" t="n">
         <v>4</v>
       </c>
@@ -9262,10 +9266,14 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H103" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-DAJIAOLIANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I103" s="3" t="inlineStr">
         <is>
           <t>直接实测/报告明确缺口</t>
@@ -9323,10 +9331,14 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H104" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-DAJIAOLIANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
           <t>直接实测/报告明确缺口</t>
@@ -9384,10 +9396,14 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H105" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-DAJIAOLIANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
           <t>直接实测/报告明确缺口</t>
@@ -9445,10 +9461,14 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H106" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-DAJIAOLIANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
           <t>直接实测/报告明确缺口</t>
@@ -35884,7 +35904,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -35894,7 +35914,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -35905,7 +35925,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -35917,7 +35937,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>06cd63cc0baff6e1e96e7ea3f3c0583c32ec7bfc</t>
+          <t>8d6b84659ef6f2827deb1f5306d6bf69191884db</t>
         </is>
       </c>
     </row>
@@ -35929,7 +35949,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>0f83d1b8143ac838bec86c0bbcaa21c6676ce2751975db561799c3154ac26e42</t>
+          <t>be66dd40db10ee19e55cd6faa37e97eceba324ef622a05f8d599c2f6be66b1f0</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -35937,7 +35937,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>8d6b84659ef6f2827deb1f5306d6bf69191884db</t>
+          <t>e0cfab82f2666d4667f568a8fec2a92ad6d61464</t>
         </is>
       </c>
     </row>
@@ -35949,7 +35949,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>be66dd40db10ee19e55cd6faa37e97eceba324ef622a05f8d599c2f6be66b1f0</t>
+          <t>f589dc7c389c36fc74bb63c6863dedf11a07f2a2c850ec4bb7fd689b56422f30</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.5710000000000001</v>
+        <v>0.607</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -1418,12 +1418,16 @@
           <t>需新建Master</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr"/>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-ZIJIAOLIANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="E44" s="3" t="n">
         <v>4</v>
       </c>
@@ -9526,10 +9530,14 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H107" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-ZIJIAOLIANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
           <t>直接实测/报告明确缺口</t>
@@ -9587,10 +9595,14 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H108" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-ZIJIAOLIANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
           <t>直接实测/报告明确缺口</t>
@@ -9648,10 +9660,14 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H109" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-ZIJIAOLIANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
           <t>直接实测/报告明确缺口</t>
@@ -9709,10 +9725,14 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H110" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-ZIJIAOLIANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I110" s="3" t="inlineStr">
         <is>
           <t>直接实测/报告明确缺口</t>
@@ -35904,7 +35924,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -35914,7 +35934,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -35925,7 +35945,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>60.7%</t>
         </is>
       </c>
     </row>
@@ -35937,7 +35957,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>e0cfab82f2666d4667f568a8fec2a92ad6d61464</t>
+          <t>ab86be0b03d6fd654364e617cdcd1ccc0b917121</t>
         </is>
       </c>
     </row>
@@ -35949,7 +35969,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>f589dc7c389c36fc74bb63c6863dedf11a07f2a2c850ec4bb7fd689b56422f30</t>
+          <t>c3a2c8e0b3d56388f1e26727444d9ed1ffecc3cb92bffd125ead196a5080a2e0</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.607</v>
+        <v>0.643</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -2181,12 +2181,16 @@
           <t>需新建Master</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr"/>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-LANE-001_MASTER</t>
+        </is>
+      </c>
       <c r="E79" s="3" t="n">
         <v>12</v>
       </c>
@@ -8246,10 +8250,14 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H87" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-LANE-001_MASTER</t>
+        </is>
+      </c>
       <c r="I87" s="3" t="inlineStr">
         <is>
           <t>分布规则直接说明+三间拓扑</t>
@@ -8311,10 +8319,14 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-LANE-001_MASTER</t>
+        </is>
+      </c>
       <c r="I88" s="3" t="inlineStr">
         <is>
           <t>分布规则直接说明+三间拓扑</t>
@@ -8376,10 +8388,14 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-LANE-001_MASTER</t>
+        </is>
+      </c>
       <c r="I89" s="3" t="inlineStr">
         <is>
           <t>分布规则直接说明+三间拓扑</t>
@@ -8441,10 +8457,14 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H90" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-LANE-001_MASTER</t>
+        </is>
+      </c>
       <c r="I90" s="3" t="inlineStr">
         <is>
           <t>分布规则直接说明+三间拓扑</t>
@@ -8506,10 +8526,14 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H91" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-LANE-001_MASTER</t>
+        </is>
+      </c>
       <c r="I91" s="3" t="inlineStr">
         <is>
           <t>分布规则直接说明+三间拓扑</t>
@@ -8571,10 +8595,14 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H92" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-LANE-001_MASTER</t>
+        </is>
+      </c>
       <c r="I92" s="3" t="inlineStr">
         <is>
           <t>分布规则直接说明+三间拓扑</t>
@@ -8636,10 +8664,14 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H93" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-LANE-001_MASTER</t>
+        </is>
+      </c>
       <c r="I93" s="3" t="inlineStr">
         <is>
           <t>分布规则直接说明+三间拓扑</t>
@@ -8701,10 +8733,14 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H94" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-LANE-001_MASTER</t>
+        </is>
+      </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
           <t>分布规则直接说明+三间拓扑</t>
@@ -8766,10 +8802,14 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H95" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-LANE-001_MASTER</t>
+        </is>
+      </c>
       <c r="I95" s="3" t="inlineStr">
         <is>
           <t>分布规则直接说明+三间拓扑</t>
@@ -8831,10 +8871,14 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H96" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-LANE-001_MASTER</t>
+        </is>
+      </c>
       <c r="I96" s="3" t="inlineStr">
         <is>
           <t>分布规则直接说明+三间拓扑</t>
@@ -8896,10 +8940,14 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H97" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-LANE-001_MASTER</t>
+        </is>
+      </c>
       <c r="I97" s="3" t="inlineStr">
         <is>
           <t>分布规则直接说明+三间拓扑</t>
@@ -8961,10 +9009,14 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H98" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-LANE-001_MASTER</t>
+        </is>
+      </c>
       <c r="I98" s="3" t="inlineStr">
         <is>
           <t>分布规则直接说明+三间拓扑</t>
@@ -35924,7 +35976,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11">
@@ -35934,7 +35986,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -35945,7 +35997,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -35957,7 +36009,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>ab86be0b03d6fd654364e617cdcd1ccc0b917121</t>
+          <t>da149c9e852bc8f8eaed9063b6d9f84413726b78</t>
         </is>
       </c>
     </row>
@@ -35969,7 +36021,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>c3a2c8e0b3d56388f1e26727444d9ed1ffecc3cb92bffd125ead196a5080a2e0</t>
+          <t>7825f5e615ba1d7e2fa03246e3df2869b417d28d6bfadf380fee5ff163e0087d</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -36009,7 +36009,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>da149c9e852bc8f8eaed9063b6d9f84413726b78</t>
+          <t>563888e2338d051173de060f82e7a421d7b217f9</t>
         </is>
       </c>
     </row>
@@ -36021,7 +36021,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>7825f5e615ba1d7e2fa03246e3df2869b417d28d6bfadf380fee5ff163e0087d</t>
+          <t>27083f939d523e1b750dbc1be759cf44da4ca8177a65a0e208a7aeb9b6a2a926</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.643</v>
+        <v>0.679</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -1904,12 +1904,16 @@
           <t>需新建Master</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr"/>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-YOUE-001_MASTER</t>
+        </is>
+      </c>
       <c r="E66" s="3" t="n">
         <v>4</v>
       </c>
@@ -9078,10 +9082,14 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H99" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-YOUE-001_MASTER</t>
+        </is>
+      </c>
       <c r="I99" s="3" t="inlineStr">
         <is>
           <t>报告直接说明分布</t>
@@ -9139,10 +9147,14 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-YOUE-001_MASTER</t>
+        </is>
+      </c>
       <c r="I100" s="3" t="inlineStr">
         <is>
           <t>报告直接说明分布</t>
@@ -9200,10 +9212,14 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H101" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-YOUE-001_MASTER</t>
+        </is>
+      </c>
       <c r="I101" s="3" t="inlineStr">
         <is>
           <t>报告直接说明分布</t>
@@ -9261,10 +9277,14 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H102" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-YOUE-001_MASTER</t>
+        </is>
+      </c>
       <c r="I102" s="3" t="inlineStr">
         <is>
           <t>报告直接说明分布</t>
@@ -35976,7 +35996,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -35986,7 +36006,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -35997,7 +36017,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>67.9%</t>
         </is>
       </c>
     </row>
@@ -36009,7 +36029,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>563888e2338d051173de060f82e7a421d7b217f9</t>
+          <t>73bf16089b2a06fc84367b34940974cc374b3eb8</t>
         </is>
       </c>
     </row>
@@ -36021,7 +36041,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>27083f939d523e1b750dbc1be759cf44da4ca8177a65a0e208a7aeb9b6a2a926</t>
+          <t>c5bfe5c3407539d2e646c99427e7b492bdca1a76d0f8b455006524cabf2a6be6</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -36029,7 +36029,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>73bf16089b2a06fc84367b34940974cc374b3eb8</t>
+          <t>e8b1c63171b0f4982a2917d34b23398d240d8e3c</t>
         </is>
       </c>
     </row>
@@ -36041,7 +36041,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>c5bfe5c3407539d2e646c99427e7b492bdca1a76d0f8b455006524cabf2a6be6</t>
+          <t>b886996d303db3d0d337eaa57bed7d28d4d55ab2942273581531192bc51c0108</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -36029,7 +36029,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>e8b1c63171b0f4982a2917d34b23398d240d8e3c</t>
+          <t>c526e8caea7aa96e70b68e6fdadc3ba2d6895ee5</t>
         </is>
       </c>
     </row>
@@ -36041,7 +36041,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>b886996d303db3d0d337eaa57bed7d28d4d55ab2942273581531192bc51c0108</t>
+          <t>6d5798777a85bd1b2c90b3b02999f0f9803e5f4c58c7f05793b2bbc8d63f7681</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.679</v>
+        <v>0.7140000000000001</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -2017,12 +2017,16 @@
           <t>需新建Master</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr"/>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>CMP-DOU-BOTTOM-LONGKAI-001_MASTER</t>
+        </is>
+      </c>
       <c r="E71" s="3" t="n">
         <v>12</v>
       </c>
@@ -15618,10 +15622,14 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H203" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H203" s="3" t="inlineStr">
+        <is>
+          <t>CMP-DOU-BOTTOM-LONGKAI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I203" s="3" t="inlineStr">
         <is>
           <t>报告直接称12组</t>
@@ -15679,10 +15687,14 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H204" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H204" s="3" t="inlineStr">
+        <is>
+          <t>CMP-DOU-BOTTOM-LONGKAI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I204" s="3" t="inlineStr">
         <is>
           <t>报告直接称12组</t>
@@ -15740,10 +15752,14 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H205" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H205" s="3" t="inlineStr">
+        <is>
+          <t>CMP-DOU-BOTTOM-LONGKAI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I205" s="3" t="inlineStr">
         <is>
           <t>报告直接称12组</t>
@@ -15801,10 +15817,14 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H206" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H206" s="3" t="inlineStr">
+        <is>
+          <t>CMP-DOU-BOTTOM-LONGKAI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I206" s="3" t="inlineStr">
         <is>
           <t>报告直接称12组</t>
@@ -15862,10 +15882,14 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H207" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H207" s="3" t="inlineStr">
+        <is>
+          <t>CMP-DOU-BOTTOM-LONGKAI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I207" s="3" t="inlineStr">
         <is>
           <t>报告直接称12组</t>
@@ -15923,10 +15947,14 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H208" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H208" s="3" t="inlineStr">
+        <is>
+          <t>CMP-DOU-BOTTOM-LONGKAI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I208" s="3" t="inlineStr">
         <is>
           <t>报告直接称12组</t>
@@ -15984,10 +16012,14 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H209" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H209" s="3" t="inlineStr">
+        <is>
+          <t>CMP-DOU-BOTTOM-LONGKAI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I209" s="3" t="inlineStr">
         <is>
           <t>报告直接称12组</t>
@@ -16045,10 +16077,14 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H210" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H210" s="3" t="inlineStr">
+        <is>
+          <t>CMP-DOU-BOTTOM-LONGKAI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I210" s="3" t="inlineStr">
         <is>
           <t>报告直接称12组</t>
@@ -16106,10 +16142,14 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H211" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H211" s="3" t="inlineStr">
+        <is>
+          <t>CMP-DOU-BOTTOM-LONGKAI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I211" s="3" t="inlineStr">
         <is>
           <t>报告直接称12组</t>
@@ -16167,10 +16207,14 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H212" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H212" s="3" t="inlineStr">
+        <is>
+          <t>CMP-DOU-BOTTOM-LONGKAI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I212" s="3" t="inlineStr">
         <is>
           <t>报告直接称12组</t>
@@ -16228,10 +16272,14 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H213" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H213" s="3" t="inlineStr">
+        <is>
+          <t>CMP-DOU-BOTTOM-LONGKAI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I213" s="3" t="inlineStr">
         <is>
           <t>报告直接称12组</t>
@@ -16289,10 +16337,14 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H214" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H214" s="3" t="inlineStr">
+        <is>
+          <t>CMP-DOU-BOTTOM-LONGKAI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I214" s="3" t="inlineStr">
         <is>
           <t>报告直接称12组</t>
@@ -35996,7 +36048,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -36006,7 +36058,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -36017,7 +36069,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -36029,7 +36081,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>c526e8caea7aa96e70b68e6fdadc3ba2d6895ee5</t>
+          <t>d122aff5db6d6fc43cdf9017533f03981c374182</t>
         </is>
       </c>
     </row>
@@ -36041,7 +36093,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>6d5798777a85bd1b2c90b3b02999f0f9803e5f4c58c7f05793b2bbc8d63f7681</t>
+          <t>1aefcdcfed83447da79b1265ade15970a4b30d7005b027a78992a644aff35b2e</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -36081,7 +36081,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>d122aff5db6d6fc43cdf9017533f03981c374182</t>
+          <t>d2147e2f1dfbf9a122fcb56a73b8f9c385dd7394</t>
         </is>
       </c>
     </row>
@@ -36093,7 +36093,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>1aefcdcfed83447da79b1265ade15970a4b30d7005b027a78992a644aff35b2e</t>
+          <t>3898ed51bf5715ec5fc97e6fd250df6f7c70bbbecd547f9d5341c4ae3e23e864</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -1351,12 +1351,16 @@
           <t>需新建Master</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr"/>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="E41" s="3" t="n">
         <v>16</v>
       </c>
@@ -1527,12 +1531,16 @@
           <t>需新建Master</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr"/>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="E49" s="3" t="n">
         <v>28</v>
       </c>
@@ -19881,10 +19889,14 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H272" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H272" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I272" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -20007,10 +20019,14 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H274" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H274" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I274" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -20318,10 +20334,14 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H279" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H279" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I279" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -20507,10 +20527,14 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H282" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H282" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I282" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -20633,10 +20657,14 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H284" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H284" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I284" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -20944,10 +20972,14 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H289" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H289" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I289" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -21133,10 +21165,14 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H292" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H292" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I292" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -21259,10 +21295,14 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H294" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H294" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I294" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -21570,10 +21610,14 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H299" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H299" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I299" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -21759,10 +21803,14 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H302" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H302" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I302" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -21885,10 +21933,14 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H304" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H304" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I304" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -22196,10 +22248,14 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H309" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H309" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I309" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -22322,10 +22378,14 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H311" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H311" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I311" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -22633,10 +22693,14 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H316" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H316" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I316" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -22822,10 +22886,14 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H319" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H319" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I319" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -22948,10 +23016,14 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H321" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H321" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I321" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -23259,10 +23331,14 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H326" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H326" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I326" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -23448,10 +23524,14 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H329" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H329" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I329" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -23574,10 +23654,14 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H331" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H331" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I331" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -23885,10 +23969,14 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H336" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H336" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I336" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -24074,10 +24162,14 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H339" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H339" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I339" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -24200,10 +24292,14 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H341" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H341" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I341" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -24511,10 +24607,14 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H346" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H346" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I346" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -24637,10 +24737,14 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H348" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H348" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I348" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -24948,10 +25052,14 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H353" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H353" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I353" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -25137,10 +25245,14 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H356" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H356" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I356" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -25263,10 +25375,14 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H358" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H358" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I358" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -25574,10 +25690,14 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H363" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H363" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I363" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -25763,10 +25883,14 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H366" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H366" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I366" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -25889,10 +26013,14 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H368" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H368" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I368" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -26200,10 +26328,14 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H373" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H373" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I373" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -26389,10 +26521,14 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H376" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H376" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I376" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -26515,10 +26651,14 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H378" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H378" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I378" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -26826,10 +26966,14 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H383" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H383" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I383" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -26952,10 +27096,14 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H385" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H385" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I385" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -27263,10 +27411,14 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H390" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H390" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I390" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -27452,10 +27604,14 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H393" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H393" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I393" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -27578,10 +27734,14 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H395" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H395" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I395" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -27889,10 +28049,14 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H400" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H400" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I400" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -28078,10 +28242,14 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H403" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H403" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I403" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -28204,10 +28372,14 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H405" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H405" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I405" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -28515,10 +28687,14 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H410" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H410" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I410" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -28704,10 +28880,14 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H413" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H413" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I413" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -28830,10 +29010,14 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H415" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H415" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="I415" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -36081,7 +36265,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>d2147e2f1dfbf9a122fcb56a73b8f9c385dd7394</t>
+          <t>7b69c7a60ed684584147141e73695eea519bae6d</t>
         </is>
       </c>
     </row>
@@ -36093,7 +36277,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>3898ed51bf5715ec5fc97e6fd250df6f7c70bbbecd547f9d5341c4ae3e23e864</t>
+          <t>e21afcc9d176b71fc68e112077930106e28ea542ba3fe57104393ad580add394</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.7140000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -36232,7 +36232,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
@@ -36242,7 +36242,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -36253,7 +36253,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75%</t>
         </is>
       </c>
     </row>
@@ -36265,7 +36265,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>7b69c7a60ed684584147141e73695eea519bae6d</t>
+          <t>7b4c0519601dbcb2c090b455c4f157ea5595a292</t>
         </is>
       </c>
     </row>
@@ -36277,7 +36277,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>e21afcc9d176b71fc68e112077930106e28ea542ba3fe57104393ad580add394</t>
+          <t>21a6abfbbed28110fdea81a0c157e0c57bd06b014d0826f899769facd2f9ce15</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.75</v>
+        <v>0.7859999999999999</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>203</v>
+        <v>247</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -1330,12 +1330,16 @@
           <t>需新建Master</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr"/>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="E40" s="3" t="n">
         <v>16</v>
       </c>
@@ -1510,12 +1514,16 @@
           <t>需新建Master</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr"/>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="E48" s="3" t="n">
         <v>28</v>
       </c>
@@ -19956,10 +19964,14 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H273" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H273" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I273" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -20086,10 +20098,14 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H275" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H275" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I275" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -20401,10 +20417,14 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H280" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H280" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I280" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -20594,10 +20614,14 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H283" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H283" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I283" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -20724,10 +20748,14 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H285" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H285" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I285" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -21039,10 +21067,14 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H290" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H290" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I290" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -21232,10 +21264,14 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H293" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H293" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I293" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -21362,10 +21398,14 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H295" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H295" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I295" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -21677,10 +21717,14 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H300" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H300" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I300" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -21870,10 +21914,14 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H303" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H303" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I303" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -22000,10 +22048,14 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H305" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H305" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I305" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -22315,10 +22367,14 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H310" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H310" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I310" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -22445,10 +22501,14 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H312" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H312" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I312" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -22760,10 +22820,14 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H317" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H317" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I317" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -22953,10 +23017,14 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H320" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H320" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I320" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -23083,10 +23151,14 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H322" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H322" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I322" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -23398,10 +23470,14 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H327" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H327" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I327" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -23591,10 +23667,14 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H330" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H330" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I330" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -23721,10 +23801,14 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H332" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H332" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I332" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -24036,10 +24120,14 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H337" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H337" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I337" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -24229,10 +24317,14 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H340" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H340" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I340" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -24359,10 +24451,14 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H342" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H342" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I342" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -24674,10 +24770,14 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H347" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H347" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I347" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -24804,10 +24904,14 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H349" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H349" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I349" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -25119,10 +25223,14 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H354" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H354" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I354" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -25312,10 +25420,14 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H357" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H357" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I357" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -25442,10 +25554,14 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H359" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H359" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I359" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -25757,10 +25873,14 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H364" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H364" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I364" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -25950,10 +26070,14 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H367" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H367" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I367" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -26080,10 +26204,14 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H369" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H369" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I369" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -26395,10 +26523,14 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H374" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H374" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I374" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -26588,10 +26720,14 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H377" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H377" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I377" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -26718,10 +26854,14 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H379" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H379" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I379" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -27033,10 +27173,14 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H384" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H384" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I384" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -27163,10 +27307,14 @@
       </c>
       <c r="G386" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H386" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H386" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I386" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -27478,10 +27626,14 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H391" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H391" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I391" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -27671,10 +27823,14 @@
       </c>
       <c r="G394" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H394" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H394" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I394" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -27801,10 +27957,14 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H396" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H396" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I396" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -28116,10 +28276,14 @@
       </c>
       <c r="G401" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H401" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H401" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I401" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -28309,10 +28473,14 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H404" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H404" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I404" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -28439,10 +28607,14 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H406" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H406" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I406" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -28754,10 +28926,14 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H411" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H411" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I411" s="3" t="inlineStr">
         <is>
           <t>小型总28中的补间泥道12</t>
@@ -28947,10 +29123,14 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H414" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H414" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I414" s="3" t="inlineStr">
         <is>
           <t>大型实测16+柱头类16方向单元</t>
@@ -29077,10 +29257,14 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H416" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H416" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I416" s="3" t="inlineStr">
         <is>
           <t>小型总28中的柱头类二跳16</t>
@@ -36232,7 +36416,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -36242,7 +36426,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -36253,7 +36437,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>78.6%</t>
         </is>
       </c>
     </row>
@@ -36265,7 +36449,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>7b4c0519601dbcb2c090b455c4f157ea5595a292</t>
+          <t>17d9369230226d407d3e7e0fdc45cc372054f5da</t>
         </is>
       </c>
     </row>
@@ -36277,7 +36461,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>21a6abfbbed28110fdea81a0c157e0c57bd06b014d0826f899769facd2f9ce15</t>
+          <t>35ddcd9189a23a1eac8a9bf3986411cdc97e3f842d6df216d75603cfc8b3f157</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -36449,7 +36449,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>17d9369230226d407d3e7e0fdc45cc372054f5da</t>
+          <t>749abaeefa7892009a26071c5236cbc4a131f223</t>
         </is>
       </c>
     </row>
@@ -36461,7 +36461,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>35ddcd9189a23a1eac8a9bf3986411cdc97e3f842d6df216d75603cfc8b3f157</t>
+          <t>1e0ad71c6d1810058e8d0c76ac02662974651372e588843ac305590da2e90f67</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.7859999999999999</v>
+        <v>0.821</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>247</v>
+        <v>275</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -957,12 +957,16 @@
           <t>需新建Master</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr"/>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="E23" s="3" t="n">
         <v>28</v>
       </c>
@@ -19834,10 +19838,14 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H271" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H271" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I271" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -20287,10 +20295,14 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H278" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H278" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I278" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -20484,10 +20496,14 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H281" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H281" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I281" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -20937,10 +20953,14 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H288" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H288" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I288" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -21134,10 +21154,14 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H291" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H291" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I291" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -21587,10 +21611,14 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H298" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H298" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I298" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -21784,10 +21812,14 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H301" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H301" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I301" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -22237,10 +22269,14 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H308" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H308" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I308" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -22690,10 +22726,14 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H315" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H315" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I315" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -22887,10 +22927,14 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H318" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H318" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I318" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -23340,10 +23384,14 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H325" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H325" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I325" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -23537,10 +23585,14 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H328" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H328" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I328" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -23990,10 +24042,14 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H335" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H335" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I335" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -24187,10 +24243,14 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H338" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H338" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I338" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -24640,10 +24700,14 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H345" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H345" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I345" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -25093,10 +25157,14 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H352" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H352" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I352" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -25290,10 +25358,14 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H355" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H355" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I355" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -25743,10 +25815,14 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H362" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H362" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I362" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -25940,10 +26016,14 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H365" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H365" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I365" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -26393,10 +26473,14 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H372" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H372" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I372" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -26590,10 +26674,14 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H375" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H375" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I375" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -27043,10 +27131,14 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H382" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H382" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I382" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -27496,10 +27588,14 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H389" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H389" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I389" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -27693,10 +27789,14 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H392" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H392" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I392" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -28146,10 +28246,14 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H399" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H399" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I399" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -28343,10 +28447,14 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H402" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H402" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I402" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -28796,10 +28904,14 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H409" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H409" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I409" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -28993,10 +29105,14 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H412" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H412" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-LINGGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I412" s="3" t="inlineStr">
         <is>
           <t>实测28组+方向单元闭合</t>
@@ -36416,7 +36532,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11">
@@ -36426,7 +36542,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -36437,7 +36553,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>82.1%</t>
         </is>
       </c>
     </row>
@@ -36449,7 +36565,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>749abaeefa7892009a26071c5236cbc4a131f223</t>
+          <t>119dc2ae9b18a536cefb02360fa84fafe66016a7</t>
         </is>
       </c>
     </row>
@@ -36461,7 +36577,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>1e0ad71c6d1810058e8d0c76ac02662974651372e588843ac305590da2e90f67</t>
+          <t>9f54bfb8ae79eaf63670d9732aa20efd6a03990ad234093487a52cbe09a3ab0c</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -36565,7 +36565,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>119dc2ae9b18a536cefb02360fa84fafe66016a7</t>
+          <t>47d945e6fa5dc495d569b88a46f7a61a57539e80</t>
         </is>
       </c>
     </row>
@@ -36577,7 +36577,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>9f54bfb8ae79eaf63670d9732aa20efd6a03990ad234093487a52cbe09a3ab0c</t>
+          <t>c10083efe039f378967b13a9b84944c6dcc336dc02a7ccc9acf4379966acf8d3</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.821</v>
+        <v>0.857</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>275</v>
+        <v>331</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -1070,12 +1070,16 @@
           <t>需新建Master</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr"/>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="E28" s="3" t="n">
         <v>56</v>
       </c>
@@ -16422,10 +16426,14 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H215" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H215" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I215" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -16448,7 +16456,11 @@
       </c>
       <c r="U215" s="3" t="inlineStr"/>
       <c r="V215" s="3" t="inlineStr"/>
-      <c r="W215" s="3" t="inlineStr"/>
+      <c r="W215" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="3" t="inlineStr">
@@ -16483,10 +16495,14 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H216" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H216" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I216" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -16509,7 +16525,11 @@
       </c>
       <c r="U216" s="3" t="inlineStr"/>
       <c r="V216" s="3" t="inlineStr"/>
-      <c r="W216" s="3" t="inlineStr"/>
+      <c r="W216" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="3" t="inlineStr">
@@ -16544,10 +16564,14 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H217" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H217" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I217" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -16570,7 +16594,11 @@
       </c>
       <c r="U217" s="3" t="inlineStr"/>
       <c r="V217" s="3" t="inlineStr"/>
-      <c r="W217" s="3" t="inlineStr"/>
+      <c r="W217" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="3" t="inlineStr">
@@ -16605,10 +16633,14 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H218" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H218" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I218" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -16631,7 +16663,11 @@
       </c>
       <c r="U218" s="3" t="inlineStr"/>
       <c r="V218" s="3" t="inlineStr"/>
-      <c r="W218" s="3" t="inlineStr"/>
+      <c r="W218" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="3" t="inlineStr">
@@ -16666,10 +16702,14 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H219" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H219" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I219" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -16692,7 +16732,11 @@
       </c>
       <c r="U219" s="3" t="inlineStr"/>
       <c r="V219" s="3" t="inlineStr"/>
-      <c r="W219" s="3" t="inlineStr"/>
+      <c r="W219" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="3" t="inlineStr">
@@ -16727,10 +16771,14 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H220" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H220" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I220" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -16753,7 +16801,11 @@
       </c>
       <c r="U220" s="3" t="inlineStr"/>
       <c r="V220" s="3" t="inlineStr"/>
-      <c r="W220" s="3" t="inlineStr"/>
+      <c r="W220" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="3" t="inlineStr">
@@ -16788,10 +16840,14 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H221" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H221" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I221" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -16814,7 +16870,11 @@
       </c>
       <c r="U221" s="3" t="inlineStr"/>
       <c r="V221" s="3" t="inlineStr"/>
-      <c r="W221" s="3" t="inlineStr"/>
+      <c r="W221" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
@@ -16849,10 +16909,14 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H222" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H222" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I222" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -16875,7 +16939,11 @@
       </c>
       <c r="U222" s="3" t="inlineStr"/>
       <c r="V222" s="3" t="inlineStr"/>
-      <c r="W222" s="3" t="inlineStr"/>
+      <c r="W222" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
@@ -16910,10 +16978,14 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H223" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H223" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I223" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -16936,7 +17008,11 @@
       </c>
       <c r="U223" s="3" t="inlineStr"/>
       <c r="V223" s="3" t="inlineStr"/>
-      <c r="W223" s="3" t="inlineStr"/>
+      <c r="W223" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="3" t="inlineStr">
@@ -16971,10 +17047,14 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H224" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H224" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I224" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -16997,7 +17077,11 @@
       </c>
       <c r="U224" s="3" t="inlineStr"/>
       <c r="V224" s="3" t="inlineStr"/>
-      <c r="W224" s="3" t="inlineStr"/>
+      <c r="W224" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="3" t="inlineStr">
@@ -17032,10 +17116,14 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H225" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H225" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I225" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -17058,7 +17146,11 @@
       </c>
       <c r="U225" s="3" t="inlineStr"/>
       <c r="V225" s="3" t="inlineStr"/>
-      <c r="W225" s="3" t="inlineStr"/>
+      <c r="W225" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="3" t="inlineStr">
@@ -17093,10 +17185,14 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H226" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H226" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I226" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -17119,7 +17215,11 @@
       </c>
       <c r="U226" s="3" t="inlineStr"/>
       <c r="V226" s="3" t="inlineStr"/>
-      <c r="W226" s="3" t="inlineStr"/>
+      <c r="W226" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="3" t="inlineStr">
@@ -17154,10 +17254,14 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H227" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H227" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I227" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -17180,7 +17284,11 @@
       </c>
       <c r="U227" s="3" t="inlineStr"/>
       <c r="V227" s="3" t="inlineStr"/>
-      <c r="W227" s="3" t="inlineStr"/>
+      <c r="W227" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="3" t="inlineStr">
@@ -17215,10 +17323,14 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H228" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H228" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I228" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -17241,7 +17353,11 @@
       </c>
       <c r="U228" s="3" t="inlineStr"/>
       <c r="V228" s="3" t="inlineStr"/>
-      <c r="W228" s="3" t="inlineStr"/>
+      <c r="W228" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
@@ -17276,10 +17392,14 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H229" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H229" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I229" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -17302,7 +17422,11 @@
       </c>
       <c r="U229" s="3" t="inlineStr"/>
       <c r="V229" s="3" t="inlineStr"/>
-      <c r="W229" s="3" t="inlineStr"/>
+      <c r="W229" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="3" t="inlineStr">
@@ -17337,10 +17461,14 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H230" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H230" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I230" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -17363,7 +17491,11 @@
       </c>
       <c r="U230" s="3" t="inlineStr"/>
       <c r="V230" s="3" t="inlineStr"/>
-      <c r="W230" s="3" t="inlineStr"/>
+      <c r="W230" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
@@ -17398,10 +17530,14 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H231" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H231" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I231" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -17424,7 +17560,11 @@
       </c>
       <c r="U231" s="3" t="inlineStr"/>
       <c r="V231" s="3" t="inlineStr"/>
-      <c r="W231" s="3" t="inlineStr"/>
+      <c r="W231" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="3" t="inlineStr">
@@ -17459,10 +17599,14 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H232" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H232" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I232" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -17485,7 +17629,11 @@
       </c>
       <c r="U232" s="3" t="inlineStr"/>
       <c r="V232" s="3" t="inlineStr"/>
-      <c r="W232" s="3" t="inlineStr"/>
+      <c r="W232" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="3" t="inlineStr">
@@ -17520,10 +17668,14 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H233" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H233" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I233" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -17546,7 +17698,11 @@
       </c>
       <c r="U233" s="3" t="inlineStr"/>
       <c r="V233" s="3" t="inlineStr"/>
-      <c r="W233" s="3" t="inlineStr"/>
+      <c r="W233" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="3" t="inlineStr">
@@ -17581,10 +17737,14 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H234" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H234" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I234" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -17607,7 +17767,11 @@
       </c>
       <c r="U234" s="3" t="inlineStr"/>
       <c r="V234" s="3" t="inlineStr"/>
-      <c r="W234" s="3" t="inlineStr"/>
+      <c r="W234" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
@@ -17642,10 +17806,14 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H235" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H235" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I235" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -17668,7 +17836,11 @@
       </c>
       <c r="U235" s="3" t="inlineStr"/>
       <c r="V235" s="3" t="inlineStr"/>
-      <c r="W235" s="3" t="inlineStr"/>
+      <c r="W235" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
@@ -17703,10 +17875,14 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H236" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H236" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I236" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -17729,7 +17905,11 @@
       </c>
       <c r="U236" s="3" t="inlineStr"/>
       <c r="V236" s="3" t="inlineStr"/>
-      <c r="W236" s="3" t="inlineStr"/>
+      <c r="W236" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
@@ -17764,10 +17944,14 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H237" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H237" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I237" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -17790,7 +17974,11 @@
       </c>
       <c r="U237" s="3" t="inlineStr"/>
       <c r="V237" s="3" t="inlineStr"/>
-      <c r="W237" s="3" t="inlineStr"/>
+      <c r="W237" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
@@ -17825,10 +18013,14 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H238" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H238" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I238" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -17851,7 +18043,11 @@
       </c>
       <c r="U238" s="3" t="inlineStr"/>
       <c r="V238" s="3" t="inlineStr"/>
-      <c r="W238" s="3" t="inlineStr"/>
+      <c r="W238" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
@@ -17886,10 +18082,14 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H239" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H239" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I239" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -17912,7 +18112,11 @@
       </c>
       <c r="U239" s="3" t="inlineStr"/>
       <c r="V239" s="3" t="inlineStr"/>
-      <c r="W239" s="3" t="inlineStr"/>
+      <c r="W239" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
@@ -17947,10 +18151,14 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H240" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H240" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I240" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -17973,7 +18181,11 @@
       </c>
       <c r="U240" s="3" t="inlineStr"/>
       <c r="V240" s="3" t="inlineStr"/>
-      <c r="W240" s="3" t="inlineStr"/>
+      <c r="W240" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
@@ -18008,10 +18220,14 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H241" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H241" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I241" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -18034,7 +18250,11 @@
       </c>
       <c r="U241" s="3" t="inlineStr"/>
       <c r="V241" s="3" t="inlineStr"/>
-      <c r="W241" s="3" t="inlineStr"/>
+      <c r="W241" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
@@ -18069,10 +18289,14 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H242" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H242" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I242" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -18095,7 +18319,11 @@
       </c>
       <c r="U242" s="3" t="inlineStr"/>
       <c r="V242" s="3" t="inlineStr"/>
-      <c r="W242" s="3" t="inlineStr"/>
+      <c r="W242" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
@@ -18130,10 +18358,14 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H243" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H243" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I243" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -18156,7 +18388,11 @@
       </c>
       <c r="U243" s="3" t="inlineStr"/>
       <c r="V243" s="3" t="inlineStr"/>
-      <c r="W243" s="3" t="inlineStr"/>
+      <c r="W243" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
@@ -18191,10 +18427,14 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H244" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H244" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I244" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -18217,7 +18457,11 @@
       </c>
       <c r="U244" s="3" t="inlineStr"/>
       <c r="V244" s="3" t="inlineStr"/>
-      <c r="W244" s="3" t="inlineStr"/>
+      <c r="W244" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
@@ -18252,10 +18496,14 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H245" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H245" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I245" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -18278,7 +18526,11 @@
       </c>
       <c r="U245" s="3" t="inlineStr"/>
       <c r="V245" s="3" t="inlineStr"/>
-      <c r="W245" s="3" t="inlineStr"/>
+      <c r="W245" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
@@ -18313,10 +18565,14 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H246" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H246" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I246" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -18339,7 +18595,11 @@
       </c>
       <c r="U246" s="3" t="inlineStr"/>
       <c r="V246" s="3" t="inlineStr"/>
-      <c r="W246" s="3" t="inlineStr"/>
+      <c r="W246" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
@@ -18374,10 +18634,14 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H247" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H247" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I247" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -18400,7 +18664,11 @@
       </c>
       <c r="U247" s="3" t="inlineStr"/>
       <c r="V247" s="3" t="inlineStr"/>
-      <c r="W247" s="3" t="inlineStr"/>
+      <c r="W247" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
@@ -18435,10 +18703,14 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H248" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H248" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I248" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -18461,7 +18733,11 @@
       </c>
       <c r="U248" s="3" t="inlineStr"/>
       <c r="V248" s="3" t="inlineStr"/>
-      <c r="W248" s="3" t="inlineStr"/>
+      <c r="W248" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
@@ -18496,10 +18772,14 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H249" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H249" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I249" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -18522,7 +18802,11 @@
       </c>
       <c r="U249" s="3" t="inlineStr"/>
       <c r="V249" s="3" t="inlineStr"/>
-      <c r="W249" s="3" t="inlineStr"/>
+      <c r="W249" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
@@ -18557,10 +18841,14 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H250" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H250" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I250" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -18583,7 +18871,11 @@
       </c>
       <c r="U250" s="3" t="inlineStr"/>
       <c r="V250" s="3" t="inlineStr"/>
-      <c r="W250" s="3" t="inlineStr"/>
+      <c r="W250" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="3" t="inlineStr">
@@ -18618,10 +18910,14 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H251" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H251" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I251" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -18644,7 +18940,11 @@
       </c>
       <c r="U251" s="3" t="inlineStr"/>
       <c r="V251" s="3" t="inlineStr"/>
-      <c r="W251" s="3" t="inlineStr"/>
+      <c r="W251" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
@@ -18679,10 +18979,14 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H252" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H252" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I252" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -18705,7 +19009,11 @@
       </c>
       <c r="U252" s="3" t="inlineStr"/>
       <c r="V252" s="3" t="inlineStr"/>
-      <c r="W252" s="3" t="inlineStr"/>
+      <c r="W252" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
@@ -18740,10 +19048,14 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H253" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H253" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I253" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -18766,7 +19078,11 @@
       </c>
       <c r="U253" s="3" t="inlineStr"/>
       <c r="V253" s="3" t="inlineStr"/>
-      <c r="W253" s="3" t="inlineStr"/>
+      <c r="W253" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
@@ -18801,10 +19117,14 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H254" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H254" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I254" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -18827,7 +19147,11 @@
       </c>
       <c r="U254" s="3" t="inlineStr"/>
       <c r="V254" s="3" t="inlineStr"/>
-      <c r="W254" s="3" t="inlineStr"/>
+      <c r="W254" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
@@ -18862,10 +19186,14 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H255" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H255" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I255" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -18888,7 +19216,11 @@
       </c>
       <c r="U255" s="3" t="inlineStr"/>
       <c r="V255" s="3" t="inlineStr"/>
-      <c r="W255" s="3" t="inlineStr"/>
+      <c r="W255" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
@@ -18923,10 +19255,14 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H256" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H256" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I256" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -18949,7 +19285,11 @@
       </c>
       <c r="U256" s="3" t="inlineStr"/>
       <c r="V256" s="3" t="inlineStr"/>
-      <c r="W256" s="3" t="inlineStr"/>
+      <c r="W256" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
@@ -18984,10 +19324,14 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H257" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H257" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I257" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -19010,7 +19354,11 @@
       </c>
       <c r="U257" s="3" t="inlineStr"/>
       <c r="V257" s="3" t="inlineStr"/>
-      <c r="W257" s="3" t="inlineStr"/>
+      <c r="W257" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
@@ -19045,10 +19393,14 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H258" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H258" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I258" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -19071,7 +19423,11 @@
       </c>
       <c r="U258" s="3" t="inlineStr"/>
       <c r="V258" s="3" t="inlineStr"/>
-      <c r="W258" s="3" t="inlineStr"/>
+      <c r="W258" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
@@ -19106,10 +19462,14 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H259" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H259" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I259" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -19132,7 +19492,11 @@
       </c>
       <c r="U259" s="3" t="inlineStr"/>
       <c r="V259" s="3" t="inlineStr"/>
-      <c r="W259" s="3" t="inlineStr"/>
+      <c r="W259" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
@@ -19167,10 +19531,14 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H260" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H260" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I260" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -19193,7 +19561,11 @@
       </c>
       <c r="U260" s="3" t="inlineStr"/>
       <c r="V260" s="3" t="inlineStr"/>
-      <c r="W260" s="3" t="inlineStr"/>
+      <c r="W260" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
@@ -19228,10 +19600,14 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H261" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H261" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I261" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -19254,7 +19630,11 @@
       </c>
       <c r="U261" s="3" t="inlineStr"/>
       <c r="V261" s="3" t="inlineStr"/>
-      <c r="W261" s="3" t="inlineStr"/>
+      <c r="W261" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
@@ -19289,10 +19669,14 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H262" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H262" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I262" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -19315,7 +19699,11 @@
       </c>
       <c r="U262" s="3" t="inlineStr"/>
       <c r="V262" s="3" t="inlineStr"/>
-      <c r="W262" s="3" t="inlineStr"/>
+      <c r="W262" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="3" t="inlineStr">
@@ -19350,10 +19738,14 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H263" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H263" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I263" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -19376,7 +19768,11 @@
       </c>
       <c r="U263" s="3" t="inlineStr"/>
       <c r="V263" s="3" t="inlineStr"/>
-      <c r="W263" s="3" t="inlineStr"/>
+      <c r="W263" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
@@ -19411,10 +19807,14 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H264" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H264" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I264" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -19437,7 +19837,11 @@
       </c>
       <c r="U264" s="3" t="inlineStr"/>
       <c r="V264" s="3" t="inlineStr"/>
-      <c r="W264" s="3" t="inlineStr"/>
+      <c r="W264" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
@@ -19472,10 +19876,14 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H265" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H265" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I265" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -19498,7 +19906,11 @@
       </c>
       <c r="U265" s="3" t="inlineStr"/>
       <c r="V265" s="3" t="inlineStr"/>
-      <c r="W265" s="3" t="inlineStr"/>
+      <c r="W265" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
@@ -19533,10 +19945,14 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H266" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H266" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I266" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -19559,7 +19975,11 @@
       </c>
       <c r="U266" s="3" t="inlineStr"/>
       <c r="V266" s="3" t="inlineStr"/>
-      <c r="W266" s="3" t="inlineStr"/>
+      <c r="W266" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
@@ -19594,10 +20014,14 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H267" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H267" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I267" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -19620,7 +20044,11 @@
       </c>
       <c r="U267" s="3" t="inlineStr"/>
       <c r="V267" s="3" t="inlineStr"/>
-      <c r="W267" s="3" t="inlineStr"/>
+      <c r="W267" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
@@ -19655,10 +20083,14 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H268" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H268" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I268" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -19681,7 +20113,11 @@
       </c>
       <c r="U268" s="3" t="inlineStr"/>
       <c r="V268" s="3" t="inlineStr"/>
-      <c r="W268" s="3" t="inlineStr"/>
+      <c r="W268" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
@@ -19716,10 +20152,14 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H269" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H269" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I269" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -19742,7 +20182,11 @@
       </c>
       <c r="U269" s="3" t="inlineStr"/>
       <c r="V269" s="3" t="inlineStr"/>
-      <c r="W269" s="3" t="inlineStr"/>
+      <c r="W269" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_1_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
@@ -19777,10 +20221,14 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H270" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H270" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I270" s="3" t="inlineStr">
         <is>
           <t>每方向单元一、二跳各1</t>
@@ -19803,7 +20251,11 @@
       </c>
       <c r="U270" s="3" t="inlineStr"/>
       <c r="V270" s="3" t="inlineStr"/>
-      <c r="W270" s="3" t="inlineStr"/>
+      <c r="W270" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"JUMP_2_HUAGONG","reference_specimen_length_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
@@ -36532,7 +36984,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -36542,7 +36994,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -36553,7 +37005,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -36565,7 +37017,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>47d945e6fa5dc495d569b88a46f7a61a57539e80</t>
+          <t>0e0c084f42deffc068b8a8bae25bac596a74cef2</t>
         </is>
       </c>
     </row>
@@ -36577,7 +37029,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>c10083efe039f378967b13a9b84944c6dcc336dc02a7ccc9acf4379966acf8d3</t>
+          <t>cc43517f53601ace183bcb05d09f64c5ddad8fa3134d6838b379880b29001c37</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -37017,7 +37017,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>0e0c084f42deffc068b8a8bae25bac596a74cef2</t>
+          <t>4b915d32c3e11022764323c875f665cae8801c13</t>
         </is>
       </c>
     </row>
@@ -37029,7 +37029,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>cc43517f53601ace183bcb05d09f64c5ddad8fa3134d6838b379880b29001c37</t>
+          <t>68952b6c7dd02b7aedfa76015848164128c3e9309340f5f4f9d6b497517f1883</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.857</v>
+        <v>0.893</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -890,12 +890,16 @@
           <t>需新建Master</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr"/>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="E20" s="3" t="n">
         <v>16</v>
       </c>
@@ -1413,12 +1417,16 @@
           <t>需新建Master</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr"/>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="E43" s="3" t="n">
         <v>16</v>
       </c>
@@ -20625,10 +20633,14 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H276" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H276" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I276" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -20651,7 +20663,11 @@
       <c r="T276" s="3" t="inlineStr"/>
       <c r="U276" s="3" t="inlineStr"/>
       <c r="V276" s="3" t="inlineStr"/>
-      <c r="W276" s="3" t="inlineStr"/>
+      <c r="W276" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"TOU_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
@@ -20686,10 +20702,14 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H277" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H277" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I277" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -20712,7 +20732,11 @@
       <c r="T277" s="3" t="inlineStr"/>
       <c r="U277" s="3" t="inlineStr"/>
       <c r="V277" s="3" t="inlineStr"/>
-      <c r="W277" s="3" t="inlineStr"/>
+      <c r="W277" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"ER_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
@@ -21283,10 +21307,14 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H286" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H286" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I286" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -21309,7 +21337,11 @@
       <c r="T286" s="3" t="inlineStr"/>
       <c r="U286" s="3" t="inlineStr"/>
       <c r="V286" s="3" t="inlineStr"/>
-      <c r="W286" s="3" t="inlineStr"/>
+      <c r="W286" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"TOU_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
@@ -21344,10 +21376,14 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H287" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H287" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I287" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -21370,7 +21406,11 @@
       <c r="T287" s="3" t="inlineStr"/>
       <c r="U287" s="3" t="inlineStr"/>
       <c r="V287" s="3" t="inlineStr"/>
-      <c r="W287" s="3" t="inlineStr"/>
+      <c r="W287" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"ER_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
@@ -21941,10 +21981,14 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H296" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H296" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I296" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -21967,7 +22011,11 @@
       <c r="T296" s="3" t="inlineStr"/>
       <c r="U296" s="3" t="inlineStr"/>
       <c r="V296" s="3" t="inlineStr"/>
-      <c r="W296" s="3" t="inlineStr"/>
+      <c r="W296" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"TOU_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="3" t="inlineStr">
@@ -22002,10 +22050,14 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H297" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H297" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I297" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -22028,7 +22080,11 @@
       <c r="T297" s="3" t="inlineStr"/>
       <c r="U297" s="3" t="inlineStr"/>
       <c r="V297" s="3" t="inlineStr"/>
-      <c r="W297" s="3" t="inlineStr"/>
+      <c r="W297" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"ER_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="3" t="inlineStr">
@@ -22599,10 +22655,14 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H306" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H306" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I306" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -22625,7 +22685,11 @@
       <c r="T306" s="3" t="inlineStr"/>
       <c r="U306" s="3" t="inlineStr"/>
       <c r="V306" s="3" t="inlineStr"/>
-      <c r="W306" s="3" t="inlineStr"/>
+      <c r="W306" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"TOU_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="3" t="inlineStr">
@@ -22660,10 +22724,14 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H307" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H307" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I307" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -22686,7 +22754,11 @@
       <c r="T307" s="3" t="inlineStr"/>
       <c r="U307" s="3" t="inlineStr"/>
       <c r="V307" s="3" t="inlineStr"/>
-      <c r="W307" s="3" t="inlineStr"/>
+      <c r="W307" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"ER_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="3" t="inlineStr">
@@ -23056,10 +23128,14 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H313" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H313" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I313" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -23082,7 +23158,11 @@
       <c r="T313" s="3" t="inlineStr"/>
       <c r="U313" s="3" t="inlineStr"/>
       <c r="V313" s="3" t="inlineStr"/>
-      <c r="W313" s="3" t="inlineStr"/>
+      <c r="W313" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"TOU_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="3" t="inlineStr">
@@ -23117,10 +23197,14 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H314" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H314" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I314" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -23143,7 +23227,11 @@
       <c r="T314" s="3" t="inlineStr"/>
       <c r="U314" s="3" t="inlineStr"/>
       <c r="V314" s="3" t="inlineStr"/>
-      <c r="W314" s="3" t="inlineStr"/>
+      <c r="W314" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"ER_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="3" t="inlineStr">
@@ -23714,10 +23802,14 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H323" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H323" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I323" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -23740,7 +23832,11 @@
       <c r="T323" s="3" t="inlineStr"/>
       <c r="U323" s="3" t="inlineStr"/>
       <c r="V323" s="3" t="inlineStr"/>
-      <c r="W323" s="3" t="inlineStr"/>
+      <c r="W323" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"TOU_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="3" t="inlineStr">
@@ -23775,10 +23871,14 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H324" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H324" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I324" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -23801,7 +23901,11 @@
       <c r="T324" s="3" t="inlineStr"/>
       <c r="U324" s="3" t="inlineStr"/>
       <c r="V324" s="3" t="inlineStr"/>
-      <c r="W324" s="3" t="inlineStr"/>
+      <c r="W324" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"ER_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="3" t="inlineStr">
@@ -24372,10 +24476,14 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H333" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H333" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I333" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -24398,7 +24506,11 @@
       <c r="T333" s="3" t="inlineStr"/>
       <c r="U333" s="3" t="inlineStr"/>
       <c r="V333" s="3" t="inlineStr"/>
-      <c r="W333" s="3" t="inlineStr"/>
+      <c r="W333" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"TOU_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="3" t="inlineStr">
@@ -24433,10 +24545,14 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H334" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H334" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I334" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -24459,7 +24575,11 @@
       <c r="T334" s="3" t="inlineStr"/>
       <c r="U334" s="3" t="inlineStr"/>
       <c r="V334" s="3" t="inlineStr"/>
-      <c r="W334" s="3" t="inlineStr"/>
+      <c r="W334" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"ER_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="3" t="inlineStr">
@@ -25030,10 +25150,14 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H343" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H343" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I343" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -25056,7 +25180,11 @@
       <c r="T343" s="3" t="inlineStr"/>
       <c r="U343" s="3" t="inlineStr"/>
       <c r="V343" s="3" t="inlineStr"/>
-      <c r="W343" s="3" t="inlineStr"/>
+      <c r="W343" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"TOU_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="3" t="inlineStr">
@@ -25091,10 +25219,14 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H344" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H344" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I344" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -25117,7 +25249,11 @@
       <c r="T344" s="3" t="inlineStr"/>
       <c r="U344" s="3" t="inlineStr"/>
       <c r="V344" s="3" t="inlineStr"/>
-      <c r="W344" s="3" t="inlineStr"/>
+      <c r="W344" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"ER_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="3" t="inlineStr">
@@ -25487,10 +25623,14 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H350" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H350" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I350" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -25513,7 +25653,11 @@
       <c r="T350" s="3" t="inlineStr"/>
       <c r="U350" s="3" t="inlineStr"/>
       <c r="V350" s="3" t="inlineStr"/>
-      <c r="W350" s="3" t="inlineStr"/>
+      <c r="W350" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"TOU_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="3" t="inlineStr">
@@ -25548,10 +25692,14 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H351" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H351" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I351" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -25574,7 +25722,11 @@
       <c r="T351" s="3" t="inlineStr"/>
       <c r="U351" s="3" t="inlineStr"/>
       <c r="V351" s="3" t="inlineStr"/>
-      <c r="W351" s="3" t="inlineStr"/>
+      <c r="W351" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"ER_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="3" t="inlineStr">
@@ -26145,10 +26297,14 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H360" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H360" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I360" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -26171,7 +26327,11 @@
       <c r="T360" s="3" t="inlineStr"/>
       <c r="U360" s="3" t="inlineStr"/>
       <c r="V360" s="3" t="inlineStr"/>
-      <c r="W360" s="3" t="inlineStr"/>
+      <c r="W360" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"TOU_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="3" t="inlineStr">
@@ -26206,10 +26366,14 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H361" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H361" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I361" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -26232,7 +26396,11 @@
       <c r="T361" s="3" t="inlineStr"/>
       <c r="U361" s="3" t="inlineStr"/>
       <c r="V361" s="3" t="inlineStr"/>
-      <c r="W361" s="3" t="inlineStr"/>
+      <c r="W361" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"ER_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="3" t="inlineStr">
@@ -26803,10 +26971,14 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H370" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H370" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I370" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -26829,7 +27001,11 @@
       <c r="T370" s="3" t="inlineStr"/>
       <c r="U370" s="3" t="inlineStr"/>
       <c r="V370" s="3" t="inlineStr"/>
-      <c r="W370" s="3" t="inlineStr"/>
+      <c r="W370" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"TOU_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="3" t="inlineStr">
@@ -26864,10 +27040,14 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H371" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H371" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I371" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -26890,7 +27070,11 @@
       <c r="T371" s="3" t="inlineStr"/>
       <c r="U371" s="3" t="inlineStr"/>
       <c r="V371" s="3" t="inlineStr"/>
-      <c r="W371" s="3" t="inlineStr"/>
+      <c r="W371" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"ER_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="3" t="inlineStr">
@@ -27461,10 +27645,14 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H380" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H380" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I380" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -27487,7 +27675,11 @@
       <c r="T380" s="3" t="inlineStr"/>
       <c r="U380" s="3" t="inlineStr"/>
       <c r="V380" s="3" t="inlineStr"/>
-      <c r="W380" s="3" t="inlineStr"/>
+      <c r="W380" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"TOU_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="3" t="inlineStr">
@@ -27522,10 +27714,14 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H381" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H381" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I381" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -27548,7 +27744,11 @@
       <c r="T381" s="3" t="inlineStr"/>
       <c r="U381" s="3" t="inlineStr"/>
       <c r="V381" s="3" t="inlineStr"/>
-      <c r="W381" s="3" t="inlineStr"/>
+      <c r="W381" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"ER_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="3" t="inlineStr">
@@ -27918,10 +28118,14 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H387" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H387" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I387" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -27944,7 +28148,11 @@
       <c r="T387" s="3" t="inlineStr"/>
       <c r="U387" s="3" t="inlineStr"/>
       <c r="V387" s="3" t="inlineStr"/>
-      <c r="W387" s="3" t="inlineStr"/>
+      <c r="W387" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"TOU_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="3" t="inlineStr">
@@ -27979,10 +28187,14 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H388" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H388" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I388" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -28005,7 +28217,11 @@
       <c r="T388" s="3" t="inlineStr"/>
       <c r="U388" s="3" t="inlineStr"/>
       <c r="V388" s="3" t="inlineStr"/>
-      <c r="W388" s="3" t="inlineStr"/>
+      <c r="W388" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"ER_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="3" t="inlineStr">
@@ -28576,10 +28792,14 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H397" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H397" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I397" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -28602,7 +28822,11 @@
       <c r="T397" s="3" t="inlineStr"/>
       <c r="U397" s="3" t="inlineStr"/>
       <c r="V397" s="3" t="inlineStr"/>
-      <c r="W397" s="3" t="inlineStr"/>
+      <c r="W397" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"TOU_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="3" t="inlineStr">
@@ -28637,10 +28861,14 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H398" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H398" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I398" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -28663,7 +28891,11 @@
       <c r="T398" s="3" t="inlineStr"/>
       <c r="U398" s="3" t="inlineStr"/>
       <c r="V398" s="3" t="inlineStr"/>
-      <c r="W398" s="3" t="inlineStr"/>
+      <c r="W398" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"ER_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="3" t="inlineStr">
@@ -29234,10 +29466,14 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H407" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H407" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I407" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -29260,7 +29496,11 @@
       <c r="T407" s="3" t="inlineStr"/>
       <c r="U407" s="3" t="inlineStr"/>
       <c r="V407" s="3" t="inlineStr"/>
-      <c r="W407" s="3" t="inlineStr"/>
+      <c r="W407" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"TOU_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="3" t="inlineStr">
@@ -29295,10 +29535,14 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H408" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H408" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I408" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -29321,7 +29565,11 @@
       <c r="T408" s="3" t="inlineStr"/>
       <c r="U408" s="3" t="inlineStr"/>
       <c r="V408" s="3" t="inlineStr"/>
-      <c r="W408" s="3" t="inlineStr"/>
+      <c r="W408" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"ER_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="3" t="inlineStr">
@@ -29892,10 +30140,14 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H417" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H417" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I417" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -29918,7 +30170,11 @@
       <c r="T417" s="3" t="inlineStr"/>
       <c r="U417" s="3" t="inlineStr"/>
       <c r="V417" s="3" t="inlineStr"/>
-      <c r="W417" s="3" t="inlineStr"/>
+      <c r="W417" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"TOU_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="3" t="inlineStr">
@@ -29953,10 +30209,14 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H418" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H418" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I418" s="3" t="inlineStr">
         <is>
           <t>实测16+柱头类16方向单元</t>
@@ -29979,7 +30239,11 @@
       <c r="T418" s="3" t="inlineStr"/>
       <c r="U418" s="3" t="inlineStr"/>
       <c r="V418" s="3" t="inlineStr"/>
-      <c r="W418" s="3" t="inlineStr"/>
+      <c r="W418" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"ER_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="3" t="inlineStr">
@@ -36984,7 +37248,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -36994,7 +37258,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -37005,7 +37269,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>89.3%</t>
         </is>
       </c>
     </row>
@@ -37017,7 +37281,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>4b915d32c3e11022764323c875f665cae8801c13</t>
+          <t>b6b679b84f78a06e0d115f613f0f2d9fef30b271</t>
         </is>
       </c>
     </row>
@@ -37029,7 +37293,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>68952b6c7dd02b7aedfa76015848164128c3e9309340f5f4f9d6b497517f1883</t>
+          <t>c431aeaa54c665b0388a89f29a20e3255efc5877c8b6198baa3cc20da8365cbc</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -627,15 +627,15 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>已批准 Master</t>
+          <t>已覆盖 Master-scope 类型</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>PRODUCT_OWNER_APPROVED Master available</t>
+          <t>Master-scope对象类型中已有APPROVED_MASTER_AVAILABLE绑定的类型数</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -647,15 +647,15 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>待完成 Master</t>
+          <t>待完成 Master-scope 类型</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Master范围 - 已批准Master</t>
+          <t>Master-scope对象类型中尚未覆盖的类型数</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -667,15 +667,15 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Master完成度</t>
+          <t>Master-scope 覆盖率</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.893</v>
+        <v>1</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>已批准Master / Stage1 Master范围</t>
+          <t>已覆盖Master-scope对象类型 / Stage1 Master范围；不得用Master family数量作分子</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -687,38 +687,58 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>已绑定Master的登记记录</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>363</v>
+          <t>已批准 Master families</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>25</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>仅表示V008登记行覆盖数，不等于物理构件总件数</t>
+          <t>PRODUCT_OWNER_APPROVED Master family数量；与object type覆盖数是不同维度</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>COMPLETE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>已绑定Master的登记记录</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>363</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>仅表示V008登记行覆盖数，不等于物理构件总件数</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>PENDING_SOURCE_BINDING</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="B12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>仍在V008之外、不得静默视为已覆盖的对象</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>PENDING</t>
         </is>
@@ -37132,7 +37152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -37244,114 +37264,124 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>已批准Master</t>
+          <t>已覆盖Master-scope类型</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>待完成Master</t>
+          <t>待完成Master-scope类型</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Master完成度</t>
+          <t>Master-scope覆盖率</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>源 GitHub 提交</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>b6b679b84f78a06e0d115f613f0f2d9fef30b271</t>
-        </is>
+          <t>已批准Master families</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>源 JSON SHA-256</t>
+          <t>源 GitHub 提交</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>c431aeaa54c665b0388a89f29a20e3255efc5877c8b6198baa3cc20da8365cbc</t>
+          <t>823c21f87610823bbfee734963fbaae31d4d714f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>生成器版本</t>
+          <t>源 JSON SHA-256</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>1.0.2</t>
+          <t>4f32e65e5310ae4d92e7d20db5e8aa0fc0fa0b6923491827dfe94018dc242e97</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>生成器 SHA-256</t>
+          <t>生成器版本</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>e2695a9584e8a2c7e05f36713d92f5302595b5a877fd0b93f8615cfd4f35ab68</t>
+          <t>1.0.3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>同步规则</t>
+          <t>生成器 SHA-256</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>JSON先更新；Excel由自动流程生成。禁止人工修改Excel作为事实更新。</t>
+          <t>14f5092df95acb01ee1036ee5486fe791c78a5dbff93afa38ef3cc88cddb6383</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>版本规则</t>
+          <t>同步规则</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>CURRENT.xlsx对应CURRENT.json；Vxxx.xlsx对应同版本Vxxx.json快照。</t>
+          <t>JSON先更新；Excel由自动流程生成。禁止人工修改Excel作为事实更新。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>版本规则</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>CURRENT.xlsx对应CURRENT.json；Vxxx.xlsx对应同版本Vxxx.json快照。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>失败规则</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>自动生成失败时保持旧Excel并标记同步失败；不得假装已同步。</t>
         </is>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -4050,7 +4050,7 @@
       <c r="H24" s="3" t="inlineStr"/>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>同建筑结构说明明确：四椽栿上用驼峰、令栱承平梁；平梁之上设驼峰、蜀柱、叉手。当前仅锁定构件身份与结构角色；精确原页 source-binding、全殿数量、逐件位置、尺寸与轮廓待补。</t>
+          <t>A2同建筑官方数字专题直接说明：四椽栿上用驼峰、令栱承平梁；平梁之上设驼峰、蜀柱、叉手。A1 SRC-ZG-WF-001 PDF p83/印刷p68/图2-41、PDF p106/印刷p91/图2-71、PDF p109/印刷p94/图2-73提供同建筑梁架视觉与相对位置交叉核对；本轮未在A1相关实测表/附件中发现可独立锁定驼峰精确尺寸的条目。</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr"/>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>{"known_unknowns":["whole_hall_instance_count","per_instance_location_mapping","exact_dimensions","exact_profile","hidden_joinery"],"modeling_disposition":"EVIDENCE_BOUNDED_MASTER_REQUIRED / GEOMETRY_NOT_YET_BUILT","planned_master_reference":"CMP-FRAME-TUOFENG-001_MASTER","record_role":"FAMILY_UNKNOWN_COUNT","total_count":"UNKNOWN"}</t>
+          <t>{"known_unknowns":["whole_hall_instance_count","per_instance_location_mapping","exact_dimensions","exact_profile","hidden_joinery"],"master_readiness":"IDENTITY_READY / ASSEMBLY_ROLE_READY / GEOMETRY_SPEC NOT YET READY","modeling_disposition":"EVIDENCE_BOUNDED_MASTER_REQUIRED / GEOMETRY_NOT_YET_BUILT","planned_master_reference":"CMP-FRAME-TUOFENG-001_MASTER","record_role":"FAMILY_UNKNOWN_COUNT","source_binding":{"a1_locations":["PDF p83 / printed p68 / Fig. 2-41","PDF p106 / printed p91 / Fig. 2-71","PDF p109 / printed p94 / Fig. 2-73","PDF p344-345 / printed p329-330 / Appendix 1-7 to 1-9 targeted check"],"a1_primary_source":"SRC-ZG-WF-001","a2_direct_statement":"四椽栿上用驼峰、令栱承平梁；平梁之上设驼峰、蜀柱、叉手。","a2_official_same_building":"https://szbwgvue.chwhyun.cn/wanfodian/","document":"docs/evidence/zhenguo_wanfo/P3_3_TUOFENG_SOURCE_BINDING_V001.md","evidence_classification":{"assembly_roles":"FACT / A2 DIRECT","component_identity":"FACT / A2 DIRECT","exact_dimensions":"UNKNOWN","exact_profile":"UNKNOWN","hidden_joinery":"UNKNOWN","mapping_visible_hump_blocks_to_named_tuofeng":"INFERENCE / A1+A2 CROSS-CHECK","per_instance_mapping":"UNKNOWN","same_building_visual_correspondence":"FACT / A1 FIGURES","whole_hall_count":"UNKNOWN"},"status":"BOUND_FOR_IDENTITY_AND_ASSEMBLY_ROLE / GEOMETRY_UNRESOLVED"},"total_count":"UNKNOWN","variant_boundary":"AT_LEAST_TWO_ASSEMBLY_ROLES OBSERVED IN A2 STATEMENT: FOUR_CHUANFU_TO_PINGLIANG_SUPPORT and PINGLIANG_TO_RIDGE_SUPPORT. WHETHER ONE GEOMETRY FAMILY OR ROLE VARIANTS IS UNRESOLVED."}</t>
         </is>
       </c>
     </row>
@@ -37412,7 +37412,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>7743709c56e8f212953ac60f96b3aae2d1bb05e2</t>
+          <t>a91b2eed91ec238b6d4bacf9c4ff365c51d1c0ec</t>
         </is>
       </c>
     </row>
@@ -37424,7 +37424,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>9c98baba6eb20fd7574f653060ddcf97c740ae64efa17c091d460382c2dc21bf</t>
+          <t>89a56c31daef3141814d5d085470f8499cbdc9fc342cc15d1976ff619b3dddff</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -14,8 +14,8 @@
     <sheet name="使用规则" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'进度总览'!$A$14:$E$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'实例登记'!$A$1:$W$507</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'进度总览'!$A$14:$E$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'实例登记'!$A$1:$W$508</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -205,8 +205,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WanfoComponentRegistry" displayName="WanfoComponentRegistry" ref="A1:W507" headerRowCount="1">
-  <autoFilter ref="A1:W507"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WanfoComponentRegistry" displayName="WanfoComponentRegistry" ref="A1:W508" headerRowCount="1">
+  <autoFilter ref="A1:W508"/>
   <tableColumns count="23">
     <tableColumn id="1" name="系统"/>
     <tableColumn id="2" name="构件/对象"/>
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.966</v>
+        <v>0.9670000000000001</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -998,17 +998,17 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>内槽斗栱/隔架位置</t>
+          <t>令栱（梁架承托）</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>非实体装配/拓扑</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>NOT_PHYSICAL_MASTER</t>
+          <t>需新建Master</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>MASTER_REQUIRED_PENDING</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr"/>
@@ -1019,53 +1019,53 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>剳牵</t>
+          <t>内槽斗栱/隔架位置</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>需新建Master</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>APPROVED_MASTER_AVAILABLE</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>CMP-FRAME-ZHAQIAN-001_MASTER</t>
-        </is>
-      </c>
+          <t>非实体装配/拓扑</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>NOT_PHYSICAL_MASTER</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr"/>
       <c r="E25" s="3" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>北坡筒瓦</t>
+          <t>剳牵</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>参数化补全</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr"/>
+          <t>需新建Master</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-ZHAQIAN-001_MASTER</t>
+        </is>
+      </c>
       <c r="E26" s="3" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>北门洞</t>
+          <t>北坡筒瓦</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1086,37 +1086,33 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>华栱</t>
+          <t>北门洞</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>需新建Master</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>APPROVED_MASTER_AVAILABLE</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>CMP-GONG-HUAGONG-001_MASTER</t>
-        </is>
-      </c>
+          <t>参数化补全</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr"/>
       <c r="E28" s="3" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>单向长开斗族</t>
+          <t>华栱</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>已有Master｜族边界UNKNOWN</t>
+          <t>需新建Master</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1126,30 +1122,34 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>CMP-DOU-SINGLE-LONGKAI-001_MASTER</t>
+          <t>CMP-GONG-HUAGONG-001_MASTER</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>南坡筒瓦</t>
+          <t>单向长开斗族</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>参数化补全</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr"/>
+          <t>已有Master｜族边界UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>CMP-DOU-SINGLE-LONGKAI-001_MASTER</t>
+        </is>
+      </c>
       <c r="E30" s="3" t="n">
         <v>1</v>
       </c>
@@ -1157,7 +1157,7 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>南立面窗洞</t>
+          <t>南坡筒瓦</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1172,13 +1172,13 @@
       </c>
       <c r="D31" s="3" t="inlineStr"/>
       <c r="E31" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>南门洞</t>
+          <t>南立面窗洞</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1193,115 +1193,115 @@
       </c>
       <c r="D32" s="3" t="inlineStr"/>
       <c r="E32" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>叉手</t>
+          <t>南门洞</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>需新建Master</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>APPROVED_MASTER_AVAILABLE</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>CMP-FRAME-CHASHOU-001_MASTER</t>
-        </is>
-      </c>
+          <t>参数化补全</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr"/>
       <c r="E33" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>台基整体</t>
+          <t>叉手</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>简化Proxy</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>SIMPLIFIED_PROXY</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr"/>
+          <t>需新建Master</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-CHASHOU-001_MASTER</t>
+        </is>
+      </c>
       <c r="E34" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>四椽栿</t>
+          <t>台基整体</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>需新建Master</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>APPROVED_MASTER_AVAILABLE</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>CMP-FRAME-FOUR-CHUANFU-001_MASTER</t>
-        </is>
-      </c>
+          <t>简化Proxy</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>SIMPLIFIED_PROXY</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr"/>
       <c r="E35" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>垂兽</t>
+          <t>四椽栿</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>简化Proxy</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>SIMPLIFIED_PROXY</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr"/>
+          <t>需新建Master</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-FOUR-CHUANFU-001_MASTER</t>
+        </is>
+      </c>
       <c r="E36" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>垂脊</t>
+          <t>垂兽</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>参数化补全</t>
+          <t>简化Proxy</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
+          <t>SIMPLIFIED_PROXY</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr"/>
@@ -1312,7 +1312,7 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>墙体</t>
+          <t>垂脊</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1333,7 +1333,7 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>墙砖族</t>
+          <t>墙体</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1348,38 +1348,34 @@
       </c>
       <c r="D39" s="3" t="inlineStr"/>
       <c r="E39" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>大型慢栱</t>
+          <t>墙砖族</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>需新建Master</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>APPROVED_MASTER_AVAILABLE</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>CMP-GONG-MANGONG-001_MASTER</t>
-        </is>
-      </c>
+          <t>参数化补全</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr"/>
       <c r="E40" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>大型瓜子栱</t>
+          <t>大型慢栱</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1394,7 +1390,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>CMP-GONG-GUAZI-001_MASTER</t>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
@@ -1404,7 +1400,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>大角梁</t>
+          <t>大型瓜子栱</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1419,17 +1415,17 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>CMP-FRAME-DAJIAOLIANG-001_MASTER</t>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>头昂</t>
+          <t>大角梁</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1444,17 +1440,17 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>CMP-GONG-ANG-001_MASTER</t>
+          <t>CMP-FRAME-DAJIAOLIANG-001_MASTER</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>子角梁</t>
+          <t>头昂</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1469,38 +1465,42 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>CMP-FRAME-ZIJIAOLIANG-001_MASTER</t>
+          <t>CMP-GONG-ANG-001_MASTER</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>室内地面系统</t>
+          <t>子角梁</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>参数化补全</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr"/>
+          <t>需新建Master</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-ZIJIAOLIANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="E45" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>室内方砖族</t>
+          <t>室内地面系统</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1515,13 +1515,13 @@
       </c>
       <c r="D46" s="3" t="inlineStr"/>
       <c r="E46" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>室内条砖族</t>
+          <t>室内方砖族</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1536,38 +1536,34 @@
       </c>
       <c r="D47" s="3" t="inlineStr"/>
       <c r="E47" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>小型慢栱</t>
+          <t>室内条砖族</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>需新建Master</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>APPROVED_MASTER_AVAILABLE</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>CMP-GONG-MANGONG-001_MASTER</t>
-        </is>
-      </c>
+          <t>参数化补全</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr"/>
       <c r="E48" s="3" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>小型瓜子栱</t>
+          <t>小型慢栱</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1582,7 +1578,7 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>CMP-GONG-GUAZI-001_MASTER</t>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
@@ -1592,66 +1588,70 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>嵌墙石碑</t>
+          <t>小型瓜子栱</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>简化Proxy</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>SIMPLIFIED_PROXY</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr"/>
+          <t>需新建Master</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
+        </is>
+      </c>
       <c r="E50" s="3" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>平梁</t>
+          <t>嵌墙石碑</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>需新建Master</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>APPROVED_MASTER_AVAILABLE</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>CMP-FRAME-PINGLIANG-001_MASTER</t>
-        </is>
-      </c>
+          <t>简化Proxy</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>SIMPLIFIED_PROXY</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr"/>
       <c r="E51" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>戗兽</t>
+          <t>平梁</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>简化Proxy</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>SIMPLIFIED_PROXY</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr"/>
+          <t>需新建Master</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PINGLIANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="E52" s="3" t="n">
         <v>4</v>
       </c>
@@ -1659,17 +1659,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>戗脊</t>
+          <t>戗兽</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>参数化补全</t>
+          <t>简化Proxy</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
+          <t>SIMPLIFIED_PROXY</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr"/>
@@ -1680,53 +1680,53 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>托脚</t>
+          <t>戗脊</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>需新建Master</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>APPROVED_MASTER_AVAILABLE</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>CMP-FRAME-TUOJIAO-001_MASTER</t>
-        </is>
-      </c>
+          <t>参数化补全</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr"/>
       <c r="E54" s="3" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>散斗族</t>
+          <t>托脚</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN/参考边界</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>UNKNOWN_REFERENCE_BOUNDARY</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr"/>
+          <t>需新建Master</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-TUOJIAO-001_MASTER</t>
+        </is>
+      </c>
       <c r="E55" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>替木实体族</t>
+          <t>散斗族</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -1747,7 +1747,7 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>替木测量边界</t>
+          <t>替木实体族</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -1768,17 +1768,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>望板系统</t>
+          <t>替木测量边界</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>参数化补全</t>
+          <t>UNKNOWN/参考边界</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
+          <t>UNKNOWN_REFERENCE_BOUNDARY</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr"/>
@@ -1789,32 +1789,28 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>柱</t>
+          <t>望板系统</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>已有Master｜可直接绑定</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>APPROVED_MASTER_AVAILABLE</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>CMP-COLUMN-001_MASTER</t>
-        </is>
-      </c>
+          <t>参数化补全</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr"/>
       <c r="E59" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>柱头栌斗</t>
+          <t>柱</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -1829,7 +1825,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>CMP-LUDOU-COLUMN-001_MASTER</t>
+          <t>CMP-COLUMN-001_MASTER</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
@@ -1839,162 +1835,166 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>柱头铺作</t>
+          <t>柱头栌斗</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>非实体装配/拓扑</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>NOT_PHYSICAL_MASTER</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr"/>
+          <t>已有Master｜可直接绑定</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>CMP-LUDOU-COLUMN-001_MASTER</t>
+        </is>
+      </c>
       <c r="E61" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>椽系</t>
+          <t>柱头铺作</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>参数化补全</t>
+          <t>非实体装配/拓扑</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
+          <t>NOT_PHYSICAL_MASTER</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr"/>
       <c r="E62" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>槫</t>
+          <t>椽系</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>需新建Master</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>APPROVED_MASTER_AVAILABLE</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>CMP-FRAME-PURLIN-001_MASTER</t>
-        </is>
-      </c>
+          <t>参数化补全</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr"/>
       <c r="E63" s="3" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>正吻</t>
+          <t>槫</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>简化Proxy</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>SIMPLIFIED_PROXY</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr"/>
+          <t>需新建Master</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-PURLIN-001_MASTER</t>
+        </is>
+      </c>
       <c r="E64" s="3" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>正脊</t>
+          <t>正吻</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>参数化补全</t>
+          <t>简化Proxy</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
+          <t>SIMPLIFIED_PROXY</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr"/>
       <c r="E65" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>由额</t>
+          <t>正脊</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>需新建Master</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>APPROVED_MASTER_AVAILABLE</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>CMP-FRAME-YOUE-001_MASTER</t>
-        </is>
-      </c>
+          <t>参数化补全</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr"/>
       <c r="E66" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>神台</t>
+          <t>由额</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>参数化补全</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr"/>
+          <t>需新建Master</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-YOUE-001_MASTER</t>
+        </is>
+      </c>
       <c r="E67" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>窗木作系统</t>
+          <t>神台</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2009,76 +2009,72 @@
       </c>
       <c r="D68" s="3" t="inlineStr"/>
       <c r="E68" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>蜀柱</t>
+          <t>窗木作系统</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>需新建Master</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>APPROVED_MASTER_AVAILABLE</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>CMP-FRAME-SHUZHU-001_MASTER</t>
-        </is>
-      </c>
+          <t>参数化补全</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr"/>
       <c r="E69" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>补间铺作</t>
+          <t>蜀柱</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>非实体装配/拓扑</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>NOT_PHYSICAL_MASTER</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr"/>
+          <t>需新建Master</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-SHUZHU-001_MASTER</t>
+        </is>
+      </c>
       <c r="E70" s="3" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>补间铺作底斗</t>
+          <t>补间铺作</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>需新建Master</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>APPROVED_MASTER_AVAILABLE</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>CMP-DOU-BOTTOM-LONGKAI-001_MASTER</t>
-        </is>
-      </c>
+          <t>非实体装配/拓扑</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>NOT_PHYSICAL_MASTER</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr"/>
       <c r="E71" s="3" t="n">
         <v>12</v>
       </c>
@@ -2086,20 +2082,24 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>襻间枋</t>
+          <t>补间铺作底斗</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>参数化补全</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr"/>
+          <t>需新建Master</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>CMP-DOU-BOTTOM-LONGKAI-001_MASTER</t>
+        </is>
+      </c>
       <c r="E72" s="3" t="n">
         <v>12</v>
       </c>
@@ -2107,7 +2107,7 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>西坡筒瓦</t>
+          <t>襻间枋</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2122,44 +2122,44 @@
       </c>
       <c r="D73" s="3" t="inlineStr"/>
       <c r="E73" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>角石</t>
+          <t>西坡筒瓦</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>简化Proxy</t>
+          <t>参数化补全</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>SIMPLIFIED_PROXY</t>
+          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr"/>
       <c r="E74" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>转角铺作</t>
+          <t>角石</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>非实体装配/拓扑</t>
+          <t>简化Proxy</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>NOT_PHYSICAL_MASTER</t>
+          <t>SIMPLIFIED_PROXY</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr"/>
@@ -2170,135 +2170,160 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>透风孔</t>
+          <t>转角铺作</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>参数化补全</t>
+          <t>非实体装配/拓扑</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
+          <t>NOT_PHYSICAL_MASTER</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr"/>
       <c r="E76" s="3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>铺作方向单元</t>
+          <t>透风孔</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>非实体装配/拓扑</t>
+          <t>参数化补全</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>NOT_PHYSICAL_MASTER</t>
+          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr"/>
       <c r="E77" s="3" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>门木作系统</t>
+          <t>铺作方向单元</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>参数化补全</t>
+          <t>非实体装配/拓扑</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
+          <t>NOT_PHYSICAL_MASTER</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr"/>
       <c r="E78" s="3" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>阑额</t>
+          <t>门木作系统</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>需新建Master</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>APPROVED_MASTER_AVAILABLE</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>CMP-FRAME-LANE-001_MASTER</t>
-        </is>
-      </c>
+          <t>参数化补全</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr"/>
       <c r="E79" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>隐角梁</t>
+          <t>阑额</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>参数化补全</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr"/>
+          <t>需新建Master</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-LANE-001_MASTER</t>
+        </is>
+      </c>
       <c r="E80" s="3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>驼峰</t>
+          <t>隐角梁</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>需新建Master</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>MASTER_REQUIRED_PENDING</t>
+          <t>参数化补全</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr"/>
       <c r="E81" s="3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>驼峰</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>已有Master｜族边界UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-TUOFENG-001_MASTER</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A14:E81"/>
+  <autoFilter ref="A14:E82"/>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
   </mergeCells>
@@ -2312,7 +2337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W507"/>
+  <dimension ref="A1:W508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4039,15 +4064,19 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>需新建Master</t>
+          <t>已有Master｜族边界UNKNOWN</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-TUOFENG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
           <t>A2同建筑官方数字专题直接说明：四椽栿上用驼峰、令栱承平梁；平梁之上设驼峰、蜀柱、叉手。A1 SRC-ZG-WF-001 PDF p83/印刷p68/图2-41、PDF p106/印刷p91/图2-71、PDF p109/印刷p94/图2-73提供同建筑梁架视觉与相对位置交叉核对；本轮未在A1相关实测表/附件中发现可独立锁定驼峰精确尺寸的条目。</t>
@@ -4072,7 +4101,7 @@
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>{"known_unknowns":["whole_hall_instance_count","per_instance_location_mapping","exact_dimensions","exact_profile","hidden_joinery"],"master_readiness":"IDENTITY_READY / ASSEMBLY_ROLE_READY / GEOMETRY_SPEC NOT YET READY","modeling_disposition":"EVIDENCE_BOUNDED_MASTER_REQUIRED / GEOMETRY_NOT_YET_BUILT","planned_master_reference":"CMP-FRAME-TUOFENG-001_MASTER","record_role":"FAMILY_UNKNOWN_COUNT","source_binding":{"a1_locations":["PDF p83 / printed p68 / Fig. 2-41","PDF p106 / printed p91 / Fig. 2-71","PDF p109 / printed p94 / Fig. 2-73","PDF p344-345 / printed p329-330 / Appendix 1-7 to 1-9 targeted check"],"a1_primary_source":"SRC-ZG-WF-001","a2_direct_statement":"四椽栿上用驼峰、令栱承平梁；平梁之上设驼峰、蜀柱、叉手。","a2_official_same_building":"https://szbwgvue.chwhyun.cn/wanfodian/","document":"docs/evidence/zhenguo_wanfo/P3_3_TUOFENG_SOURCE_BINDING_V001.md","evidence_classification":{"assembly_roles":"FACT / A2 DIRECT","component_identity":"FACT / A2 DIRECT","exact_dimensions":"UNKNOWN","exact_profile":"UNKNOWN","hidden_joinery":"UNKNOWN","mapping_visible_hump_blocks_to_named_tuofeng":"INFERENCE / A1+A2 CROSS-CHECK","per_instance_mapping":"UNKNOWN","same_building_visual_correspondence":"FACT / A1 FIGURES","whole_hall_count":"UNKNOWN"},"status":"BOUND_FOR_IDENTITY_AND_ASSEMBLY_ROLE / GEOMETRY_UNRESOLVED"},"total_count":"UNKNOWN","variant_boundary":"AT_LEAST_TWO_ASSEMBLY_ROLES OBSERVED IN A2 STATEMENT: FOUR_CHUANFU_TO_PINGLIANG_SUPPORT and PINGLIANG_TO_RIDGE_SUPPORT. WHETHER ONE GEOMETRY FAMILY OR ROLE VARIANTS IS UNRESOLVED."}</t>
+          <t>{"formalization":{"artifact_id":11391915287,"canonical_blend_sha256":"eb24ca1ad0e39df0bac3558f777f3844d2952cf2e0cbfe7b699b1d268ec60c7b","family_signature":"a6ec7f0c43f2639810e41751e9bce0b618ea4684294a54d8e21646516207415f","merge_authorized":false,"status":"FORMALIZED / PRODUCT_OWNER_APPROVED"},"hidden_joinery":"UNKNOWN / DEFERRED","historical_metric_dimensions":"UNKNOWN","known_unknowns":["whole_hall_instance_count","per_instance_location_mapping","exact_dimensions","exact_profile","hidden_joinery"],"master_readiness":"APPROVED_MASTER_AVAILABLE / ASSEMBLY READY SUBJECT TO LOCAL METRIC ENVELOPE","master_variants":["LOWER_SUPPORT","UPPER_RIDGE_SUPPORT"],"modeling_disposition":"APPROVED_MASTER_AVAILABLE / ASSEMBLY_METRIC_ENVELOPE_OWNED / HISTORICAL_METRICS_UNKNOWN","planned_master_reference":"CMP-FRAME-TUOFENG-001_MASTER","record_role":"FAMILY_UNKNOWN_COUNT","source_binding":{"a1_locations":["PDF p83 / printed p68 / Fig. 2-41","PDF p106 / printed p91 / Fig. 2-71","PDF p109 / printed p94 / Fig. 2-73","PDF p344-345 / printed p329-330 / Appendix 1-7 to 1-9 targeted check"],"a1_primary_source":"SRC-ZG-WF-001","a2_direct_statement":"四椽栿上用驼峰、令栱承平梁；平梁之上设驼峰、蜀柱、叉手。","a2_official_same_building":"https://szbwgvue.chwhyun.cn/wanfodian/","document":"docs/evidence/zhenguo_wanfo/P3_3_TUOFENG_SOURCE_BINDING_V001.md","evidence_classification":{"assembly_roles":"FACT / A2 DIRECT","component_identity":"FACT / A2 DIRECT","exact_dimensions":"UNKNOWN","exact_profile":"UNKNOWN","hidden_joinery":"UNKNOWN","mapping_visible_hump_blocks_to_named_tuofeng":"INFERENCE / A1+A2 CROSS-CHECK","per_instance_mapping":"UNKNOWN","same_building_visual_correspondence":"FACT / A1 FIGURES","whole_hall_count":"UNKNOWN"},"status":"BOUND_FOR_IDENTITY_AND_ASSEMBLY_ROLE / GEOMETRY_UNRESOLVED"},"total_count":"UNKNOWN","variant_boundary":"ONE MASTER FAMILY / TWO ROLE VARIANTS: LOWER_SUPPORT + UPPER_RIDGE_SUPPORT"}</t>
         </is>
       </c>
     </row>
@@ -29948,27 +29977,27 @@
     <row r="414">
       <c r="A414" s="3" t="inlineStr">
         <is>
-          <t>外檐斗栱</t>
+          <t>主体梁架</t>
         </is>
       </c>
       <c r="B414" s="3" t="inlineStr">
         <is>
-          <t>大型瓜子栱</t>
+          <t>令栱（梁架承托）</t>
         </is>
       </c>
       <c r="C414" s="3" t="inlineStr">
         <is>
-          <t>大型瓜子栱-西-07-泥道</t>
+          <t>令栱（梁架承托）-族边界UNKNOWN</t>
         </is>
       </c>
       <c r="D414" s="3" t="inlineStr">
         <is>
-          <t>西南角转角铺作西向分支 / 泥道</t>
+          <t>四椽栿—平梁承托体系；东缝 Minimum Proof 先行，whole-hall mapping 未闭合</t>
         </is>
       </c>
       <c r="E414" s="3" t="inlineStr">
         <is>
-          <t>LOCKED_DERIVED</t>
+          <t>FAMILY_UNKNOWN_COUNT</t>
         </is>
       </c>
       <c r="F414" s="3" t="inlineStr">
@@ -29978,17 +30007,13 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>APPROVED_MASTER_AVAILABLE</t>
-        </is>
-      </c>
-      <c r="H414" s="3" t="inlineStr">
-        <is>
-          <t>CMP-GONG-GUAZI-001_MASTER</t>
-        </is>
-      </c>
+          <t>MASTER_REQUIRED_PENDING</t>
+        </is>
+      </c>
+      <c r="H414" s="3" t="inlineStr"/>
       <c r="I414" s="3" t="inlineStr">
         <is>
-          <t>大型实测16+柱头类16方向单元</t>
+          <t>A2同建筑官方数字专题直接说明“ 四椽栿上用驼峰、令栱承平梁 ”，足以锁定构件身份与承托角色。现有 CMP-GONG-LINGGONG-001_MASTER 的 897×217.4×155.6 mm 及14点轮廓来自28个外檐斗栱令栱样本，不得静默继承到梁架内部角色。当前 bound evidence 未隔离出梁架承托令栱的独立历史尺寸、精确轮廓或隐藏榫卯。</t>
         </is>
       </c>
       <c r="J414" s="3" t="inlineStr"/>
@@ -29998,19 +30023,21 @@
       <c r="N414" s="3" t="inlineStr"/>
       <c r="O414" s="3" t="inlineStr"/>
       <c r="P414" s="3" t="inlineStr"/>
-      <c r="Q414" s="3" t="n">
-        <v>1007</v>
-      </c>
-      <c r="R414" s="3" t="n">
-        <v>214.7</v>
-      </c>
-      <c r="S414" s="3" t="n">
-        <v>156.5</v>
-      </c>
+      <c r="Q414" s="3" t="inlineStr"/>
+      <c r="R414" s="3" t="inlineStr"/>
+      <c r="S414" s="3" t="inlineStr"/>
       <c r="T414" s="3" t="inlineStr"/>
       <c r="U414" s="3" t="inlineStr"/>
-      <c r="V414" s="3" t="inlineStr"/>
-      <c r="W414" s="3" t="inlineStr"/>
+      <c r="V414" s="3" t="inlineStr">
+        <is>
+          <t>MP-01B Gate A/B: 与外檐令栱分开管理是证据/数据模型边界，不主张历史上一定属于不同命名构件类型。若后续直接证据证明同型，可在保留 provenance 的前提下 reconciliation。</t>
+        </is>
+      </c>
+      <c r="W414" s="3" t="inlineStr">
+        <is>
+          <t>{"known_unknowns":["whole_hall_instance_count","exact_per_instance_mapping","exact_length","exact_width_depth","exact_profile","hidden_joinery","equivalence_to_outer_eaves_linggong"],"modeling_disposition":"SOURCE_GUIDED_SIMPLIFIED / ASSEMBLY_ENVELOPE_OWNED / REPLACEABLE","planned_master_reference":"CMP-FRAME-LINGGONG-INTERIOR-001_MASTER","record_role":"FAMILY_UNKNOWN_COUNT","source_binding":"docs/evidence/zhenguo_wanfo/P3_3_INTERIOR_LINGGONG_SOURCE_BINDING_V001.md","total_count":"UNKNOWN"}</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="3" t="inlineStr">
@@ -30020,12 +30047,12 @@
       </c>
       <c r="B415" s="3" t="inlineStr">
         <is>
-          <t>大型慢栱</t>
+          <t>大型瓜子栱</t>
         </is>
       </c>
       <c r="C415" s="3" t="inlineStr">
         <is>
-          <t>大型慢栱-西-07-泥道</t>
+          <t>大型瓜子栱-西-07-泥道</t>
         </is>
       </c>
       <c r="D415" s="3" t="inlineStr">
@@ -30050,7 +30077,7 @@
       </c>
       <c r="H415" s="3" t="inlineStr">
         <is>
-          <t>CMP-GONG-MANGONG-001_MASTER</t>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
         </is>
       </c>
       <c r="I415" s="3" t="inlineStr">
@@ -30066,13 +30093,13 @@
       <c r="O415" s="3" t="inlineStr"/>
       <c r="P415" s="3" t="inlineStr"/>
       <c r="Q415" s="3" t="n">
-        <v>1641</v>
+        <v>1007</v>
       </c>
       <c r="R415" s="3" t="n">
-        <v>218.9</v>
+        <v>214.7</v>
       </c>
       <c r="S415" s="3" t="n">
-        <v>156.9</v>
+        <v>156.5</v>
       </c>
       <c r="T415" s="3" t="inlineStr"/>
       <c r="U415" s="3" t="inlineStr"/>
@@ -30087,17 +30114,17 @@
       </c>
       <c r="B416" s="3" t="inlineStr">
         <is>
-          <t>小型瓜子栱</t>
+          <t>大型慢栱</t>
         </is>
       </c>
       <c r="C416" s="3" t="inlineStr">
         <is>
-          <t>小型瓜子栱-西-07-二跳</t>
+          <t>大型慢栱-西-07-泥道</t>
         </is>
       </c>
       <c r="D416" s="3" t="inlineStr">
         <is>
-          <t>西南角转角铺作西向分支 / 二跳</t>
+          <t>西南角转角铺作西向分支 / 泥道</t>
         </is>
       </c>
       <c r="E416" s="3" t="inlineStr">
@@ -30117,12 +30144,12 @@
       </c>
       <c r="H416" s="3" t="inlineStr">
         <is>
-          <t>CMP-GONG-GUAZI-001_MASTER</t>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
         </is>
       </c>
       <c r="I416" s="3" t="inlineStr">
         <is>
-          <t>小型总28中的柱头类二跳16</t>
+          <t>大型实测16+柱头类16方向单元</t>
         </is>
       </c>
       <c r="J416" s="3" t="inlineStr"/>
@@ -30133,13 +30160,13 @@
       <c r="O416" s="3" t="inlineStr"/>
       <c r="P416" s="3" t="inlineStr"/>
       <c r="Q416" s="3" t="n">
-        <v>895</v>
+        <v>1641</v>
       </c>
       <c r="R416" s="3" t="n">
-        <v>214.7</v>
+        <v>218.9</v>
       </c>
       <c r="S416" s="3" t="n">
-        <v>156.5</v>
+        <v>156.9</v>
       </c>
       <c r="T416" s="3" t="inlineStr"/>
       <c r="U416" s="3" t="inlineStr"/>
@@ -30154,12 +30181,12 @@
       </c>
       <c r="B417" s="3" t="inlineStr">
         <is>
-          <t>小型慢栱</t>
+          <t>小型瓜子栱</t>
         </is>
       </c>
       <c r="C417" s="3" t="inlineStr">
         <is>
-          <t>小型慢栱-西-07-二跳</t>
+          <t>小型瓜子栱-西-07-二跳</t>
         </is>
       </c>
       <c r="D417" s="3" t="inlineStr">
@@ -30184,7 +30211,7 @@
       </c>
       <c r="H417" s="3" t="inlineStr">
         <is>
-          <t>CMP-GONG-MANGONG-001_MASTER</t>
+          <t>CMP-GONG-GUAZI-001_MASTER</t>
         </is>
       </c>
       <c r="I417" s="3" t="inlineStr">
@@ -30200,13 +30227,13 @@
       <c r="O417" s="3" t="inlineStr"/>
       <c r="P417" s="3" t="inlineStr"/>
       <c r="Q417" s="3" t="n">
-        <v>1607</v>
+        <v>895</v>
       </c>
       <c r="R417" s="3" t="n">
-        <v>218.9</v>
+        <v>214.7</v>
       </c>
       <c r="S417" s="3" t="n">
-        <v>156.9</v>
+        <v>156.5</v>
       </c>
       <c r="T417" s="3" t="inlineStr"/>
       <c r="U417" s="3" t="inlineStr"/>
@@ -30221,17 +30248,17 @@
       </c>
       <c r="B418" s="3" t="inlineStr">
         <is>
-          <t>头昂</t>
+          <t>小型慢栱</t>
         </is>
       </c>
       <c r="C418" s="3" t="inlineStr">
         <is>
-          <t>头昂-西-07</t>
+          <t>小型慢栱-西-07-二跳</t>
         </is>
       </c>
       <c r="D418" s="3" t="inlineStr">
         <is>
-          <t>西南角转角铺作西向分支 / 头昂</t>
+          <t>西南角转角铺作西向分支 / 二跳</t>
         </is>
       </c>
       <c r="E418" s="3" t="inlineStr">
@@ -30251,12 +30278,12 @@
       </c>
       <c r="H418" s="3" t="inlineStr">
         <is>
-          <t>CMP-GONG-ANG-001_MASTER</t>
+          <t>CMP-GONG-MANGONG-001_MASTER</t>
         </is>
       </c>
       <c r="I418" s="3" t="inlineStr">
         <is>
-          <t>实测16+柱头类16方向单元</t>
+          <t>小型总28中的柱头类二跳16</t>
         </is>
       </c>
       <c r="J418" s="3" t="inlineStr"/>
@@ -30266,21 +30293,19 @@
       <c r="N418" s="3" t="inlineStr"/>
       <c r="O418" s="3" t="inlineStr"/>
       <c r="P418" s="3" t="inlineStr"/>
-      <c r="Q418" s="3" t="inlineStr"/>
+      <c r="Q418" s="3" t="n">
+        <v>1607</v>
+      </c>
       <c r="R418" s="3" t="n">
-        <v>278.4</v>
+        <v>218.9</v>
       </c>
       <c r="S418" s="3" t="n">
-        <v>154</v>
+        <v>156.9</v>
       </c>
       <c r="T418" s="3" t="inlineStr"/>
       <c r="U418" s="3" t="inlineStr"/>
       <c r="V418" s="3" t="inlineStr"/>
-      <c r="W418" s="3" t="inlineStr">
-        <is>
-          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"TOU_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
-        </is>
-      </c>
+      <c r="W418" s="3" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="3" t="inlineStr">
@@ -30290,17 +30315,17 @@
       </c>
       <c r="B419" s="3" t="inlineStr">
         <is>
-          <t>二昂</t>
+          <t>头昂</t>
         </is>
       </c>
       <c r="C419" s="3" t="inlineStr">
         <is>
-          <t>二昂-西-07</t>
+          <t>头昂-西-07</t>
         </is>
       </c>
       <c r="D419" s="3" t="inlineStr">
         <is>
-          <t>西南角转角铺作西向分支 / 二昂</t>
+          <t>西南角转角铺作西向分支 / 头昂</t>
         </is>
       </c>
       <c r="E419" s="3" t="inlineStr">
@@ -30337,7 +30362,7 @@
       <c r="P419" s="3" t="inlineStr"/>
       <c r="Q419" s="3" t="inlineStr"/>
       <c r="R419" s="3" t="n">
-        <v>187</v>
+        <v>278.4</v>
       </c>
       <c r="S419" s="3" t="n">
         <v>154</v>
@@ -30347,74 +30372,78 @@
       <c r="V419" s="3" t="inlineStr"/>
       <c r="W419" s="3" t="inlineStr">
         <is>
-          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"ER_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"TOU_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="3" t="inlineStr">
         <is>
-          <t>内槽</t>
+          <t>外檐斗栱</t>
         </is>
       </c>
       <c r="B420" s="3" t="inlineStr">
         <is>
-          <t>襻间枋</t>
+          <t>二昂</t>
         </is>
       </c>
       <c r="C420" s="3" t="inlineStr">
         <is>
-          <t>襻间枋-01</t>
+          <t>二昂-西-07</t>
         </is>
       </c>
       <c r="D420" s="3" t="inlineStr">
         <is>
-          <t>东缝前下平槫下</t>
+          <t>西南角转角铺作西向分支 / 二昂</t>
         </is>
       </c>
       <c r="E420" s="3" t="inlineStr">
         <is>
-          <t>LOCKED_SITE</t>
+          <t>LOCKED_DERIVED</t>
         </is>
       </c>
       <c r="F420" s="3" t="inlineStr">
         <is>
-          <t>参数化补全</t>
+          <t>需新建Master</t>
         </is>
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
-        </is>
-      </c>
-      <c r="H420" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H420" s="3" t="inlineStr">
+        <is>
+          <t>CMP-GONG-ANG-001_MASTER</t>
+        </is>
+      </c>
       <c r="I420" s="3" t="inlineStr">
         <is>
-          <t>附件1-9逐位记录</t>
+          <t>实测16+柱头类16方向单元</t>
         </is>
       </c>
       <c r="J420" s="3" t="inlineStr"/>
       <c r="K420" s="3" t="inlineStr"/>
       <c r="L420" s="3" t="inlineStr"/>
-      <c r="M420" s="3" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
+      <c r="M420" s="3" t="inlineStr"/>
       <c r="N420" s="3" t="inlineStr"/>
       <c r="O420" s="3" t="inlineStr"/>
       <c r="P420" s="3" t="inlineStr"/>
       <c r="Q420" s="3" t="inlineStr"/>
-      <c r="R420" s="3" t="inlineStr"/>
-      <c r="S420" s="3" t="inlineStr"/>
+      <c r="R420" s="3" t="n">
+        <v>187</v>
+      </c>
+      <c r="S420" s="3" t="n">
+        <v>154</v>
+      </c>
       <c r="T420" s="3" t="inlineStr"/>
       <c r="U420" s="3" t="inlineStr"/>
-      <c r="V420" s="3" t="inlineStr">
-        <is>
-          <t>215.0×153.6mm不属于襻间枋统一截面</t>
-        </is>
-      </c>
-      <c r="W420" s="3" t="inlineStr"/>
+      <c r="V420" s="3" t="inlineStr"/>
+      <c r="W420" s="3" t="inlineStr">
+        <is>
+          <t>{"historical_standalone_full_length_status":"UNRESOLVED","master_variant":"ER_ANG","per_instance_exact_dimension_claim":false,"reference_control_span_applies_to_instance":false}</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="3" t="inlineStr">
@@ -30429,12 +30458,12 @@
       </c>
       <c r="C421" s="3" t="inlineStr">
         <is>
-          <t>襻间枋-02</t>
+          <t>襻间枋-01</t>
         </is>
       </c>
       <c r="D421" s="3" t="inlineStr">
         <is>
-          <t>东缝后下平槫下</t>
+          <t>东缝前下平槫下</t>
         </is>
       </c>
       <c r="E421" s="3" t="inlineStr">
@@ -30494,12 +30523,12 @@
       </c>
       <c r="C422" s="3" t="inlineStr">
         <is>
-          <t>襻间枋-03</t>
+          <t>襻间枋-02</t>
         </is>
       </c>
       <c r="D422" s="3" t="inlineStr">
         <is>
-          <t>西缝前下平槫下</t>
+          <t>东缝后下平槫下</t>
         </is>
       </c>
       <c r="E422" s="3" t="inlineStr">
@@ -30559,12 +30588,12 @@
       </c>
       <c r="C423" s="3" t="inlineStr">
         <is>
-          <t>襻间枋-04</t>
+          <t>襻间枋-03</t>
         </is>
       </c>
       <c r="D423" s="3" t="inlineStr">
         <is>
-          <t>西缝后下平槫下</t>
+          <t>西缝前下平槫下</t>
         </is>
       </c>
       <c r="E423" s="3" t="inlineStr">
@@ -30624,12 +30653,12 @@
       </c>
       <c r="C424" s="3" t="inlineStr">
         <is>
-          <t>襻间枋-05</t>
+          <t>襻间枋-04</t>
         </is>
       </c>
       <c r="D424" s="3" t="inlineStr">
         <is>
-          <t>东山南下平槫下</t>
+          <t>西缝后下平槫下</t>
         </is>
       </c>
       <c r="E424" s="3" t="inlineStr">
@@ -30689,12 +30718,12 @@
       </c>
       <c r="C425" s="3" t="inlineStr">
         <is>
-          <t>襻间枋-06</t>
+          <t>襻间枋-05</t>
         </is>
       </c>
       <c r="D425" s="3" t="inlineStr">
         <is>
-          <t>东山北下平槫下</t>
+          <t>东山南下平槫下</t>
         </is>
       </c>
       <c r="E425" s="3" t="inlineStr">
@@ -30754,12 +30783,12 @@
       </c>
       <c r="C426" s="3" t="inlineStr">
         <is>
-          <t>襻间枋-07</t>
+          <t>襻间枋-06</t>
         </is>
       </c>
       <c r="D426" s="3" t="inlineStr">
         <is>
-          <t>西山南下平槫下</t>
+          <t>东山北下平槫下</t>
         </is>
       </c>
       <c r="E426" s="3" t="inlineStr">
@@ -30819,12 +30848,12 @@
       </c>
       <c r="C427" s="3" t="inlineStr">
         <is>
-          <t>襻间枋-08</t>
+          <t>襻间枋-07</t>
         </is>
       </c>
       <c r="D427" s="3" t="inlineStr">
         <is>
-          <t>西山北下平槫下</t>
+          <t>西山南下平槫下</t>
         </is>
       </c>
       <c r="E427" s="3" t="inlineStr">
@@ -30884,12 +30913,12 @@
       </c>
       <c r="C428" s="3" t="inlineStr">
         <is>
-          <t>襻间枋-09</t>
+          <t>襻间枋-08</t>
         </is>
       </c>
       <c r="D428" s="3" t="inlineStr">
         <is>
-          <t>东缝前上平槫下</t>
+          <t>西山北下平槫下</t>
         </is>
       </c>
       <c r="E428" s="3" t="inlineStr">
@@ -30949,12 +30978,12 @@
       </c>
       <c r="C429" s="3" t="inlineStr">
         <is>
-          <t>襻间枋-10</t>
+          <t>襻间枋-09</t>
         </is>
       </c>
       <c r="D429" s="3" t="inlineStr">
         <is>
-          <t>东缝后上平槫下</t>
+          <t>东缝前上平槫下</t>
         </is>
       </c>
       <c r="E429" s="3" t="inlineStr">
@@ -31014,12 +31043,12 @@
       </c>
       <c r="C430" s="3" t="inlineStr">
         <is>
-          <t>襻间枋-11</t>
+          <t>襻间枋-10</t>
         </is>
       </c>
       <c r="D430" s="3" t="inlineStr">
         <is>
-          <t>西缝前上平槫下</t>
+          <t>东缝后上平槫下</t>
         </is>
       </c>
       <c r="E430" s="3" t="inlineStr">
@@ -31079,12 +31108,12 @@
       </c>
       <c r="C431" s="3" t="inlineStr">
         <is>
-          <t>襻间枋-12</t>
+          <t>襻间枋-11</t>
         </is>
       </c>
       <c r="D431" s="3" t="inlineStr">
         <is>
-          <t>西缝后上平槫下</t>
+          <t>西缝前上平槫下</t>
         </is>
       </c>
       <c r="E431" s="3" t="inlineStr">
@@ -31139,44 +31168,48 @@
       </c>
       <c r="B432" s="3" t="inlineStr">
         <is>
-          <t>内槽斗栱/隔架位置</t>
+          <t>襻间枋</t>
         </is>
       </c>
       <c r="C432" s="3" t="inlineStr">
         <is>
-          <t>内槽位置总表</t>
+          <t>襻间枋-12</t>
         </is>
       </c>
       <c r="D432" s="3" t="inlineStr">
         <is>
-          <t>24处</t>
+          <t>西缝后上平槫下</t>
         </is>
       </c>
       <c r="E432" s="3" t="inlineStr">
         <is>
-          <t>LOCKED_SITE_COUNT</t>
+          <t>LOCKED_SITE</t>
         </is>
       </c>
       <c r="F432" s="3" t="inlineStr">
         <is>
-          <t>非实体装配/拓扑</t>
+          <t>参数化补全</t>
         </is>
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>NOT_PHYSICAL_MASTER</t>
+          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
         </is>
       </c>
       <c r="H432" s="3" t="inlineStr"/>
       <c r="I432" s="3" t="inlineStr">
         <is>
-          <t>附件1-9</t>
+          <t>附件1-9逐位记录</t>
         </is>
       </c>
       <c r="J432" s="3" t="inlineStr"/>
       <c r="K432" s="3" t="inlineStr"/>
       <c r="L432" s="3" t="inlineStr"/>
-      <c r="M432" s="3" t="inlineStr"/>
+      <c r="M432" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
       <c r="N432" s="3" t="inlineStr"/>
       <c r="O432" s="3" t="inlineStr"/>
       <c r="P432" s="3" t="inlineStr"/>
@@ -31185,12 +31218,12 @@
       <c r="S432" s="3" t="inlineStr"/>
       <c r="T432" s="3" t="inlineStr"/>
       <c r="U432" s="3" t="inlineStr"/>
-      <c r="V432" s="3" t="inlineStr"/>
-      <c r="W432" s="3" t="inlineStr">
-        <is>
-          <t>{"breakdown":"上下六椽栿间4；上六椽栿与四椽栿间4；下平槫下8；上平槫下4；脊槫下4"}</t>
-        </is>
-      </c>
+      <c r="V432" s="3" t="inlineStr">
+        <is>
+          <t>215.0×153.6mm不属于襻间枋统一截面</t>
+        </is>
+      </c>
+      <c r="W432" s="3" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="3" t="inlineStr">
@@ -31200,38 +31233,38 @@
       </c>
       <c r="B433" s="3" t="inlineStr">
         <is>
-          <t>替木测量边界</t>
+          <t>内槽斗栱/隔架位置</t>
         </is>
       </c>
       <c r="C433" s="3" t="inlineStr">
         <is>
-          <t>替木-测量边界</t>
+          <t>内槽位置总表</t>
         </is>
       </c>
       <c r="D433" s="3" t="inlineStr">
         <is>
-          <t>全殿多处</t>
+          <t>24处</t>
         </is>
       </c>
       <c r="E433" s="3" t="inlineStr">
         <is>
-          <t>MEASUREMENT_SAMPLE_NOT_TOTAL</t>
+          <t>LOCKED_SITE_COUNT</t>
         </is>
       </c>
       <c r="F433" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN/参考边界</t>
+          <t>非实体装配/拓扑</t>
         </is>
       </c>
       <c r="G433" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN_REFERENCE_BOUNDARY</t>
+          <t>NOT_PHYSICAL_MASTER</t>
         </is>
       </c>
       <c r="H433" s="3" t="inlineStr"/>
       <c r="I433" s="3" t="inlineStr">
         <is>
-          <t>附件1-8</t>
+          <t>附件1-9</t>
         </is>
       </c>
       <c r="J433" s="3" t="inlineStr"/>
@@ -31249,60 +31282,56 @@
       <c r="V433" s="3" t="inlineStr"/>
       <c r="W433" s="3" t="inlineStr">
         <is>
-          <t>{"mean_mm":{"asymmetric_half_exposed_length":680.1,"symmetric_length":1757,"thickness":151.8,"width":150.4},"measured_records":23,"total_count":"UNKNOWN"}</t>
+          <t>{"breakdown":"上下六椽栿间4；上六椽栿与四椽栿间4；下平槫下8；上平槫下4；脊槫下4"}</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="3" t="inlineStr">
         <is>
-          <t>屋面</t>
+          <t>内槽</t>
         </is>
       </c>
       <c r="B434" s="3" t="inlineStr">
         <is>
-          <t>椽系</t>
+          <t>替木测量边界</t>
         </is>
       </c>
       <c r="C434" s="3" t="inlineStr">
         <is>
-          <t>椽系-参数化补全</t>
+          <t>替木-测量边界</t>
         </is>
       </c>
       <c r="D434" s="3" t="inlineStr">
         <is>
-          <t>四坡及翼角</t>
+          <t>全殿多处</t>
         </is>
       </c>
       <c r="E434" s="3" t="inlineStr">
         <is>
-          <t>PARAMETRIC_COMPLETION</t>
+          <t>MEASUREMENT_SAMPLE_NOT_TOTAL</t>
         </is>
       </c>
       <c r="F434" s="3" t="inlineStr">
         <is>
-          <t>参数化补全</t>
+          <t>UNKNOWN/参考边界</t>
         </is>
       </c>
       <c r="G434" s="3" t="inlineStr">
         <is>
-          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
+          <t>UNKNOWN_REFERENCE_BOUNDARY</t>
         </is>
       </c>
       <c r="H434" s="3" t="inlineStr"/>
       <c r="I434" s="3" t="inlineStr">
         <is>
-          <t>测绘立剖面+槫位</t>
+          <t>附件1-8</t>
         </is>
       </c>
       <c r="J434" s="3" t="inlineStr"/>
       <c r="K434" s="3" t="inlineStr"/>
       <c r="L434" s="3" t="inlineStr"/>
-      <c r="M434" s="3" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
+      <c r="M434" s="3" t="inlineStr"/>
       <c r="N434" s="3" t="inlineStr"/>
       <c r="O434" s="3" t="inlineStr"/>
       <c r="P434" s="3" t="inlineStr"/>
@@ -31314,34 +31343,34 @@
       <c r="V434" s="3" t="inlineStr"/>
       <c r="W434" s="3" t="inlineStr">
         <is>
-          <t>{"real_count":"UNKNOWN","spacing":"UNKNOWN"}</t>
+          <t>{"mean_mm":{"asymmetric_half_exposed_length":680.1,"symmetric_length":1757,"thickness":151.8,"width":150.4},"measured_records":23,"total_count":"UNKNOWN"}</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="3" t="inlineStr">
         <is>
-          <t>瓦作</t>
+          <t>屋面</t>
         </is>
       </c>
       <c r="B435" s="3" t="inlineStr">
         <is>
-          <t>南坡筒瓦</t>
+          <t>椽系</t>
         </is>
       </c>
       <c r="C435" s="3" t="inlineStr">
         <is>
-          <t>南坡筒瓦-阵列</t>
+          <t>椽系-参数化补全</t>
         </is>
       </c>
       <c r="D435" s="3" t="inlineStr">
         <is>
-          <t>南坡</t>
+          <t>四坡及翼角</t>
         </is>
       </c>
       <c r="E435" s="3" t="inlineStr">
         <is>
-          <t>LOCKED_ARRAY</t>
+          <t>PARAMETRIC_COMPLETION</t>
         </is>
       </c>
       <c r="F435" s="3" t="inlineStr">
@@ -31357,13 +31386,17 @@
       <c r="H435" s="3" t="inlineStr"/>
       <c r="I435" s="3" t="inlineStr">
         <is>
-          <t>报告直接记录</t>
+          <t>测绘立剖面+槫位</t>
         </is>
       </c>
       <c r="J435" s="3" t="inlineStr"/>
       <c r="K435" s="3" t="inlineStr"/>
       <c r="L435" s="3" t="inlineStr"/>
-      <c r="M435" s="3" t="inlineStr"/>
+      <c r="M435" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
       <c r="N435" s="3" t="inlineStr"/>
       <c r="O435" s="3" t="inlineStr"/>
       <c r="P435" s="3" t="inlineStr"/>
@@ -31371,13 +31404,13 @@
       <c r="R435" s="3" t="inlineStr"/>
       <c r="S435" s="3" t="inlineStr"/>
       <c r="T435" s="3" t="inlineStr"/>
-      <c r="U435" s="3" t="inlineStr">
-        <is>
-          <t>62陇</t>
-        </is>
-      </c>
+      <c r="U435" s="3" t="inlineStr"/>
       <c r="V435" s="3" t="inlineStr"/>
-      <c r="W435" s="3" t="inlineStr"/>
+      <c r="W435" s="3" t="inlineStr">
+        <is>
+          <t>{"real_count":"UNKNOWN","spacing":"UNKNOWN"}</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="3" t="inlineStr">
@@ -31387,17 +31420,17 @@
       </c>
       <c r="B436" s="3" t="inlineStr">
         <is>
-          <t>北坡筒瓦</t>
+          <t>南坡筒瓦</t>
         </is>
       </c>
       <c r="C436" s="3" t="inlineStr">
         <is>
-          <t>北坡筒瓦-阵列</t>
+          <t>南坡筒瓦-阵列</t>
         </is>
       </c>
       <c r="D436" s="3" t="inlineStr">
         <is>
-          <t>北坡</t>
+          <t>南坡</t>
         </is>
       </c>
       <c r="E436" s="3" t="inlineStr">
@@ -31448,17 +31481,17 @@
       </c>
       <c r="B437" s="3" t="inlineStr">
         <is>
-          <t>东坡筒瓦</t>
+          <t>北坡筒瓦</t>
         </is>
       </c>
       <c r="C437" s="3" t="inlineStr">
         <is>
-          <t>东坡筒瓦-阵列</t>
+          <t>北坡筒瓦-阵列</t>
         </is>
       </c>
       <c r="D437" s="3" t="inlineStr">
         <is>
-          <t>东坡</t>
+          <t>北坡</t>
         </is>
       </c>
       <c r="E437" s="3" t="inlineStr">
@@ -31495,7 +31528,7 @@
       <c r="T437" s="3" t="inlineStr"/>
       <c r="U437" s="3" t="inlineStr">
         <is>
-          <t>91陇</t>
+          <t>62陇</t>
         </is>
       </c>
       <c r="V437" s="3" t="inlineStr"/>
@@ -31509,17 +31542,17 @@
       </c>
       <c r="B438" s="3" t="inlineStr">
         <is>
-          <t>西坡筒瓦</t>
+          <t>东坡筒瓦</t>
         </is>
       </c>
       <c r="C438" s="3" t="inlineStr">
         <is>
-          <t>西坡筒瓦-阵列</t>
+          <t>东坡筒瓦-阵列</t>
         </is>
       </c>
       <c r="D438" s="3" t="inlineStr">
         <is>
-          <t>西坡</t>
+          <t>东坡</t>
         </is>
       </c>
       <c r="E438" s="3" t="inlineStr">
@@ -31556,7 +31589,7 @@
       <c r="T438" s="3" t="inlineStr"/>
       <c r="U438" s="3" t="inlineStr">
         <is>
-          <t>90陇</t>
+          <t>91陇</t>
         </is>
       </c>
       <c r="V438" s="3" t="inlineStr"/>
@@ -31570,22 +31603,22 @@
       </c>
       <c r="B439" s="3" t="inlineStr">
         <is>
-          <t>正脊</t>
+          <t>西坡筒瓦</t>
         </is>
       </c>
       <c r="C439" s="3" t="inlineStr">
         <is>
-          <t>正脊-01</t>
+          <t>西坡筒瓦-阵列</t>
         </is>
       </c>
       <c r="D439" s="3" t="inlineStr">
         <is>
-          <t>屋脊</t>
+          <t>西坡</t>
         </is>
       </c>
       <c r="E439" s="3" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>LOCKED_ARRAY</t>
         </is>
       </c>
       <c r="F439" s="3" t="inlineStr">
@@ -31615,13 +31648,13 @@
       <c r="R439" s="3" t="inlineStr"/>
       <c r="S439" s="3" t="inlineStr"/>
       <c r="T439" s="3" t="inlineStr"/>
-      <c r="U439" s="3" t="inlineStr"/>
+      <c r="U439" s="3" t="inlineStr">
+        <is>
+          <t>90陇</t>
+        </is>
+      </c>
       <c r="V439" s="3" t="inlineStr"/>
-      <c r="W439" s="3" t="inlineStr">
-        <is>
-          <t>{"chijiao_tongji":17,"count":1}</t>
-        </is>
-      </c>
+      <c r="W439" s="3" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="3" t="inlineStr">
@@ -31631,22 +31664,22 @@
       </c>
       <c r="B440" s="3" t="inlineStr">
         <is>
-          <t>垂脊</t>
+          <t>正脊</t>
         </is>
       </c>
       <c r="C440" s="3" t="inlineStr">
         <is>
-          <t>垂脊-01</t>
+          <t>正脊-01</t>
         </is>
       </c>
       <c r="D440" s="3" t="inlineStr">
         <is>
-          <t>垂脊01</t>
+          <t>屋脊</t>
         </is>
       </c>
       <c r="E440" s="3" t="inlineStr">
         <is>
-          <t>LOCKED_DERIVED</t>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="F440" s="3" t="inlineStr">
@@ -31662,7 +31695,7 @@
       <c r="H440" s="3" t="inlineStr"/>
       <c r="I440" s="3" t="inlineStr">
         <is>
-          <t>四条脊+单条构造语境</t>
+          <t>报告直接记录</t>
         </is>
       </c>
       <c r="J440" s="3" t="inlineStr"/>
@@ -31680,7 +31713,7 @@
       <c r="V440" s="3" t="inlineStr"/>
       <c r="W440" s="3" t="inlineStr">
         <is>
-          <t>{"tongji_per_ridge":20}</t>
+          <t>{"chijiao_tongji":17,"count":1}</t>
         </is>
       </c>
     </row>
@@ -31697,12 +31730,12 @@
       </c>
       <c r="C441" s="3" t="inlineStr">
         <is>
-          <t>垂脊-02</t>
+          <t>垂脊-01</t>
         </is>
       </c>
       <c r="D441" s="3" t="inlineStr">
         <is>
-          <t>垂脊02</t>
+          <t>垂脊01</t>
         </is>
       </c>
       <c r="E441" s="3" t="inlineStr">
@@ -31758,12 +31791,12 @@
       </c>
       <c r="C442" s="3" t="inlineStr">
         <is>
-          <t>垂脊-03</t>
+          <t>垂脊-02</t>
         </is>
       </c>
       <c r="D442" s="3" t="inlineStr">
         <is>
-          <t>垂脊03</t>
+          <t>垂脊02</t>
         </is>
       </c>
       <c r="E442" s="3" t="inlineStr">
@@ -31819,12 +31852,12 @@
       </c>
       <c r="C443" s="3" t="inlineStr">
         <is>
-          <t>垂脊-04</t>
+          <t>垂脊-03</t>
         </is>
       </c>
       <c r="D443" s="3" t="inlineStr">
         <is>
-          <t>垂脊04</t>
+          <t>垂脊03</t>
         </is>
       </c>
       <c r="E443" s="3" t="inlineStr">
@@ -31875,17 +31908,17 @@
       </c>
       <c r="B444" s="3" t="inlineStr">
         <is>
-          <t>戗脊</t>
+          <t>垂脊</t>
         </is>
       </c>
       <c r="C444" s="3" t="inlineStr">
         <is>
-          <t>戗脊-01</t>
+          <t>垂脊-04</t>
         </is>
       </c>
       <c r="D444" s="3" t="inlineStr">
         <is>
-          <t>戗脊01</t>
+          <t>垂脊04</t>
         </is>
       </c>
       <c r="E444" s="3" t="inlineStr">
@@ -31924,7 +31957,7 @@
       <c r="V444" s="3" t="inlineStr"/>
       <c r="W444" s="3" t="inlineStr">
         <is>
-          <t>{"tongji_per_ridge":"5-6 + 找头"}</t>
+          <t>{"tongji_per_ridge":20}</t>
         </is>
       </c>
     </row>
@@ -31941,12 +31974,12 @@
       </c>
       <c r="C445" s="3" t="inlineStr">
         <is>
-          <t>戗脊-02</t>
+          <t>戗脊-01</t>
         </is>
       </c>
       <c r="D445" s="3" t="inlineStr">
         <is>
-          <t>戗脊02</t>
+          <t>戗脊01</t>
         </is>
       </c>
       <c r="E445" s="3" t="inlineStr">
@@ -32002,12 +32035,12 @@
       </c>
       <c r="C446" s="3" t="inlineStr">
         <is>
-          <t>戗脊-03</t>
+          <t>戗脊-02</t>
         </is>
       </c>
       <c r="D446" s="3" t="inlineStr">
         <is>
-          <t>戗脊03</t>
+          <t>戗脊02</t>
         </is>
       </c>
       <c r="E446" s="3" t="inlineStr">
@@ -32063,12 +32096,12 @@
       </c>
       <c r="C447" s="3" t="inlineStr">
         <is>
-          <t>戗脊-04</t>
+          <t>戗脊-03</t>
         </is>
       </c>
       <c r="D447" s="3" t="inlineStr">
         <is>
-          <t>戗脊04</t>
+          <t>戗脊03</t>
         </is>
       </c>
       <c r="E447" s="3" t="inlineStr">
@@ -32114,43 +32147,43 @@
     <row r="448">
       <c r="A448" s="3" t="inlineStr">
         <is>
-          <t>台基</t>
+          <t>瓦作</t>
         </is>
       </c>
       <c r="B448" s="3" t="inlineStr">
         <is>
-          <t>台基整体</t>
+          <t>戗脊</t>
         </is>
       </c>
       <c r="C448" s="3" t="inlineStr">
         <is>
-          <t>台基-01</t>
+          <t>戗脊-04</t>
         </is>
       </c>
       <c r="D448" s="3" t="inlineStr">
         <is>
-          <t>万佛殿主体下方</t>
+          <t>戗脊04</t>
         </is>
       </c>
       <c r="E448" s="3" t="inlineStr">
         <is>
-          <t>LOCKED_OUTER_UNKNOWN_INTERNAL</t>
+          <t>LOCKED_DERIVED</t>
         </is>
       </c>
       <c r="F448" s="3" t="inlineStr">
         <is>
-          <t>简化Proxy</t>
+          <t>参数化补全</t>
         </is>
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>SIMPLIFIED_PROXY</t>
+          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
         </is>
       </c>
       <c r="H448" s="3" t="inlineStr"/>
       <c r="I448" s="3" t="inlineStr">
         <is>
-          <t>报告直接记录</t>
+          <t>四条脊+单条构造语境</t>
         </is>
       </c>
       <c r="J448" s="3" t="inlineStr"/>
@@ -32168,7 +32201,7 @@
       <c r="V448" s="3" t="inlineStr"/>
       <c r="W448" s="3" t="inlineStr">
         <is>
-          <t>{"internal_structure":"UNKNOWN"}</t>
+          <t>{"tongji_per_ridge":"5-6 + 找头"}</t>
         </is>
       </c>
     </row>
@@ -32180,22 +32213,22 @@
       </c>
       <c r="B449" s="3" t="inlineStr">
         <is>
-          <t>角石</t>
+          <t>台基整体</t>
         </is>
       </c>
       <c r="C449" s="3" t="inlineStr">
         <is>
-          <t>台基角石-西北</t>
+          <t>台基-01</t>
         </is>
       </c>
       <c r="D449" s="3" t="inlineStr">
         <is>
-          <t>西北转角</t>
+          <t>万佛殿主体下方</t>
         </is>
       </c>
       <c r="E449" s="3" t="inlineStr">
         <is>
-          <t>LOCKED_DERIVED</t>
+          <t>LOCKED_OUTER_UNKNOWN_INTERNAL</t>
         </is>
       </c>
       <c r="F449" s="3" t="inlineStr">
@@ -32211,7 +32244,7 @@
       <c r="H449" s="3" t="inlineStr"/>
       <c r="I449" s="3" t="inlineStr">
         <is>
-          <t>转角处施角石+矩形拓扑</t>
+          <t>报告直接记录</t>
         </is>
       </c>
       <c r="J449" s="3" t="inlineStr"/>
@@ -32227,7 +32260,11 @@
       <c r="T449" s="3" t="inlineStr"/>
       <c r="U449" s="3" t="inlineStr"/>
       <c r="V449" s="3" t="inlineStr"/>
-      <c r="W449" s="3" t="inlineStr"/>
+      <c r="W449" s="3" t="inlineStr">
+        <is>
+          <t>{"internal_structure":"UNKNOWN"}</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="3" t="inlineStr">
@@ -32242,12 +32279,12 @@
       </c>
       <c r="C450" s="3" t="inlineStr">
         <is>
-          <t>台基角石-东北</t>
+          <t>台基角石-西北</t>
         </is>
       </c>
       <c r="D450" s="3" t="inlineStr">
         <is>
-          <t>东北转角</t>
+          <t>西北转角</t>
         </is>
       </c>
       <c r="E450" s="3" t="inlineStr">
@@ -32299,12 +32336,12 @@
       </c>
       <c r="C451" s="3" t="inlineStr">
         <is>
-          <t>台基角石-东南</t>
+          <t>台基角石-东北</t>
         </is>
       </c>
       <c r="D451" s="3" t="inlineStr">
         <is>
-          <t>东南转角</t>
+          <t>东北转角</t>
         </is>
       </c>
       <c r="E451" s="3" t="inlineStr">
@@ -32356,12 +32393,12 @@
       </c>
       <c r="C452" s="3" t="inlineStr">
         <is>
-          <t>台基角石-西南</t>
+          <t>台基角石-东南</t>
         </is>
       </c>
       <c r="D452" s="3" t="inlineStr">
         <is>
-          <t>西南转角</t>
+          <t>东南转角</t>
         </is>
       </c>
       <c r="E452" s="3" t="inlineStr">
@@ -32403,43 +32440,43 @@
     <row r="453">
       <c r="A453" s="3" t="inlineStr">
         <is>
-          <t>围护</t>
+          <t>台基</t>
         </is>
       </c>
       <c r="B453" s="3" t="inlineStr">
         <is>
-          <t>南门洞</t>
+          <t>角石</t>
         </is>
       </c>
       <c r="C453" s="3" t="inlineStr">
         <is>
-          <t>门洞-南-中央</t>
+          <t>台基角石-西南</t>
         </is>
       </c>
       <c r="D453" s="3" t="inlineStr">
         <is>
-          <t>南立面中央</t>
+          <t>西南转角</t>
         </is>
       </c>
       <c r="E453" s="3" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>LOCKED_DERIVED</t>
         </is>
       </c>
       <c r="F453" s="3" t="inlineStr">
         <is>
-          <t>参数化补全</t>
+          <t>简化Proxy</t>
         </is>
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
+          <t>SIMPLIFIED_PROXY</t>
         </is>
       </c>
       <c r="H453" s="3" t="inlineStr"/>
       <c r="I453" s="3" t="inlineStr">
         <is>
-          <t>报告直接记录</t>
+          <t>转角处施角石+矩形拓扑</t>
         </is>
       </c>
       <c r="J453" s="3" t="inlineStr"/>
@@ -32455,11 +32492,7 @@
       <c r="T453" s="3" t="inlineStr"/>
       <c r="U453" s="3" t="inlineStr"/>
       <c r="V453" s="3" t="inlineStr"/>
-      <c r="W453" s="3" t="inlineStr">
-        <is>
-          <t>{"woodwork":"VISUAL_MODEL + PARAMETRIC_SECTION"}</t>
-        </is>
-      </c>
+      <c r="W453" s="3" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="3" t="inlineStr">
@@ -32469,17 +32502,17 @@
       </c>
       <c r="B454" s="3" t="inlineStr">
         <is>
-          <t>北门洞</t>
+          <t>南门洞</t>
         </is>
       </c>
       <c r="C454" s="3" t="inlineStr">
         <is>
-          <t>门洞-北-中央</t>
+          <t>门洞-南-中央</t>
         </is>
       </c>
       <c r="D454" s="3" t="inlineStr">
         <is>
-          <t>北立面中央</t>
+          <t>南立面中央</t>
         </is>
       </c>
       <c r="E454" s="3" t="inlineStr">
@@ -32530,17 +32563,17 @@
       </c>
       <c r="B455" s="3" t="inlineStr">
         <is>
-          <t>南立面窗洞</t>
+          <t>北门洞</t>
         </is>
       </c>
       <c r="C455" s="3" t="inlineStr">
         <is>
-          <t>窗洞-南-东窗</t>
+          <t>门洞-北-中央</t>
         </is>
       </c>
       <c r="D455" s="3" t="inlineStr">
         <is>
-          <t>南立面东窗</t>
+          <t>北立面中央</t>
         </is>
       </c>
       <c r="E455" s="3" t="inlineStr">
@@ -32579,7 +32612,7 @@
       <c r="V455" s="3" t="inlineStr"/>
       <c r="W455" s="3" t="inlineStr">
         <is>
-          <t>{"outer_wall_cm":84}</t>
+          <t>{"woodwork":"VISUAL_MODEL + PARAMETRIC_SECTION"}</t>
         </is>
       </c>
     </row>
@@ -32596,12 +32629,12 @@
       </c>
       <c r="C456" s="3" t="inlineStr">
         <is>
-          <t>窗洞-南-西窗</t>
+          <t>窗洞-南-东窗</t>
         </is>
       </c>
       <c r="D456" s="3" t="inlineStr">
         <is>
-          <t>南立面西窗</t>
+          <t>南立面东窗</t>
         </is>
       </c>
       <c r="E456" s="3" t="inlineStr">
@@ -32640,7 +32673,7 @@
       <c r="V456" s="3" t="inlineStr"/>
       <c r="W456" s="3" t="inlineStr">
         <is>
-          <t>{"outer_wall_cm":101}</t>
+          <t>{"outer_wall_cm":84}</t>
         </is>
       </c>
     </row>
@@ -32652,22 +32685,22 @@
       </c>
       <c r="B457" s="3" t="inlineStr">
         <is>
-          <t>透风孔</t>
+          <t>南立面窗洞</t>
         </is>
       </c>
       <c r="C457" s="3" t="inlineStr">
         <is>
-          <t>透风孔-01</t>
+          <t>窗洞-南-西窗</t>
         </is>
       </c>
       <c r="D457" s="3" t="inlineStr">
         <is>
-          <t>四立面柱位；具体纹样见V007证据文档</t>
+          <t>南立面西窗</t>
         </is>
       </c>
       <c r="E457" s="3" t="inlineStr">
         <is>
-          <t>LOCKED_SITE_PATTERN</t>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="F457" s="3" t="inlineStr">
@@ -32683,7 +32716,7 @@
       <c r="H457" s="3" t="inlineStr"/>
       <c r="I457" s="3" t="inlineStr">
         <is>
-          <t>报告直接记录+柱网展开</t>
+          <t>报告直接记录</t>
         </is>
       </c>
       <c r="J457" s="3" t="inlineStr"/>
@@ -32699,7 +32732,11 @@
       <c r="T457" s="3" t="inlineStr"/>
       <c r="U457" s="3" t="inlineStr"/>
       <c r="V457" s="3" t="inlineStr"/>
-      <c r="W457" s="3" t="inlineStr"/>
+      <c r="W457" s="3" t="inlineStr">
+        <is>
+          <t>{"outer_wall_cm":101}</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="3" t="inlineStr">
@@ -32714,7 +32751,7 @@
       </c>
       <c r="C458" s="3" t="inlineStr">
         <is>
-          <t>透风孔-02</t>
+          <t>透风孔-01</t>
         </is>
       </c>
       <c r="D458" s="3" t="inlineStr">
@@ -32771,7 +32808,7 @@
       </c>
       <c r="C459" s="3" t="inlineStr">
         <is>
-          <t>透风孔-03</t>
+          <t>透风孔-02</t>
         </is>
       </c>
       <c r="D459" s="3" t="inlineStr">
@@ -32828,7 +32865,7 @@
       </c>
       <c r="C460" s="3" t="inlineStr">
         <is>
-          <t>透风孔-04</t>
+          <t>透风孔-03</t>
         </is>
       </c>
       <c r="D460" s="3" t="inlineStr">
@@ -32885,7 +32922,7 @@
       </c>
       <c r="C461" s="3" t="inlineStr">
         <is>
-          <t>透风孔-05</t>
+          <t>透风孔-04</t>
         </is>
       </c>
       <c r="D461" s="3" t="inlineStr">
@@ -32942,7 +32979,7 @@
       </c>
       <c r="C462" s="3" t="inlineStr">
         <is>
-          <t>透风孔-06</t>
+          <t>透风孔-05</t>
         </is>
       </c>
       <c r="D462" s="3" t="inlineStr">
@@ -32999,7 +33036,7 @@
       </c>
       <c r="C463" s="3" t="inlineStr">
         <is>
-          <t>透风孔-07</t>
+          <t>透风孔-06</t>
         </is>
       </c>
       <c r="D463" s="3" t="inlineStr">
@@ -33056,7 +33093,7 @@
       </c>
       <c r="C464" s="3" t="inlineStr">
         <is>
-          <t>透风孔-08</t>
+          <t>透风孔-07</t>
         </is>
       </c>
       <c r="D464" s="3" t="inlineStr">
@@ -33113,7 +33150,7 @@
       </c>
       <c r="C465" s="3" t="inlineStr">
         <is>
-          <t>透风孔-09</t>
+          <t>透风孔-08</t>
         </is>
       </c>
       <c r="D465" s="3" t="inlineStr">
@@ -33170,7 +33207,7 @@
       </c>
       <c r="C466" s="3" t="inlineStr">
         <is>
-          <t>透风孔-10</t>
+          <t>透风孔-09</t>
         </is>
       </c>
       <c r="D466" s="3" t="inlineStr">
@@ -33227,7 +33264,7 @@
       </c>
       <c r="C467" s="3" t="inlineStr">
         <is>
-          <t>透风孔-11</t>
+          <t>透风孔-10</t>
         </is>
       </c>
       <c r="D467" s="3" t="inlineStr">
@@ -33284,7 +33321,7 @@
       </c>
       <c r="C468" s="3" t="inlineStr">
         <is>
-          <t>透风孔-12</t>
+          <t>透风孔-11</t>
         </is>
       </c>
       <c r="D468" s="3" t="inlineStr">
@@ -33341,7 +33378,7 @@
       </c>
       <c r="C469" s="3" t="inlineStr">
         <is>
-          <t>透风孔-13</t>
+          <t>透风孔-12</t>
         </is>
       </c>
       <c r="D469" s="3" t="inlineStr">
@@ -33398,7 +33435,7 @@
       </c>
       <c r="C470" s="3" t="inlineStr">
         <is>
-          <t>透风孔-14</t>
+          <t>透风孔-13</t>
         </is>
       </c>
       <c r="D470" s="3" t="inlineStr">
@@ -33455,7 +33492,7 @@
       </c>
       <c r="C471" s="3" t="inlineStr">
         <is>
-          <t>透风孔-15</t>
+          <t>透风孔-14</t>
         </is>
       </c>
       <c r="D471" s="3" t="inlineStr">
@@ -33512,7 +33549,7 @@
       </c>
       <c r="C472" s="3" t="inlineStr">
         <is>
-          <t>透风孔-16</t>
+          <t>透风孔-15</t>
         </is>
       </c>
       <c r="D472" s="3" t="inlineStr">
@@ -33564,38 +33601,38 @@
       </c>
       <c r="B473" s="3" t="inlineStr">
         <is>
-          <t>嵌墙石碑</t>
+          <t>透风孔</t>
         </is>
       </c>
       <c r="C473" s="3" t="inlineStr">
         <is>
-          <t>石碑-大门西侧</t>
+          <t>透风孔-16</t>
         </is>
       </c>
       <c r="D473" s="3" t="inlineStr">
         <is>
-          <t>南立面大门西侧</t>
+          <t>四立面柱位；具体纹样见V007证据文档</t>
         </is>
       </c>
       <c r="E473" s="3" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>LOCKED_SITE_PATTERN</t>
         </is>
       </c>
       <c r="F473" s="3" t="inlineStr">
         <is>
-          <t>简化Proxy</t>
+          <t>参数化补全</t>
         </is>
       </c>
       <c r="G473" s="3" t="inlineStr">
         <is>
-          <t>SIMPLIFIED_PROXY</t>
+          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
         </is>
       </c>
       <c r="H473" s="3" t="inlineStr"/>
       <c r="I473" s="3" t="inlineStr">
         <is>
-          <t>报告直接记录</t>
+          <t>报告直接记录+柱网展开</t>
         </is>
       </c>
       <c r="J473" s="3" t="inlineStr"/>
@@ -33626,12 +33663,12 @@
       </c>
       <c r="C474" s="3" t="inlineStr">
         <is>
-          <t>石碑-大门东侧</t>
+          <t>石碑-大门西侧</t>
         </is>
       </c>
       <c r="D474" s="3" t="inlineStr">
         <is>
-          <t>南立面大门东侧</t>
+          <t>南立面大门西侧</t>
         </is>
       </c>
       <c r="E474" s="3" t="inlineStr">
@@ -33678,38 +33715,38 @@
       </c>
       <c r="B475" s="3" t="inlineStr">
         <is>
-          <t>墙体</t>
+          <t>嵌墙石碑</t>
         </is>
       </c>
       <c r="C475" s="3" t="inlineStr">
         <is>
-          <t>墙体-南立面</t>
+          <t>石碑-大门东侧</t>
         </is>
       </c>
       <c r="D475" s="3" t="inlineStr">
         <is>
-          <t>南立面</t>
+          <t>南立面大门东侧</t>
         </is>
       </c>
       <c r="E475" s="3" t="inlineStr">
         <is>
-          <t>SYSTEM_PARAMETRIC</t>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="F475" s="3" t="inlineStr">
         <is>
-          <t>参数化补全</t>
+          <t>简化Proxy</t>
         </is>
       </c>
       <c r="G475" s="3" t="inlineStr">
         <is>
-          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
+          <t>SIMPLIFIED_PROXY</t>
         </is>
       </c>
       <c r="H475" s="3" t="inlineStr"/>
       <c r="I475" s="3" t="inlineStr">
         <is>
-          <t>V007：墙体砌筑与南墙局部厚度已记录</t>
+          <t>报告直接记录</t>
         </is>
       </c>
       <c r="J475" s="3" t="inlineStr"/>
@@ -33724,16 +33761,8 @@
       <c r="S475" s="3" t="inlineStr"/>
       <c r="T475" s="3" t="inlineStr"/>
       <c r="U475" s="3" t="inlineStr"/>
-      <c r="V475" s="3" t="inlineStr">
-        <is>
-          <t>墙砖均值277.4×134×63.1mm；南墙局部厚约820–880mm，仅局部适用</t>
-        </is>
-      </c>
-      <c r="W475" s="3" t="inlineStr">
-        <is>
-          <t>{"record_role":"SYSTEM"}</t>
-        </is>
-      </c>
+      <c r="V475" s="3" t="inlineStr"/>
+      <c r="W475" s="3" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="3" t="inlineStr">
@@ -33748,12 +33777,12 @@
       </c>
       <c r="C476" s="3" t="inlineStr">
         <is>
-          <t>墙体-北立面</t>
+          <t>墙体-南立面</t>
         </is>
       </c>
       <c r="D476" s="3" t="inlineStr">
         <is>
-          <t>北立面</t>
+          <t>南立面</t>
         </is>
       </c>
       <c r="E476" s="3" t="inlineStr">
@@ -33774,7 +33803,7 @@
       <c r="H476" s="3" t="inlineStr"/>
       <c r="I476" s="3" t="inlineStr">
         <is>
-          <t>V007：四立面墙体砌筑系统</t>
+          <t>V007：墙体砌筑与南墙局部厚度已记录</t>
         </is>
       </c>
       <c r="J476" s="3" t="inlineStr"/>
@@ -33791,7 +33820,7 @@
       <c r="U476" s="3" t="inlineStr"/>
       <c r="V476" s="3" t="inlineStr">
         <is>
-          <t>不得套用南墙局部820–880mm厚度</t>
+          <t>墙砖均值277.4×134×63.1mm；南墙局部厚约820–880mm，仅局部适用</t>
         </is>
       </c>
       <c r="W476" s="3" t="inlineStr">
@@ -33813,12 +33842,12 @@
       </c>
       <c r="C477" s="3" t="inlineStr">
         <is>
-          <t>墙体-东立面</t>
+          <t>墙体-北立面</t>
         </is>
       </c>
       <c r="D477" s="3" t="inlineStr">
         <is>
-          <t>东立面</t>
+          <t>北立面</t>
         </is>
       </c>
       <c r="E477" s="3" t="inlineStr">
@@ -33856,7 +33885,7 @@
       <c r="U477" s="3" t="inlineStr"/>
       <c r="V477" s="3" t="inlineStr">
         <is>
-          <t>连续墙体/透风孔关系；统一墙厚UNKNOWN</t>
+          <t>不得套用南墙局部820–880mm厚度</t>
         </is>
       </c>
       <c r="W477" s="3" t="inlineStr">
@@ -33878,12 +33907,12 @@
       </c>
       <c r="C478" s="3" t="inlineStr">
         <is>
-          <t>墙体-西立面</t>
+          <t>墙体-东立面</t>
         </is>
       </c>
       <c r="D478" s="3" t="inlineStr">
         <is>
-          <t>西立面</t>
+          <t>东立面</t>
         </is>
       </c>
       <c r="E478" s="3" t="inlineStr">
@@ -33938,22 +33967,22 @@
       </c>
       <c r="B479" s="3" t="inlineStr">
         <is>
-          <t>墙砖族</t>
+          <t>墙体</t>
         </is>
       </c>
       <c r="C479" s="3" t="inlineStr">
         <is>
-          <t>墙砖族-UNKNOWN</t>
+          <t>墙体-西立面</t>
         </is>
       </c>
       <c r="D479" s="3" t="inlineStr">
         <is>
-          <t>四立面墙体</t>
+          <t>西立面</t>
         </is>
       </c>
       <c r="E479" s="3" t="inlineStr">
         <is>
-          <t>FAMILY_UNKNOWN_COUNT</t>
+          <t>SYSTEM_PARAMETRIC</t>
         </is>
       </c>
       <c r="F479" s="3" t="inlineStr">
@@ -33969,7 +33998,7 @@
       <c r="H479" s="3" t="inlineStr"/>
       <c r="I479" s="3" t="inlineStr">
         <is>
-          <t>V007墙砖样本统计</t>
+          <t>V007：四立面墙体砌筑系统</t>
         </is>
       </c>
       <c r="J479" s="3" t="inlineStr"/>
@@ -33977,48 +34006,48 @@
       <c r="L479" s="3" t="inlineStr"/>
       <c r="M479" s="3" t="inlineStr"/>
       <c r="N479" s="3" t="inlineStr"/>
-      <c r="O479" s="3" t="inlineStr">
-        <is>
-          <t>均值277.4×134×63.1</t>
-        </is>
-      </c>
+      <c r="O479" s="3" t="inlineStr"/>
       <c r="P479" s="3" t="inlineStr"/>
       <c r="Q479" s="3" t="inlineStr"/>
       <c r="R479" s="3" t="inlineStr"/>
       <c r="S479" s="3" t="inlineStr"/>
       <c r="T479" s="3" t="inlineStr"/>
       <c r="U479" s="3" t="inlineStr"/>
-      <c r="V479" s="3" t="inlineStr"/>
+      <c r="V479" s="3" t="inlineStr">
+        <is>
+          <t>连续墙体/透风孔关系；统一墙厚UNKNOWN</t>
+        </is>
+      </c>
       <c r="W479" s="3" t="inlineStr">
         <is>
-          <t>{"record_role":"FAMILY_UNKNOWN_COUNT","total_count":"UNKNOWN"}</t>
+          <t>{"record_role":"SYSTEM"}</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="3" t="inlineStr">
         <is>
-          <t>室内地面</t>
+          <t>围护</t>
         </is>
       </c>
       <c r="B480" s="3" t="inlineStr">
         <is>
-          <t>室内地面系统</t>
+          <t>墙砖族</t>
         </is>
       </c>
       <c r="C480" s="3" t="inlineStr">
         <is>
-          <t>室内地面-01</t>
+          <t>墙砖族-UNKNOWN</t>
         </is>
       </c>
       <c r="D480" s="3" t="inlineStr">
         <is>
-          <t>万佛殿室内</t>
+          <t>四立面墙体</t>
         </is>
       </c>
       <c r="E480" s="3" t="inlineStr">
         <is>
-          <t>SYSTEM_PARAMETRIC</t>
+          <t>FAMILY_UNKNOWN_COUNT</t>
         </is>
       </c>
       <c r="F480" s="3" t="inlineStr">
@@ -34034,7 +34063,7 @@
       <c r="H480" s="3" t="inlineStr"/>
       <c r="I480" s="3" t="inlineStr">
         <is>
-          <t>V007地面铺砖记录</t>
+          <t>V007墙砖样本统计</t>
         </is>
       </c>
       <c r="J480" s="3" t="inlineStr"/>
@@ -34042,7 +34071,11 @@
       <c r="L480" s="3" t="inlineStr"/>
       <c r="M480" s="3" t="inlineStr"/>
       <c r="N480" s="3" t="inlineStr"/>
-      <c r="O480" s="3" t="inlineStr"/>
+      <c r="O480" s="3" t="inlineStr">
+        <is>
+          <t>均值277.4×134×63.1</t>
+        </is>
+      </c>
       <c r="P480" s="3" t="inlineStr"/>
       <c r="Q480" s="3" t="inlineStr"/>
       <c r="R480" s="3" t="inlineStr"/>
@@ -34052,7 +34085,7 @@
       <c r="V480" s="3" t="inlineStr"/>
       <c r="W480" s="3" t="inlineStr">
         <is>
-          <t>{"record_role":"SYSTEM"}</t>
+          <t>{"record_role":"FAMILY_UNKNOWN_COUNT","total_count":"UNKNOWN"}</t>
         </is>
       </c>
     </row>
@@ -34064,22 +34097,22 @@
       </c>
       <c r="B481" s="3" t="inlineStr">
         <is>
-          <t>室内条砖族</t>
+          <t>室内地面系统</t>
         </is>
       </c>
       <c r="C481" s="3" t="inlineStr">
         <is>
-          <t>室内条砖族-UNKNOWN</t>
+          <t>室内地面-01</t>
         </is>
       </c>
       <c r="D481" s="3" t="inlineStr">
         <is>
-          <t>室内地面边界/区域</t>
+          <t>万佛殿室内</t>
         </is>
       </c>
       <c r="E481" s="3" t="inlineStr">
         <is>
-          <t>FAMILY_UNKNOWN_COUNT</t>
+          <t>SYSTEM_PARAMETRIC</t>
         </is>
       </c>
       <c r="F481" s="3" t="inlineStr">
@@ -34095,7 +34128,7 @@
       <c r="H481" s="3" t="inlineStr"/>
       <c r="I481" s="3" t="inlineStr">
         <is>
-          <t>V007条砖统计</t>
+          <t>V007地面铺砖记录</t>
         </is>
       </c>
       <c r="J481" s="3" t="inlineStr"/>
@@ -34103,11 +34136,7 @@
       <c r="L481" s="3" t="inlineStr"/>
       <c r="M481" s="3" t="inlineStr"/>
       <c r="N481" s="3" t="inlineStr"/>
-      <c r="O481" s="3" t="inlineStr">
-        <is>
-          <t>约277.9×133.3；厚UNKNOWN</t>
-        </is>
-      </c>
+      <c r="O481" s="3" t="inlineStr"/>
       <c r="P481" s="3" t="inlineStr"/>
       <c r="Q481" s="3" t="inlineStr"/>
       <c r="R481" s="3" t="inlineStr"/>
@@ -34117,7 +34146,7 @@
       <c r="V481" s="3" t="inlineStr"/>
       <c r="W481" s="3" t="inlineStr">
         <is>
-          <t>{"record_role":"FAMILY_UNKNOWN_COUNT","total_count":"UNKNOWN"}</t>
+          <t>{"record_role":"SYSTEM"}</t>
         </is>
       </c>
     </row>
@@ -34129,17 +34158,17 @@
       </c>
       <c r="B482" s="3" t="inlineStr">
         <is>
-          <t>室内方砖族</t>
+          <t>室内条砖族</t>
         </is>
       </c>
       <c r="C482" s="3" t="inlineStr">
         <is>
-          <t>室内方砖-265型-UNKNOWN</t>
+          <t>室内条砖族-UNKNOWN</t>
         </is>
       </c>
       <c r="D482" s="3" t="inlineStr">
         <is>
-          <t>室内地面部分区域</t>
+          <t>室内地面边界/区域</t>
         </is>
       </c>
       <c r="E482" s="3" t="inlineStr">
@@ -34160,7 +34189,7 @@
       <c r="H482" s="3" t="inlineStr"/>
       <c r="I482" s="3" t="inlineStr">
         <is>
-          <t>V007方砖类型记录</t>
+          <t>V007条砖统计</t>
         </is>
       </c>
       <c r="J482" s="3" t="inlineStr"/>
@@ -34170,7 +34199,7 @@
       <c r="N482" s="3" t="inlineStr"/>
       <c r="O482" s="3" t="inlineStr">
         <is>
-          <t>约265×265；厚UNKNOWN</t>
+          <t>约277.9×133.3；厚UNKNOWN</t>
         </is>
       </c>
       <c r="P482" s="3" t="inlineStr"/>
@@ -34199,7 +34228,7 @@
       </c>
       <c r="C483" s="3" t="inlineStr">
         <is>
-          <t>室内方砖-315x305型-UNKNOWN</t>
+          <t>室内方砖-265型-UNKNOWN</t>
         </is>
       </c>
       <c r="D483" s="3" t="inlineStr">
@@ -34235,7 +34264,7 @@
       <c r="N483" s="3" t="inlineStr"/>
       <c r="O483" s="3" t="inlineStr">
         <is>
-          <t>约315×305；厚UNKNOWN</t>
+          <t>约265×265；厚UNKNOWN</t>
         </is>
       </c>
       <c r="P483" s="3" t="inlineStr"/>
@@ -34254,27 +34283,27 @@
     <row r="484">
       <c r="A484" s="3" t="inlineStr">
         <is>
-          <t>室内设施</t>
+          <t>室内地面</t>
         </is>
       </c>
       <c r="B484" s="3" t="inlineStr">
         <is>
-          <t>神台</t>
+          <t>室内方砖族</t>
         </is>
       </c>
       <c r="C484" s="3" t="inlineStr">
         <is>
-          <t>神台-01</t>
+          <t>室内方砖-315x305型-UNKNOWN</t>
         </is>
       </c>
       <c r="D484" s="3" t="inlineStr">
         <is>
-          <t>殿内中央区域</t>
+          <t>室内地面部分区域</t>
         </is>
       </c>
       <c r="E484" s="3" t="inlineStr">
         <is>
-          <t>SYSTEM_UNKNOWN_OVERALL_DIMENSIONS</t>
+          <t>FAMILY_UNKNOWN_COUNT</t>
         </is>
       </c>
       <c r="F484" s="3" t="inlineStr">
@@ -34290,7 +34319,7 @@
       <c r="H484" s="3" t="inlineStr"/>
       <c r="I484" s="3" t="inlineStr">
         <is>
-          <t>V007神台铺砖构造记录</t>
+          <t>V007方砖类型记录</t>
         </is>
       </c>
       <c r="J484" s="3" t="inlineStr"/>
@@ -34298,48 +34327,48 @@
       <c r="L484" s="3" t="inlineStr"/>
       <c r="M484" s="3" t="inlineStr"/>
       <c r="N484" s="3" t="inlineStr"/>
-      <c r="O484" s="3" t="inlineStr"/>
+      <c r="O484" s="3" t="inlineStr">
+        <is>
+          <t>约315×305；厚UNKNOWN</t>
+        </is>
+      </c>
       <c r="P484" s="3" t="inlineStr"/>
       <c r="Q484" s="3" t="inlineStr"/>
       <c r="R484" s="3" t="inlineStr"/>
       <c r="S484" s="3" t="inlineStr"/>
       <c r="T484" s="3" t="inlineStr"/>
       <c r="U484" s="3" t="inlineStr"/>
-      <c r="V484" s="3" t="inlineStr">
-        <is>
-          <t>四周条砖立砌压脚、表面方砖；整体长宽高UNKNOWN</t>
-        </is>
-      </c>
+      <c r="V484" s="3" t="inlineStr"/>
       <c r="W484" s="3" t="inlineStr">
         <is>
-          <t>{"record_role":"SYSTEM"}</t>
+          <t>{"record_role":"FAMILY_UNKNOWN_COUNT","total_count":"UNKNOWN"}</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="3" t="inlineStr">
         <is>
-          <t>屋面</t>
+          <t>室内设施</t>
         </is>
       </c>
       <c r="B485" s="3" t="inlineStr">
         <is>
-          <t>望板系统</t>
+          <t>神台</t>
         </is>
       </c>
       <c r="C485" s="3" t="inlineStr">
         <is>
-          <t>望板系统-01</t>
+          <t>神台-01</t>
         </is>
       </c>
       <c r="D485" s="3" t="inlineStr">
         <is>
-          <t>椽系之上/瓦面之下</t>
+          <t>殿内中央区域</t>
         </is>
       </c>
       <c r="E485" s="3" t="inlineStr">
         <is>
-          <t>PARAMETRIC_COMPLETION</t>
+          <t>SYSTEM_UNKNOWN_OVERALL_DIMENSIONS</t>
         </is>
       </c>
       <c r="F485" s="3" t="inlineStr">
@@ -34355,7 +34384,7 @@
       <c r="H485" s="3" t="inlineStr"/>
       <c r="I485" s="3" t="inlineStr">
         <is>
-          <t>V007：椽与望板、瓦面总体关系确认</t>
+          <t>V007神台铺砖构造记录</t>
         </is>
       </c>
       <c r="J485" s="3" t="inlineStr"/>
@@ -34370,53 +34399,57 @@
       <c r="S485" s="3" t="inlineStr"/>
       <c r="T485" s="3" t="inlineStr"/>
       <c r="U485" s="3" t="inlineStr"/>
-      <c r="V485" s="3" t="inlineStr"/>
+      <c r="V485" s="3" t="inlineStr">
+        <is>
+          <t>四周条砖立砌压脚、表面方砖；整体长宽高UNKNOWN</t>
+        </is>
+      </c>
       <c r="W485" s="3" t="inlineStr">
         <is>
-          <t>{"record_role":"PARAMETRIC_COMPLETION","total_count":"UNKNOWN"}</t>
+          <t>{"record_role":"SYSTEM"}</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="3" t="inlineStr">
         <is>
-          <t>瓦作</t>
+          <t>屋面</t>
         </is>
       </c>
       <c r="B486" s="3" t="inlineStr">
         <is>
-          <t>正吻</t>
+          <t>望板系统</t>
         </is>
       </c>
       <c r="C486" s="3" t="inlineStr">
         <is>
-          <t>正吻-01</t>
+          <t>望板系统-01</t>
         </is>
       </c>
       <c r="D486" s="3" t="inlineStr">
         <is>
-          <t>正脊一端</t>
+          <t>椽系之上/瓦面之下</t>
         </is>
       </c>
       <c r="E486" s="3" t="inlineStr">
         <is>
-          <t>LOCKED_COUNT_SIMPLIFIED_GEOMETRY</t>
+          <t>PARAMETRIC_COMPLETION</t>
         </is>
       </c>
       <c r="F486" s="3" t="inlineStr">
         <is>
-          <t>简化Proxy</t>
+          <t>参数化补全</t>
         </is>
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>SIMPLIFIED_PROXY</t>
+          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
         </is>
       </c>
       <c r="H486" s="3" t="inlineStr"/>
       <c r="I486" s="3" t="inlineStr">
         <is>
-          <t>V007数量2</t>
+          <t>V007：椽与望板、瓦面总体关系确认</t>
         </is>
       </c>
       <c r="J486" s="3" t="inlineStr"/>
@@ -34434,7 +34467,7 @@
       <c r="V486" s="3" t="inlineStr"/>
       <c r="W486" s="3" t="inlineStr">
         <is>
-          <t>{"record_role":"SIMPLIFIED_PROXY"}</t>
+          <t>{"record_role":"PARAMETRIC_COMPLETION","total_count":"UNKNOWN"}</t>
         </is>
       </c>
     </row>
@@ -34451,12 +34484,12 @@
       </c>
       <c r="C487" s="3" t="inlineStr">
         <is>
-          <t>正吻-02</t>
+          <t>正吻-01</t>
         </is>
       </c>
       <c r="D487" s="3" t="inlineStr">
         <is>
-          <t>正脊另一端</t>
+          <t>正脊一端</t>
         </is>
       </c>
       <c r="E487" s="3" t="inlineStr">
@@ -34507,17 +34540,17 @@
       </c>
       <c r="B488" s="3" t="inlineStr">
         <is>
-          <t>垂兽</t>
+          <t>正吻</t>
         </is>
       </c>
       <c r="C488" s="3" t="inlineStr">
         <is>
-          <t>垂兽-01</t>
+          <t>正吻-02</t>
         </is>
       </c>
       <c r="D488" s="3" t="inlineStr">
         <is>
-          <t>垂脊01</t>
+          <t>正脊另一端</t>
         </is>
       </c>
       <c r="E488" s="3" t="inlineStr">
@@ -34538,7 +34571,7 @@
       <c r="H488" s="3" t="inlineStr"/>
       <c r="I488" s="3" t="inlineStr">
         <is>
-          <t>V007数量4</t>
+          <t>V007数量2</t>
         </is>
       </c>
       <c r="J488" s="3" t="inlineStr"/>
@@ -34573,12 +34606,12 @@
       </c>
       <c r="C489" s="3" t="inlineStr">
         <is>
-          <t>垂兽-02</t>
+          <t>垂兽-01</t>
         </is>
       </c>
       <c r="D489" s="3" t="inlineStr">
         <is>
-          <t>垂脊02</t>
+          <t>垂脊01</t>
         </is>
       </c>
       <c r="E489" s="3" t="inlineStr">
@@ -34634,12 +34667,12 @@
       </c>
       <c r="C490" s="3" t="inlineStr">
         <is>
-          <t>垂兽-03</t>
+          <t>垂兽-02</t>
         </is>
       </c>
       <c r="D490" s="3" t="inlineStr">
         <is>
-          <t>垂脊03</t>
+          <t>垂脊02</t>
         </is>
       </c>
       <c r="E490" s="3" t="inlineStr">
@@ -34695,12 +34728,12 @@
       </c>
       <c r="C491" s="3" t="inlineStr">
         <is>
-          <t>垂兽-04</t>
+          <t>垂兽-03</t>
         </is>
       </c>
       <c r="D491" s="3" t="inlineStr">
         <is>
-          <t>垂脊04</t>
+          <t>垂脊03</t>
         </is>
       </c>
       <c r="E491" s="3" t="inlineStr">
@@ -34751,17 +34784,17 @@
       </c>
       <c r="B492" s="3" t="inlineStr">
         <is>
-          <t>戗兽</t>
+          <t>垂兽</t>
         </is>
       </c>
       <c r="C492" s="3" t="inlineStr">
         <is>
-          <t>戗兽-01</t>
+          <t>垂兽-04</t>
         </is>
       </c>
       <c r="D492" s="3" t="inlineStr">
         <is>
-          <t>戗脊01</t>
+          <t>垂脊04</t>
         </is>
       </c>
       <c r="E492" s="3" t="inlineStr">
@@ -34817,12 +34850,12 @@
       </c>
       <c r="C493" s="3" t="inlineStr">
         <is>
-          <t>戗兽-02</t>
+          <t>戗兽-01</t>
         </is>
       </c>
       <c r="D493" s="3" t="inlineStr">
         <is>
-          <t>戗脊02</t>
+          <t>戗脊01</t>
         </is>
       </c>
       <c r="E493" s="3" t="inlineStr">
@@ -34878,12 +34911,12 @@
       </c>
       <c r="C494" s="3" t="inlineStr">
         <is>
-          <t>戗兽-03</t>
+          <t>戗兽-02</t>
         </is>
       </c>
       <c r="D494" s="3" t="inlineStr">
         <is>
-          <t>戗脊03</t>
+          <t>戗脊02</t>
         </is>
       </c>
       <c r="E494" s="3" t="inlineStr">
@@ -34939,12 +34972,12 @@
       </c>
       <c r="C495" s="3" t="inlineStr">
         <is>
-          <t>戗兽-04</t>
+          <t>戗兽-03</t>
         </is>
       </c>
       <c r="D495" s="3" t="inlineStr">
         <is>
-          <t>戗脊04</t>
+          <t>戗脊03</t>
         </is>
       </c>
       <c r="E495" s="3" t="inlineStr">
@@ -34995,17 +35028,17 @@
       </c>
       <c r="B496" s="3" t="inlineStr">
         <is>
-          <t>仙人</t>
+          <t>戗兽</t>
         </is>
       </c>
       <c r="C496" s="3" t="inlineStr">
         <is>
-          <t>仙人-01</t>
+          <t>戗兽-04</t>
         </is>
       </c>
       <c r="D496" s="3" t="inlineStr">
         <is>
-          <t>四角戗脊端部-01</t>
+          <t>戗脊04</t>
         </is>
       </c>
       <c r="E496" s="3" t="inlineStr">
@@ -35061,12 +35094,12 @@
       </c>
       <c r="C497" s="3" t="inlineStr">
         <is>
-          <t>仙人-02</t>
+          <t>仙人-01</t>
         </is>
       </c>
       <c r="D497" s="3" t="inlineStr">
         <is>
-          <t>四角戗脊端部-02</t>
+          <t>四角戗脊端部-01</t>
         </is>
       </c>
       <c r="E497" s="3" t="inlineStr">
@@ -35122,12 +35155,12 @@
       </c>
       <c r="C498" s="3" t="inlineStr">
         <is>
-          <t>仙人-03</t>
+          <t>仙人-02</t>
         </is>
       </c>
       <c r="D498" s="3" t="inlineStr">
         <is>
-          <t>四角戗脊端部-03</t>
+          <t>四角戗脊端部-02</t>
         </is>
       </c>
       <c r="E498" s="3" t="inlineStr">
@@ -35183,12 +35216,12 @@
       </c>
       <c r="C499" s="3" t="inlineStr">
         <is>
-          <t>仙人-04</t>
+          <t>仙人-03</t>
         </is>
       </c>
       <c r="D499" s="3" t="inlineStr">
         <is>
-          <t>四角戗脊端部-04</t>
+          <t>四角戗脊端部-03</t>
         </is>
       </c>
       <c r="E499" s="3" t="inlineStr">
@@ -35234,43 +35267,43 @@
     <row r="500">
       <c r="A500" s="3" t="inlineStr">
         <is>
-          <t>围护</t>
+          <t>瓦作</t>
         </is>
       </c>
       <c r="B500" s="3" t="inlineStr">
         <is>
-          <t>门木作系统</t>
+          <t>仙人</t>
         </is>
       </c>
       <c r="C500" s="3" t="inlineStr">
         <is>
-          <t>门木作-南</t>
+          <t>仙人-04</t>
         </is>
       </c>
       <c r="D500" s="3" t="inlineStr">
         <is>
-          <t>南立面中央门洞</t>
+          <t>四角戗脊端部-04</t>
         </is>
       </c>
       <c r="E500" s="3" t="inlineStr">
         <is>
-          <t>VISUAL_MODEL_PARAMETRIC_SECTION</t>
+          <t>LOCKED_COUNT_SIMPLIFIED_GEOMETRY</t>
         </is>
       </c>
       <c r="F500" s="3" t="inlineStr">
         <is>
-          <t>参数化补全</t>
+          <t>简化Proxy</t>
         </is>
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
+          <t>SIMPLIFIED_PROXY</t>
         </is>
       </c>
       <c r="H500" s="3" t="inlineStr"/>
       <c r="I500" s="3" t="inlineStr">
         <is>
-          <t>V007南立面测绘图</t>
+          <t>V007数量4</t>
         </is>
       </c>
       <c r="J500" s="3" t="inlineStr"/>
@@ -35285,14 +35318,10 @@
       <c r="S500" s="3" t="inlineStr"/>
       <c r="T500" s="3" t="inlineStr"/>
       <c r="U500" s="3" t="inlineStr"/>
-      <c r="V500" s="3" t="inlineStr">
-        <is>
-          <t>分格视觉可建；木料断面/榫卯/完整单件尺寸UNKNOWN</t>
-        </is>
-      </c>
+      <c r="V500" s="3" t="inlineStr"/>
       <c r="W500" s="3" t="inlineStr">
         <is>
-          <t>{"record_role":"VISUAL_MODEL"}</t>
+          <t>{"record_role":"SIMPLIFIED_PROXY"}</t>
         </is>
       </c>
     </row>
@@ -35309,12 +35338,12 @@
       </c>
       <c r="C501" s="3" t="inlineStr">
         <is>
-          <t>门木作-北</t>
+          <t>门木作-南</t>
         </is>
       </c>
       <c r="D501" s="3" t="inlineStr">
         <is>
-          <t>北立面中央门洞</t>
+          <t>南立面中央门洞</t>
         </is>
       </c>
       <c r="E501" s="3" t="inlineStr">
@@ -35335,7 +35364,7 @@
       <c r="H501" s="3" t="inlineStr"/>
       <c r="I501" s="3" t="inlineStr">
         <is>
-          <t>V007北立面测绘图</t>
+          <t>V007南立面测绘图</t>
         </is>
       </c>
       <c r="J501" s="3" t="inlineStr"/>
@@ -35369,17 +35398,17 @@
       </c>
       <c r="B502" s="3" t="inlineStr">
         <is>
-          <t>窗木作系统</t>
+          <t>门木作系统</t>
         </is>
       </c>
       <c r="C502" s="3" t="inlineStr">
         <is>
-          <t>窗木作-南东</t>
+          <t>门木作-北</t>
         </is>
       </c>
       <c r="D502" s="3" t="inlineStr">
         <is>
-          <t>南立面东窗</t>
+          <t>北立面中央门洞</t>
         </is>
       </c>
       <c r="E502" s="3" t="inlineStr">
@@ -35400,7 +35429,7 @@
       <c r="H502" s="3" t="inlineStr"/>
       <c r="I502" s="3" t="inlineStr">
         <is>
-          <t>V007南立面测绘图</t>
+          <t>V007北立面测绘图</t>
         </is>
       </c>
       <c r="J502" s="3" t="inlineStr"/>
@@ -35439,12 +35468,12 @@
       </c>
       <c r="C503" s="3" t="inlineStr">
         <is>
-          <t>窗木作-南西</t>
+          <t>窗木作-南东</t>
         </is>
       </c>
       <c r="D503" s="3" t="inlineStr">
         <is>
-          <t>南立面西窗</t>
+          <t>南立面东窗</t>
         </is>
       </c>
       <c r="E503" s="3" t="inlineStr">
@@ -35494,47 +35523,43 @@
     <row r="504">
       <c r="A504" s="3" t="inlineStr">
         <is>
-          <t>外檐斗栱</t>
+          <t>围护</t>
         </is>
       </c>
       <c r="B504" s="3" t="inlineStr">
         <is>
-          <t>单向长开斗族</t>
+          <t>窗木作系统</t>
         </is>
       </c>
       <c r="C504" s="3" t="inlineStr">
         <is>
-          <t>单向长开斗族-UNKNOWN</t>
+          <t>窗木作-南西</t>
         </is>
       </c>
       <c r="D504" s="3" t="inlineStr">
         <is>
-          <t>全殿斗栱体系</t>
+          <t>南立面西窗</t>
         </is>
       </c>
       <c r="E504" s="3" t="inlineStr">
         <is>
-          <t>FAMILY_UNKNOWN_COUNT</t>
+          <t>VISUAL_MODEL_PARAMETRIC_SECTION</t>
         </is>
       </c>
       <c r="F504" s="3" t="inlineStr">
         <is>
-          <t>已有Master｜族边界UNKNOWN</t>
+          <t>参数化补全</t>
         </is>
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>APPROVED_MASTER_AVAILABLE</t>
-        </is>
-      </c>
-      <c r="H504" s="3" t="inlineStr">
-        <is>
-          <t>CMP-DOU-SINGLE-LONGKAI-001_MASTER</t>
-        </is>
-      </c>
+          <t>NOT_MASTER_TRACKED / PARAMETRIC_COMPLETION</t>
+        </is>
+      </c>
+      <c r="H504" s="3" t="inlineStr"/>
       <c r="I504" s="3" t="inlineStr">
         <is>
-          <t>V007确认存在但全殿数量未闭合</t>
+          <t>V007南立面测绘图</t>
         </is>
       </c>
       <c r="J504" s="3" t="inlineStr"/>
@@ -35549,10 +35574,14 @@
       <c r="S504" s="3" t="inlineStr"/>
       <c r="T504" s="3" t="inlineStr"/>
       <c r="U504" s="3" t="inlineStr"/>
-      <c r="V504" s="3" t="inlineStr"/>
+      <c r="V504" s="3" t="inlineStr">
+        <is>
+          <t>分格视觉可建；木料断面/榫卯/完整单件尺寸UNKNOWN</t>
+        </is>
+      </c>
       <c r="W504" s="3" t="inlineStr">
         <is>
-          <t>{"record_role":"FAMILY_UNKNOWN_COUNT","total_count":"UNKNOWN"}</t>
+          <t>{"record_role":"VISUAL_MODEL"}</t>
         </is>
       </c>
     </row>
@@ -35564,12 +35593,12 @@
       </c>
       <c r="B505" s="3" t="inlineStr">
         <is>
-          <t>交互斗族</t>
+          <t>单向长开斗族</t>
         </is>
       </c>
       <c r="C505" s="3" t="inlineStr">
         <is>
-          <t>交互斗族-UNKNOWN</t>
+          <t>单向长开斗族-UNKNOWN</t>
         </is>
       </c>
       <c r="D505" s="3" t="inlineStr">
@@ -35594,7 +35623,7 @@
       </c>
       <c r="H505" s="3" t="inlineStr">
         <is>
-          <t>CMP-DOU-INTERACTIVE-001_MASTER</t>
+          <t>CMP-DOU-SINGLE-LONGKAI-001_MASTER</t>
         </is>
       </c>
       <c r="I505" s="3" t="inlineStr">
@@ -35629,12 +35658,12 @@
       </c>
       <c r="B506" s="3" t="inlineStr">
         <is>
-          <t>散斗族</t>
+          <t>交互斗族</t>
         </is>
       </c>
       <c r="C506" s="3" t="inlineStr">
         <is>
-          <t>散斗族-UNKNOWN</t>
+          <t>交互斗族-UNKNOWN</t>
         </is>
       </c>
       <c r="D506" s="3" t="inlineStr">
@@ -35649,15 +35678,19 @@
       </c>
       <c r="F506" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN/参考边界</t>
+          <t>已有Master｜族边界UNKNOWN</t>
         </is>
       </c>
       <c r="G506" s="3" t="inlineStr">
         <is>
-          <t>UNKNOWN_REFERENCE_BOUNDARY</t>
-        </is>
-      </c>
-      <c r="H506" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H506" s="3" t="inlineStr">
+        <is>
+          <t>CMP-DOU-INTERACTIVE-001_MASTER</t>
+        </is>
+      </c>
       <c r="I506" s="3" t="inlineStr">
         <is>
           <t>V007确认存在但全殿数量未闭合</t>
@@ -35685,22 +35718,22 @@
     <row r="507">
       <c r="A507" s="3" t="inlineStr">
         <is>
-          <t>内槽</t>
+          <t>外檐斗栱</t>
         </is>
       </c>
       <c r="B507" s="3" t="inlineStr">
         <is>
-          <t>替木实体族</t>
+          <t>散斗族</t>
         </is>
       </c>
       <c r="C507" s="3" t="inlineStr">
         <is>
-          <t>替木实体族-UNKNOWN</t>
+          <t>散斗族-UNKNOWN</t>
         </is>
       </c>
       <c r="D507" s="3" t="inlineStr">
         <is>
-          <t>全殿多处</t>
+          <t>全殿斗栱体系</t>
         </is>
       </c>
       <c r="E507" s="3" t="inlineStr">
@@ -35721,7 +35754,7 @@
       <c r="H507" s="3" t="inlineStr"/>
       <c r="I507" s="3" t="inlineStr">
         <is>
-          <t>V007：23条测量记录不等于全殿总数</t>
+          <t>V007确认存在但全殿数量未闭合</t>
         </is>
       </c>
       <c r="J507" s="3" t="inlineStr"/>
@@ -35736,19 +35769,80 @@
       <c r="S507" s="3" t="inlineStr"/>
       <c r="T507" s="3" t="inlineStr"/>
       <c r="U507" s="3" t="inlineStr"/>
-      <c r="V507" s="3" t="inlineStr">
+      <c r="V507" s="3" t="inlineStr"/>
+      <c r="W507" s="3" t="inlineStr">
+        <is>
+          <t>{"record_role":"FAMILY_UNKNOWN_COUNT","total_count":"UNKNOWN"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="3" t="inlineStr">
+        <is>
+          <t>内槽</t>
+        </is>
+      </c>
+      <c r="B508" s="3" t="inlineStr">
+        <is>
+          <t>替木实体族</t>
+        </is>
+      </c>
+      <c r="C508" s="3" t="inlineStr">
+        <is>
+          <t>替木实体族-UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D508" s="3" t="inlineStr">
+        <is>
+          <t>全殿多处</t>
+        </is>
+      </c>
+      <c r="E508" s="3" t="inlineStr">
+        <is>
+          <t>FAMILY_UNKNOWN_COUNT</t>
+        </is>
+      </c>
+      <c r="F508" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN/参考边界</t>
+        </is>
+      </c>
+      <c r="G508" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN_REFERENCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="H508" s="3" t="inlineStr"/>
+      <c r="I508" s="3" t="inlineStr">
+        <is>
+          <t>V007：23条测量记录不等于全殿总数</t>
+        </is>
+      </c>
+      <c r="J508" s="3" t="inlineStr"/>
+      <c r="K508" s="3" t="inlineStr"/>
+      <c r="L508" s="3" t="inlineStr"/>
+      <c r="M508" s="3" t="inlineStr"/>
+      <c r="N508" s="3" t="inlineStr"/>
+      <c r="O508" s="3" t="inlineStr"/>
+      <c r="P508" s="3" t="inlineStr"/>
+      <c r="Q508" s="3" t="inlineStr"/>
+      <c r="R508" s="3" t="inlineStr"/>
+      <c r="S508" s="3" t="inlineStr"/>
+      <c r="T508" s="3" t="inlineStr"/>
+      <c r="U508" s="3" t="inlineStr"/>
+      <c r="V508" s="3" t="inlineStr">
         <is>
           <t>测量统计仍由替木测量边界记录承载</t>
         </is>
       </c>
-      <c r="W507" s="3" t="inlineStr">
+      <c r="W508" s="3" t="inlineStr">
         <is>
           <t>{"record_role":"FAMILY_UNKNOWN_COUNT","total_count":"UNKNOWN"}</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W507"/>
+  <autoFilter ref="A1:W508"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -35762,7 +35856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C98"/>
+  <dimension ref="A1:C100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -35810,11 +35904,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>内槽</t>
+          <t>主体梁架</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -35825,11 +35919,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>台基</t>
+          <t>内槽</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -35840,11 +35934,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>围护</t>
+          <t>台基</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -35855,11 +35949,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>外檐斗栱</t>
+          <t>围护</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>283</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -35870,11 +35964,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>室内地面</t>
+          <t>外檐斗栱</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8">
@@ -35885,11 +35979,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>室内设施</t>
+          <t>室内地面</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -35900,11 +35994,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>屋面</t>
+          <t>室内设施</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -35915,26 +36009,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>瓦作</t>
+          <t>屋面</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>构件/对象</t>
+          <t>系统</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>丁栿</t>
+          <t>瓦作</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -35945,11 +36039,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>上六椽栿</t>
+          <t>丁栿</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -35960,7 +36054,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>下六椽栿</t>
+          <t>上六椽栿</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -35975,11 +36069,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>东坡筒瓦</t>
+          <t>下六椽栿</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -35990,11 +36084,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>乳栿</t>
+          <t>东坡筒瓦</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -36005,11 +36099,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>二昂</t>
+          <t>乳栿</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -36020,11 +36114,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>交互斗族</t>
+          <t>二昂</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -36035,11 +36129,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>仙人</t>
+          <t>交互斗族</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -36050,11 +36144,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>令栱</t>
+          <t>仙人</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -36065,11 +36159,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>内槽斗栱/隔架位置</t>
+          <t>令栱</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
@@ -36080,11 +36174,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>剳牵</t>
+          <t>令栱（梁架承托）</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -36095,7 +36189,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>北坡筒瓦</t>
+          <t>内槽斗栱/隔架位置</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -36110,11 +36204,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>北门洞</t>
+          <t>剳牵</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -36125,11 +36219,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>华栱</t>
+          <t>北坡筒瓦</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -36140,7 +36234,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>单向长开斗族</t>
+          <t>北门洞</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -36155,11 +36249,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>南坡筒瓦</t>
+          <t>华栱</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27">
@@ -36170,11 +36264,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>南立面窗洞</t>
+          <t>单向长开斗族</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -36185,7 +36279,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>南门洞</t>
+          <t>南坡筒瓦</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -36200,11 +36294,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>叉手</t>
+          <t>南立面窗洞</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -36215,7 +36309,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>台基整体</t>
+          <t>南门洞</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -36230,11 +36324,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>四椽栿</t>
+          <t>叉手</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
@@ -36245,11 +36339,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>垂兽</t>
+          <t>台基整体</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -36260,11 +36354,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>垂脊</t>
+          <t>四椽栿</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -36275,7 +36369,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>墙体</t>
+          <t>垂兽</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -36290,11 +36384,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>墙砖族</t>
+          <t>垂脊</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -36305,11 +36399,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>大型慢栱</t>
+          <t>墙体</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -36320,11 +36414,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>大型瓜子栱</t>
+          <t>墙砖族</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -36335,11 +36429,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>大角梁</t>
+          <t>大型慢栱</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39">
@@ -36350,7 +36444,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>头昂</t>
+          <t>大型瓜子栱</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -36365,7 +36459,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>子角梁</t>
+          <t>大角梁</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -36380,11 +36474,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>室内地面系统</t>
+          <t>头昂</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42">
@@ -36395,11 +36489,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>室内方砖族</t>
+          <t>子角梁</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -36410,7 +36504,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>室内条砖族</t>
+          <t>室内地面系统</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -36425,11 +36519,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>小型慢栱</t>
+          <t>室内方砖族</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -36440,11 +36534,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>小型瓜子栱</t>
+          <t>室内条砖族</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -36455,11 +36549,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>嵌墙石碑</t>
+          <t>小型慢栱</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47">
@@ -36470,11 +36564,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>平梁</t>
+          <t>小型瓜子栱</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48">
@@ -36485,11 +36579,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>戗兽</t>
+          <t>嵌墙石碑</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -36500,7 +36594,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>戗脊</t>
+          <t>平梁</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -36515,11 +36609,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>托脚</t>
+          <t>戗兽</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -36530,11 +36624,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>散斗族</t>
+          <t>戗脊</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -36545,11 +36639,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>替木实体族</t>
+          <t>托脚</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53">
@@ -36560,7 +36654,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>替木测量边界</t>
+          <t>散斗族</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -36575,7 +36669,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>望板系统</t>
+          <t>替木实体族</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -36590,11 +36684,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>柱</t>
+          <t>替木测量边界</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -36605,11 +36699,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>柱头栌斗</t>
+          <t>望板系统</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -36620,11 +36714,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>柱头铺作</t>
+          <t>柱</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58">
@@ -36635,11 +36729,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>椽系</t>
+          <t>柱头栌斗</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59">
@@ -36650,11 +36744,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>槫</t>
+          <t>柱头铺作</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60">
@@ -36665,11 +36759,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>正吻</t>
+          <t>椽系</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -36680,11 +36774,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>正脊</t>
+          <t>槫</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62">
@@ -36695,11 +36789,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>由额</t>
+          <t>正吻</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -36710,7 +36804,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>神台</t>
+          <t>正脊</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -36725,11 +36819,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>窗木作系统</t>
+          <t>由额</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -36740,11 +36834,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>蜀柱</t>
+          <t>神台</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -36755,11 +36849,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>补间铺作</t>
+          <t>窗木作系统</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -36770,11 +36864,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>补间铺作底斗</t>
+          <t>蜀柱</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
@@ -36785,7 +36879,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>襻间枋</t>
+          <t>补间铺作</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -36800,11 +36894,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>西坡筒瓦</t>
+          <t>补间铺作底斗</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70">
@@ -36815,11 +36909,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>角石</t>
+          <t>襻间枋</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71">
@@ -36830,11 +36924,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>转角铺作</t>
+          <t>西坡筒瓦</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -36845,11 +36939,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>透风孔</t>
+          <t>角石</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
@@ -36860,11 +36954,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>铺作方向单元</t>
+          <t>转角铺作</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -36875,11 +36969,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>门木作系统</t>
+          <t>透风孔</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75">
@@ -36890,11 +36984,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>阑额</t>
+          <t>铺作方向单元</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
     </row>
     <row r="76">
@@ -36905,11 +36999,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>隐角梁</t>
+          <t>门木作系统</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -36920,41 +37014,41 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>驼峰</t>
+          <t>阑额</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>数量/状态口径</t>
+          <t>构件/对象</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>COUNTING_UNIT_NOT_PHYSICAL</t>
+          <t>隐角梁</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>数量/状态口径</t>
+          <t>构件/对象</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FAMILY_UNKNOWN_COUNT</t>
+          <t>驼峰</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -36965,11 +37059,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LOCKED</t>
+          <t>COUNTING_UNIT_NOT_PHYSICAL</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row r="81">
@@ -36980,11 +37074,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LOCKED_ARRAY</t>
+          <t>FAMILY_UNKNOWN_COUNT</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82">
@@ -36995,11 +37089,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LOCKED_COUNT_LOCATION</t>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>4</v>
+        <v>118</v>
       </c>
     </row>
     <row r="83">
@@ -37010,7 +37104,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LOCKED_COUNT_PARAMETRIC_GEOMETRY</t>
+          <t>LOCKED_ARRAY</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -37025,11 +37119,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LOCKED_COUNT_SIMPLIFIED_GEOMETRY</t>
+          <t>LOCKED_COUNT_LOCATION</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
@@ -37040,11 +37134,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>LOCKED_DERIVED</t>
+          <t>LOCKED_COUNT_PARAMETRIC_GEOMETRY</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>164</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
@@ -37055,11 +37149,11 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>LOCKED_ID_PARTIAL_LOCATION</t>
+          <t>LOCKED_COUNT_SIMPLIFIED_GEOMETRY</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="87">
@@ -37070,11 +37164,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LOCKED_ID_UNKNOWN_LOCATION</t>
+          <t>LOCKED_DERIVED</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10</v>
+        <v>164</v>
       </c>
     </row>
     <row r="88">
@@ -37085,11 +37179,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LOCKED_LOCATION</t>
+          <t>LOCKED_ID_PARTIAL_LOCATION</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
@@ -37100,11 +37194,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LOCKED_OUTER_UNKNOWN_INTERNAL</t>
+          <t>LOCKED_ID_UNKNOWN_LOCATION</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90">
@@ -37115,11 +37209,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LOCKED_SITE</t>
+          <t>LOCKED_LOCATION</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91">
@@ -37130,7 +37224,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LOCKED_SITE_COUNT</t>
+          <t>LOCKED_OUTER_UNKNOWN_INTERNAL</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -37145,11 +37239,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LOCKED_SITE_PATTERN</t>
+          <t>LOCKED_SITE</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
     </row>
     <row r="93">
@@ -37160,11 +37254,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LOCKED_SUBSET</t>
+          <t>LOCKED_SITE_COUNT</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -37175,11 +37269,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MEASUREMENT_SAMPLE_NOT_TOTAL</t>
+          <t>LOCKED_SITE_PATTERN</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95">
@@ -37190,11 +37284,11 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PARAMETRIC_COMPLETION</t>
+          <t>LOCKED_SUBSET</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="96">
@@ -37205,11 +37299,11 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SYSTEM_PARAMETRIC</t>
+          <t>MEASUREMENT_SAMPLE_NOT_TOTAL</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -37220,11 +37314,11 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SYSTEM_UNKNOWN_OVERALL_DIMENSIONS</t>
+          <t>PARAMETRIC_COMPLETION</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -37235,10 +37329,40 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
+          <t>SYSTEM_PARAMETRIC</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>数量/状态口径</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SYSTEM_UNKNOWN_OVERALL_DIMENSIONS</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>数量/状态口径</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
           <t>VISUAL_MODEL_PARAMETRIC_SECTION</t>
         </is>
       </c>
-      <c r="C98" t="n">
+      <c r="C100" t="n">
         <v>4</v>
       </c>
     </row>
@@ -37339,7 +37463,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="8">
@@ -37349,7 +37473,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9">
@@ -37359,7 +37483,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -37369,7 +37493,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
@@ -37390,7 +37514,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>96.7%</t>
         </is>
       </c>
     </row>
@@ -37401,7 +37525,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
@@ -37412,7 +37536,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>a91b2eed91ec238b6d4bacf9c4ff365c51d1c0ec</t>
+          <t>2f3b22278ccffd3bebdfcd19c4355f07ad242cb4</t>
         </is>
       </c>
     </row>
@@ -37424,7 +37548,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>89a56c31daef3141814d5d085470f8499cbdc9fc342cc15d1976ff619b3dddff</t>
+          <t>750988e8eec72f5703aec60a0dcf62d472cdb8ac0f2dffe51565e6de967f3013</t>
         </is>
       </c>
     </row>

--- a/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
+++ b/docs/evidence/zhenguo_wanfo/derived/P3_WANFO_COMPONENT_INSTANCE_REGISTRY_CURRENT.xlsx
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>0.9670000000000001</v>
+        <v>1</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
@@ -1003,15 +1003,19 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>需新建Master</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr"/>
+          <t>已有Master｜族边界UNKNOWN</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-LINGGONG-INTERIOR-001_MASTER</t>
+        </is>
+      </c>
       <c r="E24" s="3" t="n">
         <v>1</v>
       </c>
@@ -30002,15 +30006,19 @@
       </c>
       <c r="F414" s="3" t="inlineStr">
         <is>
-          <t>需新建Master</t>
+          <t>已有Master｜族边界UNKNOWN</t>
         </is>
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>MASTER_REQUIRED_PENDING</t>
-        </is>
-      </c>
-      <c r="H414" s="3" t="inlineStr"/>
+          <t>APPROVED_MASTER_AVAILABLE</t>
+        </is>
+      </c>
+      <c r="H414" s="3" t="inlineStr">
+        <is>
+          <t>CMP-FRAME-LINGGONG-INTERIOR-001_MASTER</t>
+        </is>
+      </c>
       <c r="I414" s="3" t="inlineStr">
         <is>
           <t>A2同建筑官方数字专题直接说明“ 四椽栿上用驼峰、令栱承平梁 ”，足以锁定构件身份与承托角色。现有 CMP-GONG-LINGGONG-001_MASTER 的 897×217.4×155.6 mm 及14点轮廓来自28个外檐斗栱令栱样本，不得静默继承到梁架内部角色。当前 bound evidence 未隔离出梁架承托令栱的独立历史尺寸、精确轮廓或隐藏榫卯。</t>
@@ -30035,7 +30043,7 @@
       </c>
       <c r="W414" s="3" t="inlineStr">
         <is>
-          <t>{"known_unknowns":["whole_hall_instance_count","exact_per_instance_mapping","exact_length","exact_width_depth","exact_profile","hidden_joinery","equivalence_to_outer_eaves_linggong"],"modeling_disposition":"SOURCE_GUIDED_SIMPLIFIED / ASSEMBLY_ENVELOPE_OWNED / REPLACEABLE","planned_master_reference":"CMP-FRAME-LINGGONG-INTERIOR-001_MASTER","record_role":"FAMILY_UNKNOWN_COUNT","source_binding":"docs/evidence/zhenguo_wanfo/P3_3_INTERIOR_LINGGONG_SOURCE_BINDING_V001.md","total_count":"UNKNOWN"}</t>
+          <t>{"formalization":{"artifact_digest":"sha256:397adf6552f3f1d9d4791cc8dbaf3ea5197ee556c673aee11ade113c3491610d","artifact_id":11394896083,"canonical_blend_sha256":"82a16ddf3c3d727ddd4cb03408ade7b4ff9a25afd8a42cb7215edc2178a22301","geometry_signature":"7ef466c39b08f7485da1c7e91af8882446da7f6d9546668ac28132445d19232f","merge_authorized":false,"run_id":37424767731,"status":"FORMALIZED / PRODUCT_OWNER_APPROVED"},"hidden_joinery":"UNKNOWN / DEFERRED","historical_metric_dimensions":"UNKNOWN","historical_profile":"UNKNOWN","known_unknowns":["whole_hall_instance_count","exact_per_instance_mapping","exact_length","exact_width_depth","exact_profile","hidden_joinery","equivalence_to_outer_eaves_linggong"],"master_readiness":"APPROVED_MASTER_AVAILABLE / MP01B ASSEMBLY READY SUBJECT TO LOCAL METRIC ENVELOPE","master_variants":["LOWER_PINGLIANG_SUPPORT"],"modeling_disposition":"APPROVED_MASTER_AVAILABLE / ASSEMBLY_METRIC_ENVELOPE_OWNED / HISTORICAL_METRICS_PROFILE_UNKNOWN","planned_master_reference":"CMP-FRAME-LINGGONG-INTERIOR-001_MASTER","record_role":"FAMILY_UNKNOWN_COUNT","source_binding":"docs/evidence/zhenguo_wanfo/P3_3_INTERIOR_LINGGONG_SOURCE_BINDING_V001.md","total_count":"UNKNOWN"}</t>
         </is>
       </c>
     </row>
@@ -37493,7 +37501,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11">
@@ -37503,7 +37511,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -37514,7 +37522,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
@@ -37525,7 +37533,7 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
@@ -37536,7 +37544,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2f3b22278ccffd3bebdfcd19c4355f07ad242cb4</t>
+          <t>ebf1e73ed307b262a367e68f80382754fe4353e3</t>
         </is>
       </c>
     </row>
@@ -37548,7 +37556,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>750988e8eec72f5703aec60a0dcf62d472cdb8ac0f2dffe51565e6de967f3013</t>
+          <t>db1420d39f8a81356bddafba4806b8468898105c5224cc5b2bcbef8cd148ff05</t>
         </is>
       </c>
     </row>
